--- a/premise/data/additional_inventories/lci-electric-car-mechanical-powertrain.xlsx
+++ b/premise/data/additional_inventories/lci-electric-car-mechanical-powertrain.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H98"/>
+  <dimension ref="A1:H168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2425,6 +2425,1709 @@
       </c>
       <c r="H98" t="inlineStr"/>
     </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>permanent magnet, measured B3 grade, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B103">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>permanent magnet, measured B3 grade, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Jones etal2025 DOI10.1021/jacs.5c04150 SI TableS2, samplesB3 andA1; Hsieh etal2026 DOI10.1007/s11367-026-02610-7 SI TableS11 PMSM bulk components.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>APPROVED TRACTION MAGNET GRADE REFERENCES, issue36, 2026-10-18. Jones etal2025 DOI10.1021/jacs.5c04150 SI TableS2, samplesB3 andA1; Hsieh etal2026 DOI10.1007/s11367-026-02610-7 SI TableS11 PMSM bulk components. Select one measured B3 magnet as engineering composition reference, NOT fleet average from two rotors. B3 masspercent:Nd21.9,Pr7.4,Tb0.5,Ho1.7,Co2.2,B0.9,Al0.2,Ca0.2,Fe64.8,Cu0.2 (sum100);Dy not detected, not proof absolutezero. Separate A1 sensitivity:Nd26.6,Tb0.6,Dy0.5,Ho2.2,Co2.4,B0.9,Al0.2,Ca0.1,Ti0.2,Fe66.2,Cu0.2;roundedsource99.9 normalized by99.9. Grade choice has substantialNd/Pr/Dy/Tb/Ho/Co sensitivity; unknown fleet penetration,gradeevolution and coercivity requirements remain gaps. Purchase individual oxide suppliers at stoichiometric containedmetal equivalents Nd2O3,Pr6O11,Tb4O7,Ho2O3,Dy2O3,Coasmetal,othermetals explicitly; B usesboricoxide/Causesquicklime/TiusesTiO2 as supply proxies. Oxide-to-metal reduction/reagents,oxygen/byproduct fate,boron/calciumretention and magnet coating are unresolved manufacturing gaps, not a closed full metallurgical process. Assume95percent magnet-material retention, matching5percentfinishedoffcut treatmentproxy, no recyclingcredit; yield sensitivity85-100percent and15kWh/kgmagnetprocess sensitivity5-30. Wholeoxide feed mass can exceed finishedmagnet mass due to oxygen:do not normalize elementalshares by gross feed mass. New roadmotor uses public PMSM non-magnet proportions20.3kgelectricalsteel,4.8Cu,14.6Al,3.9balance allocatedordinary steel as explicit shaft/bearingproxy. Missing source3.9kg componentbreakdown is not a measured steelrecipe. Keep existing0.03735849kgfinishedmagnet/kgmotor and all vehicle motor masses rather than resize magnetdemand to1.3/44.9kg/kg from a differentmotor. Distribute remainingmass across public non-magnet proportions; electricalsteelexisting3.2percentSi reference. Genericmetalworking+1kWh/kgassembly,100percentmotorassemblyretention. Existing motorsteel/Algrades remainproxies; efficiency/torque/voltage not revalidated. Dedicated name outside genericEVmetaloverlay deliberately fixes this source design over time; avoids aluminum overlay doublecount and Nd-onlyoverwrite. No unsupported future gradelearning; future static-vs-learning comparison remains required. Rewire direct car/truck/bus roadmotor inputs and explicit roadperMJ copies; inductionrail/tram unchanged. Existing sourcevehicle life andMJallocation retained. Native backgroundmotor and genericmagnet supplies remain unchanged for other consumers. Individualoxideproviders keep REidentities visible to containedmetal accounting; no primary/secondary claim.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>permanent magnet, measured B3 grade, engineering reference</t>
+        </is>
+      </c>
+      <c r="B110">
+        <v>1</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>permanent magnet, measured B3 grade, engineering reference</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>permanent magnet, measured B3 grade, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>market for neodymium oxide</t>
+        </is>
+      </c>
+      <c r="B111">
+        <v>0.26888051074984365</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>neodymium oxide</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>neodymium oxide</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>market for praseodymium oxide</t>
+        </is>
+      </c>
+      <c r="B112">
+        <v>0.09410939453838814</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>praseodymium oxide</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>praseodymium oxide</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>market for terbium oxide</t>
+        </is>
+      </c>
+      <c r="B113">
+        <v>0.00619038071051995</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>terbium oxide</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>terbium oxide</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>market for holmium oxide</t>
+        </is>
+      </c>
+      <c r="B114">
+        <v>0.020498544414098017</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>holmium oxide</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>holmium oxide</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>market for cobalt</t>
+        </is>
+      </c>
+      <c r="B115">
+        <v>0.023157894736842106</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>cobalt</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>cobalt</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>market for boric oxide</t>
+        </is>
+      </c>
+      <c r="B116">
+        <v>0.030505526072350162</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>boric oxide</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>boric oxide</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>market for aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="B117">
+        <v>0.002105263157894737</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>market for quicklime, milled, loose</t>
+        </is>
+      </c>
+      <c r="B118">
+        <v>0.0029456769825156734</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>quicklime, milled, loose</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>quicklime, milled, loose</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>market for steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="B119">
+        <v>0.6821052631578948</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>market for copper, cathode</t>
+        </is>
+      </c>
+      <c r="B120">
+        <v>0.002105263157894737</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B121">
+        <v>15</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>market for hazardous waste, for incineration</t>
+        </is>
+      </c>
+      <c r="B122">
+        <v>-0.05263157894736836</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>permanent magnet, measured A1 grade, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B127">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>permanent magnet, measured A1 grade, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Jones etal2025 DOI10.1021/jacs.5c04150 SI TableS2, samplesB3 andA1; Hsieh etal2026 DOI10.1007/s11367-026-02610-7 SI TableS11 PMSM bulk components.</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>APPROVED TRACTION MAGNET GRADE REFERENCES, issue36, 2026-10-18. Jones etal2025 DOI10.1021/jacs.5c04150 SI TableS2, samplesB3 andA1; Hsieh etal2026 DOI10.1007/s11367-026-02610-7 SI TableS11 PMSM bulk components. Select one measured B3 magnet as engineering composition reference, NOT fleet average from two rotors. B3 masspercent:Nd21.9,Pr7.4,Tb0.5,Ho1.7,Co2.2,B0.9,Al0.2,Ca0.2,Fe64.8,Cu0.2 (sum100);Dy not detected, not proof absolutezero. Separate A1 sensitivity:Nd26.6,Tb0.6,Dy0.5,Ho2.2,Co2.4,B0.9,Al0.2,Ca0.1,Ti0.2,Fe66.2,Cu0.2;roundedsource99.9 normalized by99.9. Grade choice has substantialNd/Pr/Dy/Tb/Ho/Co sensitivity; unknown fleet penetration,gradeevolution and coercivity requirements remain gaps. Purchase individual oxide suppliers at stoichiometric containedmetal equivalents Nd2O3,Pr6O11,Tb4O7,Ho2O3,Dy2O3,Coasmetal,othermetals explicitly; B usesboricoxide/Causesquicklime/TiusesTiO2 as supply proxies. Oxide-to-metal reduction/reagents,oxygen/byproduct fate,boron/calciumretention and magnet coating are unresolved manufacturing gaps, not a closed full metallurgical process. Assume95percent magnet-material retention, matching5percentfinishedoffcut treatmentproxy, no recyclingcredit; yield sensitivity85-100percent and15kWh/kgmagnetprocess sensitivity5-30. Wholeoxide feed mass can exceed finishedmagnet mass due to oxygen:do not normalize elementalshares by gross feed mass. New roadmotor uses public PMSM non-magnet proportions20.3kgelectricalsteel,4.8Cu,14.6Al,3.9balance allocatedordinary steel as explicit shaft/bearingproxy. Missing source3.9kg componentbreakdown is not a measured steelrecipe. Keep existing0.03735849kgfinishedmagnet/kgmotor and all vehicle motor masses rather than resize magnetdemand to1.3/44.9kg/kg from a differentmotor. Distribute remainingmass across public non-magnet proportions; electricalsteelexisting3.2percentSi reference. Genericmetalworking+1kWh/kgassembly,100percentmotorassemblyretention. Existing motorsteel/Algrades remainproxies; efficiency/torque/voltage not revalidated. Dedicated name outside genericEVmetaloverlay deliberately fixes this source design over time; avoids aluminum overlay doublecount and Nd-onlyoverwrite. No unsupported future gradelearning; future static-vs-learning comparison remains required. Rewire direct car/truck/bus roadmotor inputs and explicit roadperMJ copies; inductionrail/tram unchanged. Existing sourcevehicle life andMJallocation retained. Native backgroundmotor and genericmagnet supplies remain unchanged for other consumers. Individualoxideproviders keep REidentities visible to containedmetal accounting; no primary/secondary claim.</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>permanent magnet, measured A1 grade, engineering reference</t>
+        </is>
+      </c>
+      <c r="B134">
+        <v>1</v>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>permanent magnet, measured A1 grade, engineering reference</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>permanent magnet, measured A1 grade, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>market for neodymium oxide</t>
+        </is>
+      </c>
+      <c r="B135">
+        <v>0.32625920134412806</v>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>neodymium oxide</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>neodymium oxide</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>market for terbium oxide</t>
+        </is>
+      </c>
+      <c r="B136">
+        <v>0.007421035816807132</v>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>terbium oxide</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>terbium oxide</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>market for dysprosium oxide</t>
+        </is>
+      </c>
+      <c r="B137">
+        <v>0.006034402844119443</v>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>dysprosium oxide</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>dysprosium oxide</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>market for holmium oxide</t>
+        </is>
+      </c>
+      <c r="B138">
+        <v>0.026501027038265044</v>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>holmium oxide</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>holmium oxide</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>market for cobalt</t>
+        </is>
+      </c>
+      <c r="B139">
+        <v>0.025237919974762078</v>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>cobalt</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>cobalt</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>market for boric oxide</t>
+        </is>
+      </c>
+      <c r="B140">
+        <v>0.03047505102132883</v>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>boric oxide</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>boric oxide</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>market for aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="B141">
+        <v>0.00210315999789684</v>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>market for quicklime, milled, loose</t>
+        </is>
+      </c>
+      <c r="B142">
+        <v>0.001471367124133703</v>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>quicklime, milled, loose</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>quicklime, milled, loose</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>market for titanium dioxide</t>
+        </is>
+      </c>
+      <c r="B143">
+        <v>0.0035090745865007443</v>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>titanium dioxide</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>titanium dioxide</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>market for steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="B144">
+        <v>0.696145959303854</v>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>market for copper, cathode</t>
+        </is>
+      </c>
+      <c r="B145">
+        <v>0.00210315999789684</v>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B146">
+        <v>15</v>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>market for hazardous waste, for incineration</t>
+        </is>
+      </c>
+      <c r="B147">
+        <v>-0.05263157894736836</v>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>traction powertrain, permanent-magnet motor engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B152">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>traction powertrain, permanent-magnet motor engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Jones etal2025 DOI10.1021/jacs.5c04150 SI TableS2, samplesB3 andA1; Hsieh etal2026 DOI10.1007/s11367-026-02610-7 SI TableS11 PMSM bulk components.</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>APPROVED TRACTION MAGNET GRADE REFERENCES, issue36, 2026-10-18. Jones etal2025 DOI10.1021/jacs.5c04150 SI TableS2, samplesB3 andA1; Hsieh etal2026 DOI10.1007/s11367-026-02610-7 SI TableS11 PMSM bulk components. Select one measured B3 magnet as engineering composition reference, NOT fleet average from two rotors. B3 masspercent:Nd21.9,Pr7.4,Tb0.5,Ho1.7,Co2.2,B0.9,Al0.2,Ca0.2,Fe64.8,Cu0.2 (sum100);Dy not detected, not proof absolutezero. Separate A1 sensitivity:Nd26.6,Tb0.6,Dy0.5,Ho2.2,Co2.4,B0.9,Al0.2,Ca0.1,Ti0.2,Fe66.2,Cu0.2;roundedsource99.9 normalized by99.9. Grade choice has substantialNd/Pr/Dy/Tb/Ho/Co sensitivity; unknown fleet penetration,gradeevolution and coercivity requirements remain gaps. Purchase individual oxide suppliers at stoichiometric containedmetal equivalents Nd2O3,Pr6O11,Tb4O7,Ho2O3,Dy2O3,Coasmetal,othermetals explicitly; B usesboricoxide/Causesquicklime/TiusesTiO2 as supply proxies. Oxide-to-metal reduction/reagents,oxygen/byproduct fate,boron/calciumretention and magnet coating are unresolved manufacturing gaps, not a closed full metallurgical process. Assume95percent magnet-material retention, matching5percentfinishedoffcut treatmentproxy, no recyclingcredit; yield sensitivity85-100percent and15kWh/kgmagnetprocess sensitivity5-30. Wholeoxide feed mass can exceed finishedmagnet mass due to oxygen:do not normalize elementalshares by gross feed mass. New roadmotor uses public PMSM non-magnet proportions20.3kgelectricalsteel,4.8Cu,14.6Al,3.9balance allocatedordinary steel as explicit shaft/bearingproxy. Missing source3.9kg componentbreakdown is not a measured steelrecipe. Keep existing0.03735849kgfinishedmagnet/kgmotor and all vehicle motor masses rather than resize magnetdemand to1.3/44.9kg/kg from a differentmotor. Distribute remainingmass across public non-magnet proportions; electricalsteelexisting3.2percentSi reference. Genericmetalworking+1kWh/kgassembly,100percentmotorassemblyretention. Existing motorsteel/Algrades remainproxies; efficiency/torque/voltage not revalidated. Dedicated name outside genericEVmetaloverlay deliberately fixes this source design over time; avoids aluminum overlay doublecount and Nd-onlyoverwrite. No unsupported future gradelearning; future static-vs-learning comparison remains required. Rewire direct car/truck/bus roadmotor inputs and explicit roadperMJ copies; inductionrail/tram unchanged. Existing sourcevehicle life andMJallocation retained. Native backgroundmotor and genericmagnet supplies remain unchanged for other consumers. Individualoxideproviders keep REidentities visible to containedmetal accounting; no primary/secondary claim.</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>traction powertrain, permanent-magnet motor engineering reference</t>
+        </is>
+      </c>
+      <c r="B159">
+        <v>1</v>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>traction powertrain, permanent-magnet motor engineering reference</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>traction powertrain, permanent-magnet motor engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>permanent magnet, measured B3 grade, engineering reference</t>
+        </is>
+      </c>
+      <c r="B160">
+        <v>0.03735849</v>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>permanent magnet, measured B3 grade, engineering reference</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>permanent magnet, measured B3 grade, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>non-oriented electrical steel, engineering alloy reference</t>
+        </is>
+      </c>
+      <c r="B161">
+        <v>0.4482023544266055</v>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>non-oriented electrical steel, engineering alloy reference</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>non-oriented electrical steel, engineering alloy reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>market for copper, cathode</t>
+        </is>
+      </c>
+      <c r="B162">
+        <v>0.10597888183486238</v>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>market for aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="B163">
+        <v>0.3223524322477064</v>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>market for steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="B164">
+        <v>0.08610784149082568</v>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B165">
+        <v>1</v>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+      <c r="B166">
+        <v>0.5343101959174312</v>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>metal working, average for copper product manufacturing</t>
+        </is>
+      </c>
+      <c r="B167">
+        <v>0.10597888183486238</v>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>metal working, average for copper product manufacturing</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>metal working, average for copper product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>metal working, average for aluminium product manufacturing</t>
+        </is>
+      </c>
+      <c r="B168">
+        <v>0.3223524322477064</v>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>metal working, average for aluminium product manufacturing</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>metal working, average for aluminium product manufacturing</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/premise/data/additional_inventories/lci-electric-car-mechanical-powertrain.xlsx
+++ b/premise/data/additional_inventories/lci-electric-car-mechanical-powertrain.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H168"/>
+  <dimension ref="A1:H298"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4128,6 +4128,3809 @@
         </is>
       </c>
     </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>bare printed circuit board, power electronics engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B173">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>bare printed circuit board, power electronics engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>square meter</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>NewRide2013 public appendix p66 https://www.newride.ch/documents/Forschungsprojekt_E-Scooters_2013/Anhang_zu_Schlussbericht_E-Scooter_2013.pdf; BRUSA NLG513 Jan2013 datasheet6.2kgwatercooled/3.3kWDC(3.68kWAC); BRUSA2023 BSC624 https://www.brusahypower.com/wp-content/uploads/2023/08/Datasheet_BSC6xx_20230704_Rev.-2.pdf pp2-3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>APPROVED ROAD CHARGER/CONVERTER REFERENCE MASS ACCOUNTING, issue37, 2026-10-18. NewRide2013 public appendix p66 https://www.newride.ch/documents/Forschungsprojekt_E-Scooters_2013/Anhang_zu_Schlussbericht_E-Scooter_2013.pdf; BRUSA NLG513 Jan2013 datasheet6.2kgwatercooled/3.3kWDC(3.68kWAC); BRUSA2023 BSC624 https://www.brusahypower.com/wp-content/uploads/2023/08/Datasheet_BSC6xx_20230704_Rev.-2.pdf pp2-3. Historical partial9.43145percent/4.4542percent positive residuals are NOT proven overcounts. New explicit6.2kgwatercooled NLG513-class charger:public gross material purchases from p66, engineering95percentretention for nonmetalcomponent purchases,80percentCu/steel/brass retention; retain source grossAl3.812kg and calibrate only its finishedhousing mass as6.2kg minus separately declared retainedcomponents. This is a mass-budget housing ENGINEERING ASSUMPTION, not recovery of measured gross-to-net yields or uniform source normalization; housing thickness,fins and wastefactor need directteardown confirmation. Include source separate.164kgmountedboardproxy plus.263m2barethroughholeboard; their assumed distinct roles may be wrong and are a board-boundary sensitivity, not merged as duplicate without evidence. Bareboardreference1.6mm1850kg/m3FR4,4x35umCu,50percentCuarea;retained3.5872kg/m2. Manufacture95percentCu/FR4retention with matching scrap,10kWh/m2; chemicaletch/drilling/plating/finish gaps remain. Nonmetal/componentprocessloss uses hazardous-waste-incineration as an explicit unvalidated mixedcomponent fateproxy. Other filmcapacitors,ferrite,resin,stainless,Cu,brass,Al2O3,silicone,HIPS retained explicitly; processservices are not counted asproductmass. Source unsupported area-only ceramicresistorprocessing is not a retainedmaterial input;source.006kgresistors modeled by real surface-resistormanufacturingproxy. Source0.0269kWh+72.7MJheat retained as assemblyreference; no new measuredfactoryclaim. New auxiliary DC/DC reference4.8kgBSC624,220-450VHV,14V200Acontinuous =&gt;2.8kW,250Apeak=&gt;3.5kW. PDF continuous/maxpower rows conflict with these currentratings; adopt conservative current-derived2.8kWcontinuous. PUBLIC COMPONENT RECIPE NOT AVAILABLE:transfer corrected charger retained material proportions perkg as explicit DC/DC ANALOGUE,not manufacturer BSC624BOM. Sensitivityboardarea0.5-2x,componentfractions andhousingresidual; increasing a component reduceshousing withinfixedmass, not normalizeallinputs. This leaves topology-specificmagnetics/semiconductor/capacitor uncertainty, so convertermetalcoefficients are not certified. Keep existingvehiclekg/duty/replacementbudgets:chargernameplateequivalent=qkg/6.2*3.3kW;converter=qkg/4.8*2.8kW. Fractionaldeviceequivalence, thermaladequacy and voltageadaptation forbus/truck remain explicit gaps; no new inferredintegerunits or fastchargerpower.400/800Vbuscompatibility is not established by this450Vdevice reference. Separate offboard fastchargers and roadinverters unchanged; railconverters unchanged. ExistingperMJadapter retains renamedcharger/converterhardware. No chassis/road added, no sourceenergydemand or primary/secondary changes; EOL remains existingvehicle treatment boundary and dedicatedcomponentEOLgap.</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>bare printed circuit board, power electronics engineering reference</t>
+        </is>
+      </c>
+      <c r="B180">
+        <v>1</v>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>square meter</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>bare printed circuit board, power electronics engineering reference</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>bare printed circuit board, power electronics engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>market for glass fibre</t>
+        </is>
+      </c>
+      <c r="B181">
+        <v>1.8694736842105264</v>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>glass fibre</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>glass fibre</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>market for epoxy resin, liquid</t>
+        </is>
+      </c>
+      <c r="B182">
+        <v>1.2463157894736843</v>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>epoxy resin, liquid</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>epoxy resin, liquid</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>market for copper, cathode</t>
+        </is>
+      </c>
+      <c r="B183">
+        <v>0.6602105263157895</v>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>market for waste plastic, mixture</t>
+        </is>
+      </c>
+      <c r="B184">
+        <v>-0.15578947368421034</v>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>waste plastic, mixture</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>waste plastic, mixture</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>copper scrap, sorted, pressed, Recycled Content cut-off</t>
+        </is>
+      </c>
+      <c r="B185">
+        <v>-0.033010526315789435</v>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>copper scrap, sorted, pressed</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>copper scrap, sorted, pressed</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B186">
+        <v>10</v>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>charger, road onboard engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B191">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>charger, road onboard engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>NewRide2013 public appendix p66 https://www.newride.ch/documents/Forschungsprojekt_E-Scooters_2013/Anhang_zu_Schlussbericht_E-Scooter_2013.pdf; BRUSA NLG513 Jan2013 datasheet6.2kgwatercooled/3.3kWDC(3.68kWAC); BRUSA2023 BSC624 https://www.brusahypower.com/wp-content/uploads/2023/08/Datasheet_BSC6xx_20230704_Rev.-2.pdf pp2-3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>APPROVED ROAD CHARGER/CONVERTER REFERENCE MASS ACCOUNTING, issue37, 2026-10-18. NewRide2013 public appendix p66 https://www.newride.ch/documents/Forschungsprojekt_E-Scooters_2013/Anhang_zu_Schlussbericht_E-Scooter_2013.pdf; BRUSA NLG513 Jan2013 datasheet6.2kgwatercooled/3.3kWDC(3.68kWAC); BRUSA2023 BSC624 https://www.brusahypower.com/wp-content/uploads/2023/08/Datasheet_BSC6xx_20230704_Rev.-2.pdf pp2-3. Historical partial9.43145percent/4.4542percent positive residuals are NOT proven overcounts. New explicit6.2kgwatercooled NLG513-class charger:public gross material purchases from p66, engineering95percentretention for nonmetalcomponent purchases,80percentCu/steel/brass retention; retain source grossAl3.812kg and calibrate only its finishedhousing mass as6.2kg minus separately declared retainedcomponents. This is a mass-budget housing ENGINEERING ASSUMPTION, not recovery of measured gross-to-net yields or uniform source normalization; housing thickness,fins and wastefactor need directteardown confirmation. Include source separate.164kgmountedboardproxy plus.263m2barethroughholeboard; their assumed distinct roles may be wrong and are a board-boundary sensitivity, not merged as duplicate without evidence. Bareboardreference1.6mm1850kg/m3FR4,4x35umCu,50percentCuarea;retained3.5872kg/m2. Manufacture95percentCu/FR4retention with matching scrap,10kWh/m2; chemicaletch/drilling/plating/finish gaps remain. Nonmetal/componentprocessloss uses hazardous-waste-incineration as an explicit unvalidated mixedcomponent fateproxy. Other filmcapacitors,ferrite,resin,stainless,Cu,brass,Al2O3,silicone,HIPS retained explicitly; processservices are not counted asproductmass. Source unsupported area-only ceramicresistorprocessing is not a retainedmaterial input;source.006kgresistors modeled by real surface-resistormanufacturingproxy. Source0.0269kWh+72.7MJheat retained as assemblyreference; no new measuredfactoryclaim. New auxiliary DC/DC reference4.8kgBSC624,220-450VHV,14V200Acontinuous =&gt;2.8kW,250Apeak=&gt;3.5kW. PDF continuous/maxpower rows conflict with these currentratings; adopt conservative current-derived2.8kWcontinuous. PUBLIC COMPONENT RECIPE NOT AVAILABLE:transfer corrected charger retained material proportions perkg as explicit DC/DC ANALOGUE,not manufacturer BSC624BOM. Sensitivityboardarea0.5-2x,componentfractions andhousingresidual; increasing a component reduceshousing withinfixedmass, not normalizeallinputs. This leaves topology-specificmagnetics/semiconductor/capacitor uncertainty, so convertermetalcoefficients are not certified. Keep existingvehiclekg/duty/replacementbudgets:chargernameplateequivalent=qkg/6.2*3.3kW;converter=qkg/4.8*2.8kW. Fractionaldeviceequivalence, thermaladequacy and voltageadaptation forbus/truck remain explicit gaps; no new inferredintegerunits or fastchargerpower.400/800Vbuscompatibility is not established by this450Vdevice reference. Separate offboard fastchargers and roadinverters unchanged; railconverters unchanged. ExistingperMJadapter retains renamedcharger/converterhardware. No chassis/road added, no sourceenergydemand or primary/secondary changes; EOL remains existingvehicle treatment boundary and dedicatedcomponentEOLgap.</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>charger, road onboard engineering reference</t>
+        </is>
+      </c>
+      <c r="B198">
+        <v>1</v>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>charger, road onboard engineering reference</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>charger, road onboard engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>market for brass</t>
+        </is>
+      </c>
+      <c r="B199">
+        <v>0.012877419354838708</v>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>brass</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>brass</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>market for capacitor, film type, for through-hole mounting</t>
+        </is>
+      </c>
+      <c r="B200">
+        <v>0.052862903225806446</v>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>capacitor, film type, for through-hole mounting</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>capacitor, film type, for through-hole mounting</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>market for steel, chromium steel 18/8</t>
+        </is>
+      </c>
+      <c r="B201">
+        <v>0.030709677419354837</v>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>steel, chromium steel 18/8</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>steel, chromium steel 18/8</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>market for copper, cathode</t>
+        </is>
+      </c>
+      <c r="B202">
+        <v>0.09380645161290323</v>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>market for ferrite</t>
+        </is>
+      </c>
+      <c r="B203">
+        <v>0.11691129032258064</v>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>ferrite</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>ferrite</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>market for polyester resin, unsaturated</t>
+        </is>
+      </c>
+      <c r="B204">
+        <v>0.025741935483870965</v>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>polyester resin, unsaturated</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>polyester resin, unsaturated</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>market for polystyrene, high impact</t>
+        </is>
+      </c>
+      <c r="B205">
+        <v>0.01368306451612903</v>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>polystyrene, high impact</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>polystyrene, high impact</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>market for printed wiring board, surface mounted, unspecified, Pb free</t>
+        </is>
+      </c>
+      <c r="B206">
+        <v>0.025129032258064513</v>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>printed wiring board, surface mounted, unspecified, Pb free</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>printed wiring board, surface mounted, unspecified, Pb free</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>market for silicone product</t>
+        </is>
+      </c>
+      <c r="B207">
+        <v>0.0006190322580645161</v>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>silicone product</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>silicone product</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>market for steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="B208">
+        <v>0.05341935483870967</v>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>market for aluminium oxide, non-metallurgical</t>
+        </is>
+      </c>
+      <c r="B209">
+        <v>0.0009285483870967742</v>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>aluminium oxide, non-metallurgical</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>aluminium oxide, non-metallurgical</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>market for resistor, surface-mounted</t>
+        </is>
+      </c>
+      <c r="B210">
+        <v>0.0009193548387096774</v>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>resistor, surface-mounted</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>resistor, surface-mounted</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>bare printed circuit board, power electronics engineering reference</t>
+        </is>
+      </c>
+      <c r="B211">
+        <v>0.04241935483870968</v>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>square meter</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>bare printed circuit board, power electronics engineering reference</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>bare printed circuit board, power electronics engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>market for aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="B212">
+        <v>0.6148387096774193</v>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>aluminium scrap, new, Recycled Content cut-off</t>
+        </is>
+      </c>
+      <c r="B213">
+        <v>-0.19461348387096777</v>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>aluminium scrap, new</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>aluminium scrap, new</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B214">
+        <v>0.004338709677419355</v>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>market for heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+      <c r="B215">
+        <v>11.725806451612904</v>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>megajoule</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>market for brass</t>
+        </is>
+      </c>
+      <c r="B216">
+        <v>0.003219354838709677</v>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>brass</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>brass</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>copper scrap, sorted, pressed, Recycled Content cut-off</t>
+        </is>
+      </c>
+      <c r="B217">
+        <v>-0.003219354838709677</v>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>copper scrap, sorted, pressed</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>copper scrap, sorted, pressed</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>market for capacitor, film type, for through-hole mounting</t>
+        </is>
+      </c>
+      <c r="B218">
+        <v>0.0027822580645161256</v>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>capacitor, film type, for through-hole mounting</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>capacitor, film type, for through-hole mounting</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>market for hazardous waste, for incineration</t>
+        </is>
+      </c>
+      <c r="B219">
+        <v>-0.0027822580645161256</v>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>market for steel, chromium steel 18/8</t>
+        </is>
+      </c>
+      <c r="B220">
+        <v>0.007677419354838709</v>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>steel, chromium steel 18/8</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>steel, chromium steel 18/8</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>iron scrap, unsorted, Recycled Content cut-off</t>
+        </is>
+      </c>
+      <c r="B221">
+        <v>-0.007677419354838709</v>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>iron scrap, unsorted</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>iron scrap, unsorted</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>market for copper, cathode</t>
+        </is>
+      </c>
+      <c r="B222">
+        <v>0.023451612903225807</v>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>copper scrap, sorted, pressed, Recycled Content cut-off</t>
+        </is>
+      </c>
+      <c r="B223">
+        <v>-0.023451612903225807</v>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>copper scrap, sorted, pressed</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>copper scrap, sorted, pressed</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>market for ferrite</t>
+        </is>
+      </c>
+      <c r="B224">
+        <v>0.006153225806451605</v>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>ferrite</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>ferrite</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>market for hazardous waste, for incineration</t>
+        </is>
+      </c>
+      <c r="B225">
+        <v>-0.006153225806451605</v>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>market for polyester resin, unsaturated</t>
+        </is>
+      </c>
+      <c r="B226">
+        <v>0.0013548387096774179</v>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>polyester resin, unsaturated</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>polyester resin, unsaturated</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>market for hazardous waste, for incineration</t>
+        </is>
+      </c>
+      <c r="B227">
+        <v>-0.0013548387096774179</v>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>market for polystyrene, high impact</t>
+        </is>
+      </c>
+      <c r="B228">
+        <v>0.0007201612903225799</v>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>polystyrene, high impact</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>polystyrene, high impact</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>market for hazardous waste, for incineration</t>
+        </is>
+      </c>
+      <c r="B229">
+        <v>-0.0007201612903225799</v>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>market for printed wiring board, surface mounted, unspecified, Pb free</t>
+        </is>
+      </c>
+      <c r="B230">
+        <v>0.0013225806451612888</v>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>printed wiring board, surface mounted, unspecified, Pb free</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>printed wiring board, surface mounted, unspecified, Pb free</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>market for hazardous waste, for incineration</t>
+        </is>
+      </c>
+      <c r="B231">
+        <v>-0.0013225806451612888</v>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>market for silicone product</t>
+        </is>
+      </c>
+      <c r="B232">
+        <v>3.258064516129028e-05</v>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>silicone product</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>silicone product</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>market for hazardous waste, for incineration</t>
+        </is>
+      </c>
+      <c r="B233">
+        <v>-3.258064516129028e-05</v>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>market for steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="B234">
+        <v>0.013354838709677418</v>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>iron scrap, unsorted, Recycled Content cut-off</t>
+        </is>
+      </c>
+      <c r="B235">
+        <v>-0.013354838709677418</v>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>iron scrap, unsorted</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>iron scrap, unsorted</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>market for aluminium oxide, non-metallurgical</t>
+        </is>
+      </c>
+      <c r="B236">
+        <v>4.887096774193543e-05</v>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>aluminium oxide, non-metallurgical</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>aluminium oxide, non-metallurgical</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>market for hazardous waste, for incineration</t>
+        </is>
+      </c>
+      <c r="B237">
+        <v>-4.887096774193543e-05</v>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>market for resistor, surface-mounted</t>
+        </is>
+      </c>
+      <c r="B238">
+        <v>4.83870967741935e-05</v>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>resistor, surface-mounted</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>resistor, surface-mounted</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>market for hazardous waste, for incineration</t>
+        </is>
+      </c>
+      <c r="B239">
+        <v>-4.83870967741935e-05</v>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>metal working, average for aluminium product manufacturing</t>
+        </is>
+      </c>
+      <c r="B240">
+        <v>0.6148387096774193</v>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>metal working, average for aluminium product manufacturing</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>metal working, average for aluminium product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>metal working, average for copper product manufacturing</t>
+        </is>
+      </c>
+      <c r="B241">
+        <v>0.11725806451612902</v>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>metal working, average for copper product manufacturing</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>metal working, average for copper product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+      <c r="B242">
+        <v>0.10516129032258065</v>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>converter, road auxiliary DC engineering analogue</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B247">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>converter, road auxiliary DC engineering analogue</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>NewRide2013 public appendix p66 https://www.newride.ch/documents/Forschungsprojekt_E-Scooters_2013/Anhang_zu_Schlussbericht_E-Scooter_2013.pdf; BRUSA NLG513 Jan2013 datasheet6.2kgwatercooled/3.3kWDC(3.68kWAC); BRUSA2023 BSC624 https://www.brusahypower.com/wp-content/uploads/2023/08/Datasheet_BSC6xx_20230704_Rev.-2.pdf pp2-3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>APPROVED ROAD CHARGER/CONVERTER REFERENCE MASS ACCOUNTING, issue37, 2026-10-18. NewRide2013 public appendix p66 https://www.newride.ch/documents/Forschungsprojekt_E-Scooters_2013/Anhang_zu_Schlussbericht_E-Scooter_2013.pdf; BRUSA NLG513 Jan2013 datasheet6.2kgwatercooled/3.3kWDC(3.68kWAC); BRUSA2023 BSC624 https://www.brusahypower.com/wp-content/uploads/2023/08/Datasheet_BSC6xx_20230704_Rev.-2.pdf pp2-3. Historical partial9.43145percent/4.4542percent positive residuals are NOT proven overcounts. New explicit6.2kgwatercooled NLG513-class charger:public gross material purchases from p66, engineering95percentretention for nonmetalcomponent purchases,80percentCu/steel/brass retention; retain source grossAl3.812kg and calibrate only its finishedhousing mass as6.2kg minus separately declared retainedcomponents. This is a mass-budget housing ENGINEERING ASSUMPTION, not recovery of measured gross-to-net yields or uniform source normalization; housing thickness,fins and wastefactor need directteardown confirmation. Include source separate.164kgmountedboardproxy plus.263m2barethroughholeboard; their assumed distinct roles may be wrong and are a board-boundary sensitivity, not merged as duplicate without evidence. Bareboardreference1.6mm1850kg/m3FR4,4x35umCu,50percentCuarea;retained3.5872kg/m2. Manufacture95percentCu/FR4retention with matching scrap,10kWh/m2; chemicaletch/drilling/plating/finish gaps remain. Nonmetal/componentprocessloss uses hazardous-waste-incineration as an explicit unvalidated mixedcomponent fateproxy. Other filmcapacitors,ferrite,resin,stainless,Cu,brass,Al2O3,silicone,HIPS retained explicitly; processservices are not counted asproductmass. Source unsupported area-only ceramicresistorprocessing is not a retainedmaterial input;source.006kgresistors modeled by real surface-resistormanufacturingproxy. Source0.0269kWh+72.7MJheat retained as assemblyreference; no new measuredfactoryclaim. New auxiliary DC/DC reference4.8kgBSC624,220-450VHV,14V200Acontinuous =&gt;2.8kW,250Apeak=&gt;3.5kW. PDF continuous/maxpower rows conflict with these currentratings; adopt conservative current-derived2.8kWcontinuous. PUBLIC COMPONENT RECIPE NOT AVAILABLE:transfer corrected charger retained material proportions perkg as explicit DC/DC ANALOGUE,not manufacturer BSC624BOM. Sensitivityboardarea0.5-2x,componentfractions andhousingresidual; increasing a component reduceshousing withinfixedmass, not normalizeallinputs. This leaves topology-specificmagnetics/semiconductor/capacitor uncertainty, so convertermetalcoefficients are not certified. Keep existingvehiclekg/duty/replacementbudgets:chargernameplateequivalent=qkg/6.2*3.3kW;converter=qkg/4.8*2.8kW. Fractionaldeviceequivalence, thermaladequacy and voltageadaptation forbus/truck remain explicit gaps; no new inferredintegerunits or fastchargerpower.400/800Vbuscompatibility is not established by this450Vdevice reference. Separate offboard fastchargers and roadinverters unchanged; railconverters unchanged. ExistingperMJadapter retains renamedcharger/converterhardware. No chassis/road added, no sourceenergydemand or primary/secondary changes; EOL remains existingvehicle treatment boundary and dedicatedcomponentEOLgap.</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>converter, road auxiliary DC engineering analogue</t>
+        </is>
+      </c>
+      <c r="B254">
+        <v>1</v>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>converter, road auxiliary DC engineering analogue</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>converter, road auxiliary DC engineering analogue</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>market for brass</t>
+        </is>
+      </c>
+      <c r="B255">
+        <v>0.012877419354838708</v>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>brass</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>brass</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>market for capacitor, film type, for through-hole mounting</t>
+        </is>
+      </c>
+      <c r="B256">
+        <v>0.052862903225806446</v>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>capacitor, film type, for through-hole mounting</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>capacitor, film type, for through-hole mounting</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>market for steel, chromium steel 18/8</t>
+        </is>
+      </c>
+      <c r="B257">
+        <v>0.030709677419354837</v>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>steel, chromium steel 18/8</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>steel, chromium steel 18/8</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>market for copper, cathode</t>
+        </is>
+      </c>
+      <c r="B258">
+        <v>0.09380645161290323</v>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>market for ferrite</t>
+        </is>
+      </c>
+      <c r="B259">
+        <v>0.11691129032258064</v>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>ferrite</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>ferrite</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>market for polyester resin, unsaturated</t>
+        </is>
+      </c>
+      <c r="B260">
+        <v>0.025741935483870965</v>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>polyester resin, unsaturated</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>polyester resin, unsaturated</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>market for polystyrene, high impact</t>
+        </is>
+      </c>
+      <c r="B261">
+        <v>0.01368306451612903</v>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>polystyrene, high impact</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>polystyrene, high impact</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>market for printed wiring board, surface mounted, unspecified, Pb free</t>
+        </is>
+      </c>
+      <c r="B262">
+        <v>0.025129032258064513</v>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>printed wiring board, surface mounted, unspecified, Pb free</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>printed wiring board, surface mounted, unspecified, Pb free</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>market for silicone product</t>
+        </is>
+      </c>
+      <c r="B263">
+        <v>0.0006190322580645161</v>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>silicone product</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>silicone product</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>market for steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="B264">
+        <v>0.05341935483870967</v>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>market for aluminium oxide, non-metallurgical</t>
+        </is>
+      </c>
+      <c r="B265">
+        <v>0.0009285483870967742</v>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>aluminium oxide, non-metallurgical</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>aluminium oxide, non-metallurgical</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>market for resistor, surface-mounted</t>
+        </is>
+      </c>
+      <c r="B266">
+        <v>0.0009193548387096774</v>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>resistor, surface-mounted</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>resistor, surface-mounted</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>bare printed circuit board, power electronics engineering reference</t>
+        </is>
+      </c>
+      <c r="B267">
+        <v>0.04241935483870968</v>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>square meter</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>bare printed circuit board, power electronics engineering reference</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>bare printed circuit board, power electronics engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>market for aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="B268">
+        <v>0.6148387096774193</v>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>aluminium scrap, new, Recycled Content cut-off</t>
+        </is>
+      </c>
+      <c r="B269">
+        <v>-0.19461348387096777</v>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>aluminium scrap, new</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>aluminium scrap, new</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B270">
+        <v>0.004338709677419355</v>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>market for heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+      <c r="B271">
+        <v>11.725806451612904</v>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>megajoule</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>market for brass</t>
+        </is>
+      </c>
+      <c r="B272">
+        <v>0.003219354838709677</v>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>brass</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>brass</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>copper scrap, sorted, pressed, Recycled Content cut-off</t>
+        </is>
+      </c>
+      <c r="B273">
+        <v>-0.003219354838709677</v>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>copper scrap, sorted, pressed</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>copper scrap, sorted, pressed</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>market for capacitor, film type, for through-hole mounting</t>
+        </is>
+      </c>
+      <c r="B274">
+        <v>0.0027822580645161256</v>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>capacitor, film type, for through-hole mounting</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>capacitor, film type, for through-hole mounting</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>market for hazardous waste, for incineration</t>
+        </is>
+      </c>
+      <c r="B275">
+        <v>-0.0027822580645161256</v>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>market for steel, chromium steel 18/8</t>
+        </is>
+      </c>
+      <c r="B276">
+        <v>0.007677419354838709</v>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>steel, chromium steel 18/8</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>steel, chromium steel 18/8</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>iron scrap, unsorted, Recycled Content cut-off</t>
+        </is>
+      </c>
+      <c r="B277">
+        <v>-0.007677419354838709</v>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>iron scrap, unsorted</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>iron scrap, unsorted</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>market for copper, cathode</t>
+        </is>
+      </c>
+      <c r="B278">
+        <v>0.023451612903225807</v>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>copper scrap, sorted, pressed, Recycled Content cut-off</t>
+        </is>
+      </c>
+      <c r="B279">
+        <v>-0.023451612903225807</v>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>copper scrap, sorted, pressed</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>copper scrap, sorted, pressed</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>market for ferrite</t>
+        </is>
+      </c>
+      <c r="B280">
+        <v>0.006153225806451605</v>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>ferrite</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>ferrite</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>market for hazardous waste, for incineration</t>
+        </is>
+      </c>
+      <c r="B281">
+        <v>-0.006153225806451605</v>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>market for polyester resin, unsaturated</t>
+        </is>
+      </c>
+      <c r="B282">
+        <v>0.0013548387096774179</v>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>polyester resin, unsaturated</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>polyester resin, unsaturated</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>market for hazardous waste, for incineration</t>
+        </is>
+      </c>
+      <c r="B283">
+        <v>-0.0013548387096774179</v>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>market for polystyrene, high impact</t>
+        </is>
+      </c>
+      <c r="B284">
+        <v>0.0007201612903225799</v>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>polystyrene, high impact</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>polystyrene, high impact</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>market for hazardous waste, for incineration</t>
+        </is>
+      </c>
+      <c r="B285">
+        <v>-0.0007201612903225799</v>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
+        </is>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>market for printed wiring board, surface mounted, unspecified, Pb free</t>
+        </is>
+      </c>
+      <c r="B286">
+        <v>0.0013225806451612888</v>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>printed wiring board, surface mounted, unspecified, Pb free</t>
+        </is>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>printed wiring board, surface mounted, unspecified, Pb free</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>market for hazardous waste, for incineration</t>
+        </is>
+      </c>
+      <c r="B287">
+        <v>-0.0013225806451612888</v>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
+        </is>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>market for silicone product</t>
+        </is>
+      </c>
+      <c r="B288">
+        <v>3.258064516129028e-05</v>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>silicone product</t>
+        </is>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>silicone product</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>market for hazardous waste, for incineration</t>
+        </is>
+      </c>
+      <c r="B289">
+        <v>-3.258064516129028e-05</v>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
+        </is>
+      </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>market for steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="B290">
+        <v>0.013354838709677418</v>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>iron scrap, unsorted, Recycled Content cut-off</t>
+        </is>
+      </c>
+      <c r="B291">
+        <v>-0.013354838709677418</v>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>iron scrap, unsorted</t>
+        </is>
+      </c>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>iron scrap, unsorted</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>market for aluminium oxide, non-metallurgical</t>
+        </is>
+      </c>
+      <c r="B292">
+        <v>4.887096774193543e-05</v>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>aluminium oxide, non-metallurgical</t>
+        </is>
+      </c>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>aluminium oxide, non-metallurgical</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>market for hazardous waste, for incineration</t>
+        </is>
+      </c>
+      <c r="B293">
+        <v>-4.887096774193543e-05</v>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
+        </is>
+      </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>market for resistor, surface-mounted</t>
+        </is>
+      </c>
+      <c r="B294">
+        <v>4.83870967741935e-05</v>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>resistor, surface-mounted</t>
+        </is>
+      </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>resistor, surface-mounted</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>market for hazardous waste, for incineration</t>
+        </is>
+      </c>
+      <c r="B295">
+        <v>-4.83870967741935e-05</v>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
+        </is>
+      </c>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>metal working, average for aluminium product manufacturing</t>
+        </is>
+      </c>
+      <c r="B296">
+        <v>0.6148387096774193</v>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>metal working, average for aluminium product manufacturing</t>
+        </is>
+      </c>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>metal working, average for aluminium product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>metal working, average for copper product manufacturing</t>
+        </is>
+      </c>
+      <c r="B297">
+        <v>0.11725806451612902</v>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>metal working, average for copper product manufacturing</t>
+        </is>
+      </c>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>metal working, average for copper product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+      <c r="B298">
+        <v>0.10516129032258065</v>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/premise/data/additional_inventories/lci-electric-car-mechanical-powertrain.xlsx
+++ b/premise/data/additional_inventories/lci-electric-car-mechanical-powertrain.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H298"/>
+  <dimension ref="A1:I298"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>APPROVED TRACTION MAGNET GRADE REFERENCES, issue36, 2026-10-18. Jones etal2025 DOI10.1021/jacs.5c04150 SI TableS2, samplesB3 andA1; Hsieh etal2026 DOI10.1007/s11367-026-02610-7 SI TableS11 PMSM bulk components. Select one measured B3 magnet as engineering composition reference, NOT fleet average from two rotors. B3 masspercent:Nd21.9,Pr7.4,Tb0.5,Ho1.7,Co2.2,B0.9,Al0.2,Ca0.2,Fe64.8,Cu0.2 (sum100);Dy not detected, not proof absolutezero. Separate A1 sensitivity:Nd26.6,Tb0.6,Dy0.5,Ho2.2,Co2.4,B0.9,Al0.2,Ca0.1,Ti0.2,Fe66.2,Cu0.2;roundedsource99.9 normalized by99.9. Grade choice has substantialNd/Pr/Dy/Tb/Ho/Co sensitivity; unknown fleet penetration,gradeevolution and coercivity requirements remain gaps. Purchase individual oxide suppliers at stoichiometric containedmetal equivalents Nd2O3,Pr6O11,Tb4O7,Ho2O3,Dy2O3,Coasmetal,othermetals explicitly; B usesboricoxide/Causesquicklime/TiusesTiO2 as supply proxies. Oxide-to-metal reduction/reagents,oxygen/byproduct fate,boron/calciumretention and magnet coating are unresolved manufacturing gaps, not a closed full metallurgical process. Assume95percent magnet-material retention, matching5percentfinishedoffcut treatmentproxy, no recyclingcredit; yield sensitivity85-100percent and15kWh/kgmagnetprocess sensitivity5-30. Wholeoxide feed mass can exceed finishedmagnet mass due to oxygen:do not normalize elementalshares by gross feed mass. New roadmotor uses public PMSM non-magnet proportions20.3kgelectricalsteel,4.8Cu,14.6Al,3.9balance allocatedordinary steel as explicit shaft/bearingproxy. Missing source3.9kg componentbreakdown is not a measured steelrecipe. Keep existing0.03735849kgfinishedmagnet/kgmotor and all vehicle motor masses rather than resize magnetdemand to1.3/44.9kg/kg from a differentmotor. Distribute remainingmass across public non-magnet proportions; electricalsteelexisting3.2percentSi reference. Genericmetalworking+1kWh/kgassembly,100percentmotorassemblyretention. Existing motorsteel/Algrades remainproxies; efficiency/torque/voltage not revalidated. Dedicated name outside genericEVmetaloverlay deliberately fixes this source design over time; avoids aluminum overlay doublecount and Nd-onlyoverwrite. No unsupported future gradelearning; future static-vs-learning comparison remains required. Rewire direct car/truck/bus roadmotor inputs and explicit roadperMJ copies; inductionrail/tram unchanged. Existing sourcevehicle life andMJallocation retained. Native backgroundmotor and genericmagnet supplies remain unchanged for other consumers. Individualoxideproviders keep REidentities visible to containedmetal accounting; no primary/secondary claim.</t>
+          <t>APPROVED TRACTION MAGNET GRADE REFERENCES, issue36, 2026-10-18. Jones etal2025 DOI10.1021/jacs.5c04150 SI TableS2, samplesB3 andA1; Hsieh etal2026 DOI10.1007/s11367-026-02610-7 SI TableS11 PMSM bulk components. Select one measured B3 magnet as engineering composition reference, NOT fleet average from two rotors. B3 masspercent:Nd21.9,Pr7.4,Tb0.5,Ho1.7,Co2.2,B0.9,Al0.2,Ca0.2,Fe64.8,Cu0.2 (sum100);Dy not detected, not proof absolutezero. Separate A1 sensitivity:Nd26.6,Tb0.6,Dy0.5,Ho2.2,Co2.4,B0.9,Al0.2,Ca0.1,Ti0.2,Fe66.2,Cu0.2;rounded source100.1percent, divided by100.1 to resolve rounding. Grade choice has substantialNd/Pr/Dy/Tb/Ho/Co sensitivity; unknown fleet penetration,gradeevolution and coercivity requirements remain gaps. Purchase individual oxide suppliers at stoichiometric containedmetal equivalents Nd2O3,Pr6O11,Tb4O7,Ho2O3,Dy2O3,Coasmetal,othermetals explicitly; B usesboricoxide/Causesquicklime/TiusesTiO2 as supply proxies. Oxide-to-metal reduction/reagents,oxygen/byproduct fate,boron/calciumretention and magnet coating are unresolved manufacturing gaps, not a closed full metallurgical process. Assume95percent magnet-material retention, matching5percentfinishedoffcut treatmentproxy, no recyclingcredit; yield sensitivity85-100percent and15kWh/kgmagnetprocess sensitivity5-30. Wholeoxide feed mass can exceed finishedmagnet mass due to oxygen:do not normalize elementalshares by gross feed mass. New roadmotor uses public PMSM non-magnet proportions20.3kgelectricalsteel,4.8Cu,14.6Al,3.9balance allocatedordinary steel as explicit shaft/bearingproxy. Missing source3.9kg componentbreakdown is not a measured steelrecipe. Keep existing0.03735849kgfinishedmagnet/kgmotor and all vehicle motor masses rather than resize magnetdemand to1.3/44.9kg/kg from a differentmotor. Distribute remainingmass across public non-magnet proportions; electricalsteelexisting3.2percentSi reference. Genericmetalworking+1kWh/kgassembly,100percentmotorassemblyretention. Existing motorsteel/Algrades remainproxies; efficiency/torque/voltage not revalidated. Dedicated name outside genericEVmetaloverlay deliberately fixes this source design over time; avoids aluminum overlay doublecount and Nd-onlyoverwrite. No unsupported future gradelearning; future static-vs-learning comparison remains required. Rewire direct car/truck/bus roadmotor inputs and explicit roadperMJ copies; inductionrail/tram unchanged. Existing sourcevehicle life andMJallocation retained. Native backgroundmotor and genericmagnet supplies remain unchanged for other consumers. Individualoxideproviders keep REidentities visible to containedmetal accounting; no primary/secondary claim.</t>
         </is>
       </c>
     </row>
@@ -3094,7 +3094,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>APPROVED TRACTION MAGNET GRADE REFERENCES, issue36, 2026-10-18. Jones etal2025 DOI10.1021/jacs.5c04150 SI TableS2, samplesB3 andA1; Hsieh etal2026 DOI10.1007/s11367-026-02610-7 SI TableS11 PMSM bulk components. Select one measured B3 magnet as engineering composition reference, NOT fleet average from two rotors. B3 masspercent:Nd21.9,Pr7.4,Tb0.5,Ho1.7,Co2.2,B0.9,Al0.2,Ca0.2,Fe64.8,Cu0.2 (sum100);Dy not detected, not proof absolutezero. Separate A1 sensitivity:Nd26.6,Tb0.6,Dy0.5,Ho2.2,Co2.4,B0.9,Al0.2,Ca0.1,Ti0.2,Fe66.2,Cu0.2;roundedsource99.9 normalized by99.9. Grade choice has substantialNd/Pr/Dy/Tb/Ho/Co sensitivity; unknown fleet penetration,gradeevolution and coercivity requirements remain gaps. Purchase individual oxide suppliers at stoichiometric containedmetal equivalents Nd2O3,Pr6O11,Tb4O7,Ho2O3,Dy2O3,Coasmetal,othermetals explicitly; B usesboricoxide/Causesquicklime/TiusesTiO2 as supply proxies. Oxide-to-metal reduction/reagents,oxygen/byproduct fate,boron/calciumretention and magnet coating are unresolved manufacturing gaps, not a closed full metallurgical process. Assume95percent magnet-material retention, matching5percentfinishedoffcut treatmentproxy, no recyclingcredit; yield sensitivity85-100percent and15kWh/kgmagnetprocess sensitivity5-30. Wholeoxide feed mass can exceed finishedmagnet mass due to oxygen:do not normalize elementalshares by gross feed mass. New roadmotor uses public PMSM non-magnet proportions20.3kgelectricalsteel,4.8Cu,14.6Al,3.9balance allocatedordinary steel as explicit shaft/bearingproxy. Missing source3.9kg componentbreakdown is not a measured steelrecipe. Keep existing0.03735849kgfinishedmagnet/kgmotor and all vehicle motor masses rather than resize magnetdemand to1.3/44.9kg/kg from a differentmotor. Distribute remainingmass across public non-magnet proportions; electricalsteelexisting3.2percentSi reference. Genericmetalworking+1kWh/kgassembly,100percentmotorassemblyretention. Existing motorsteel/Algrades remainproxies; efficiency/torque/voltage not revalidated. Dedicated name outside genericEVmetaloverlay deliberately fixes this source design over time; avoids aluminum overlay doublecount and Nd-onlyoverwrite. No unsupported future gradelearning; future static-vs-learning comparison remains required. Rewire direct car/truck/bus roadmotor inputs and explicit roadperMJ copies; inductionrail/tram unchanged. Existing sourcevehicle life andMJallocation retained. Native backgroundmotor and genericmagnet supplies remain unchanged for other consumers. Individualoxideproviders keep REidentities visible to containedmetal accounting; no primary/secondary claim.</t>
+          <t>APPROVED TRACTION MAGNET GRADE REFERENCES, issue36, 2026-10-18. Jones etal2025 DOI10.1021/jacs.5c04150 SI TableS2, samplesB3 andA1; Hsieh etal2026 DOI10.1007/s11367-026-02610-7 SI TableS11 PMSM bulk components. Select one measured B3 magnet as engineering composition reference, NOT fleet average from two rotors. B3 masspercent:Nd21.9,Pr7.4,Tb0.5,Ho1.7,Co2.2,B0.9,Al0.2,Ca0.2,Fe64.8,Cu0.2 (sum100);Dy not detected, not proof absolutezero. Separate A1 sensitivity:Nd26.6,Tb0.6,Dy0.5,Ho2.2,Co2.4,B0.9,Al0.2,Ca0.1,Ti0.2,Fe66.2,Cu0.2;rounded source100.1percent, divided by100.1 to resolve rounding. Grade choice has substantialNd/Pr/Dy/Tb/Ho/Co sensitivity; unknown fleet penetration,gradeevolution and coercivity requirements remain gaps. Purchase individual oxide suppliers at stoichiometric containedmetal equivalents Nd2O3,Pr6O11,Tb4O7,Ho2O3,Dy2O3,Coasmetal,othermetals explicitly; B usesboricoxide/Causesquicklime/TiusesTiO2 as supply proxies. Oxide-to-metal reduction/reagents,oxygen/byproduct fate,boron/calciumretention and magnet coating are unresolved manufacturing gaps, not a closed full metallurgical process. Assume95percent magnet-material retention, matching5percentfinishedoffcut treatmentproxy, no recyclingcredit; yield sensitivity85-100percent and15kWh/kgmagnetprocess sensitivity5-30. Wholeoxide feed mass can exceed finishedmagnet mass due to oxygen:do not normalize elementalshares by gross feed mass. New roadmotor uses public PMSM non-magnet proportions20.3kgelectricalsteel,4.8Cu,14.6Al,3.9balance allocatedordinary steel as explicit shaft/bearingproxy. Missing source3.9kg componentbreakdown is not a measured steelrecipe. Keep existing0.03735849kgfinishedmagnet/kgmotor and all vehicle motor masses rather than resize magnetdemand to1.3/44.9kg/kg from a differentmotor. Distribute remainingmass across public non-magnet proportions; electricalsteelexisting3.2percentSi reference. Genericmetalworking+1kWh/kgassembly,100percentmotorassemblyretention. Existing motorsteel/Algrades remainproxies; efficiency/torque/voltage not revalidated. Dedicated name outside genericEVmetaloverlay deliberately fixes this source design over time; avoids aluminum overlay doublecount and Nd-onlyoverwrite. No unsupported future gradelearning; future static-vs-learning comparison remains required. Rewire direct car/truck/bus roadmotor inputs and explicit roadperMJ copies; inductionrail/tram unchanged. Existing sourcevehicle life andMJallocation retained. Native backgroundmotor and genericmagnet supplies remain unchanged for other consumers. Individualoxideproviders keep REidentities visible to containedmetal accounting; no primary/secondary claim.</t>
         </is>
       </c>
     </row>
@@ -3720,7 +3720,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>APPROVED TRACTION MAGNET GRADE REFERENCES, issue36, 2026-10-18. Jones etal2025 DOI10.1021/jacs.5c04150 SI TableS2, samplesB3 andA1; Hsieh etal2026 DOI10.1007/s11367-026-02610-7 SI TableS11 PMSM bulk components. Select one measured B3 magnet as engineering composition reference, NOT fleet average from two rotors. B3 masspercent:Nd21.9,Pr7.4,Tb0.5,Ho1.7,Co2.2,B0.9,Al0.2,Ca0.2,Fe64.8,Cu0.2 (sum100);Dy not detected, not proof absolutezero. Separate A1 sensitivity:Nd26.6,Tb0.6,Dy0.5,Ho2.2,Co2.4,B0.9,Al0.2,Ca0.1,Ti0.2,Fe66.2,Cu0.2;roundedsource99.9 normalized by99.9. Grade choice has substantialNd/Pr/Dy/Tb/Ho/Co sensitivity; unknown fleet penetration,gradeevolution and coercivity requirements remain gaps. Purchase individual oxide suppliers at stoichiometric containedmetal equivalents Nd2O3,Pr6O11,Tb4O7,Ho2O3,Dy2O3,Coasmetal,othermetals explicitly; B usesboricoxide/Causesquicklime/TiusesTiO2 as supply proxies. Oxide-to-metal reduction/reagents,oxygen/byproduct fate,boron/calciumretention and magnet coating are unresolved manufacturing gaps, not a closed full metallurgical process. Assume95percent magnet-material retention, matching5percentfinishedoffcut treatmentproxy, no recyclingcredit; yield sensitivity85-100percent and15kWh/kgmagnetprocess sensitivity5-30. Wholeoxide feed mass can exceed finishedmagnet mass due to oxygen:do not normalize elementalshares by gross feed mass. New roadmotor uses public PMSM non-magnet proportions20.3kgelectricalsteel,4.8Cu,14.6Al,3.9balance allocatedordinary steel as explicit shaft/bearingproxy. Missing source3.9kg componentbreakdown is not a measured steelrecipe. Keep existing0.03735849kgfinishedmagnet/kgmotor and all vehicle motor masses rather than resize magnetdemand to1.3/44.9kg/kg from a differentmotor. Distribute remainingmass across public non-magnet proportions; electricalsteelexisting3.2percentSi reference. Genericmetalworking+1kWh/kgassembly,100percentmotorassemblyretention. Existing motorsteel/Algrades remainproxies; efficiency/torque/voltage not revalidated. Dedicated name outside genericEVmetaloverlay deliberately fixes this source design over time; avoids aluminum overlay doublecount and Nd-onlyoverwrite. No unsupported future gradelearning; future static-vs-learning comparison remains required. Rewire direct car/truck/bus roadmotor inputs and explicit roadperMJ copies; inductionrail/tram unchanged. Existing sourcevehicle life andMJallocation retained. Native backgroundmotor and genericmagnet supplies remain unchanged for other consumers. Individualoxideproviders keep REidentities visible to containedmetal accounting; no primary/secondary claim.</t>
+          <t>APPROVED TRACTION MAGNET GRADE REFERENCES, issue36, 2026-10-18. Jones etal2025 DOI10.1021/jacs.5c04150 SI TableS2, samplesB3 andA1; Hsieh etal2026 DOI10.1007/s11367-026-02610-7 SI TableS11 PMSM bulk components. Select one measured B3 magnet as engineering composition reference, NOT fleet average from two rotors. B3 masspercent:Nd21.9,Pr7.4,Tb0.5,Ho1.7,Co2.2,B0.9,Al0.2,Ca0.2,Fe64.8,Cu0.2 (sum100);Dy not detected, not proof absolutezero. Separate A1 sensitivity:Nd26.6,Tb0.6,Dy0.5,Ho2.2,Co2.4,B0.9,Al0.2,Ca0.1,Ti0.2,Fe66.2,Cu0.2;rounded source100.1percent, divided by100.1 to resolve rounding. Grade choice has substantialNd/Pr/Dy/Tb/Ho/Co sensitivity; unknown fleet penetration,gradeevolution and coercivity requirements remain gaps. Purchase individual oxide suppliers at stoichiometric containedmetal equivalents Nd2O3,Pr6O11,Tb4O7,Ho2O3,Dy2O3,Coasmetal,othermetals explicitly; B usesboricoxide/Causesquicklime/TiusesTiO2 as supply proxies. Oxide-to-metal reduction/reagents,oxygen/byproduct fate,boron/calciumretention and magnet coating are unresolved manufacturing gaps, not a closed full metallurgical process. Assume95percent magnet-material retention, matching5percentfinishedoffcut treatmentproxy, no recyclingcredit; yield sensitivity85-100percent and15kWh/kgmagnetprocess sensitivity5-30. Wholeoxide feed mass can exceed finishedmagnet mass due to oxygen:do not normalize elementalshares by gross feed mass. New roadmotor uses public PMSM non-magnet proportions20.3kgelectricalsteel,4.8Cu,14.6Al,3.9balance allocatedordinary steel as explicit shaft/bearingproxy. Missing source3.9kg componentbreakdown is not a measured steelrecipe. Keep existing0.03735849kgfinishedmagnet/kgmotor and all vehicle motor masses rather than resize magnetdemand to1.3/44.9kg/kg from a differentmotor. Distribute remainingmass across public non-magnet proportions; electricalsteelexisting3.2percentSi reference. Genericmetalworking+1kWh/kgassembly,100percentmotorassemblyretention. Existing motorsteel/Algrades remainproxies; efficiency/torque/voltage not revalidated. Dedicated name outside genericEVmetaloverlay deliberately fixes this source design over time; avoids aluminum overlay doublecount and Nd-onlyoverwrite. No unsupported future gradelearning; future static-vs-learning comparison remains required. Rewire direct car/truck/bus roadmotor inputs and explicit roadperMJ copies; inductionrail/tram unchanged. Existing sourcevehicle life andMJallocation retained. Native backgroundmotor and genericmagnet supplies remain unchanged for other consumers. Individualoxideproviders keep REidentities visible to containedmetal accounting; no primary/secondary claim.</t>
         </is>
       </c>
     </row>

--- a/premise/data/additional_inventories/lci-electric-car-mechanical-powertrain.xlsx
+++ b/premise/data/additional_inventories/lci-electric-car-mechanical-powertrain.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I298"/>
+  <dimension ref="A1:I360"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7931,6 +7931,1678 @@
         </is>
       </c>
     </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>end-of-life handling, dry combustion equipment engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B303">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>end-of-life handling, dry combustion equipment engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Notter et al.2010 Contribution of Li-ion batteries to the environmental impact of electric vehicles, DOI10.1021/es903729a, public SI TableS2 drivetrain detailed component rows https://pubs.acs.org/doi/suppl/10.1021/es903729a/suppl_file/es903729a_si_001.pdf ; native perkg manufacturing utilities retained only as process proxies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>APPROVED DRY COMBUSTION ENERGY-EQUIPMENT REFERENCE, issue51, 2026-10-18. Notter et al.2010 Contribution of Li-ion batteries to the environmental impact of electric vehicles, DOI10.1021/es903729a, public SI TableS2 drivetrain detailed component rows https://pubs.acs.org/doi/suppl/10.1021/es903729a/suppl_file/es903729a_si_001.pdf ; native perkg manufacturing utilities retained only as process proxies. Sum detailed source components, not rounded275kg fuel-inclusive aggregate. Exclude42kg initialpetrol because it is delivered/consumed fuel, and18kg common12Vstarterbattery because it is a common auxiliary function also needed by other powertrains, outside agreed energy-specific boundary. Retain combustion startermotor/alternator, engine,gearbox/clutch/differential, cooling, fuelpump/tank and exhaust/catalyst. These are combustion energy functions; no chassis, body,road added. Detailed dryhardware203.2019kg; initial6kg lubricant+7kg glycol are separately purchased workingfluids, not part of dry reference output or deliveredfuel. Existing fullvehicle/perkm maintenance fluid purchases remain; this only retains initialcharge, potential initial-versus-maintenance overlap remains a sourceboundary sensitivity. All hardware sourcegrossfeeds and losses derive from eachcomponent wastefactor, including1.25machinedsteel and1.5reinforcingsteel/exhaustfactor, not a uniform0.2 multiplier. Lowalloyretained85.7/gross108.375 andreinforcingretained28/gross42 imply36.675kg totalferrousfabricationloss after excluding starterbattery, which contains noferrous. Source Al49.5retained/61.875gross/12.375scrap is preserved; no repeat of former275kgAlrepair. Source products and ordinarycastalloy retain alloy-type proxies; no AlLi or source100%secondary mandate. Genericmetalworking purchases are services and do not add anotherkg of retainedmetal. Copper2kg, rubber3kg, PPS21kg,HDPE14kg and catalystPt1.6g/Pd0.3g retained explicitly; actual steelgrades/catalystsupport and modernemissionstandard remain gaps. Fabricationmetaloffcuts go once to existingcutoffscrapsinks; plasticloss goes towasteplastic. Dedicatedendoflife helper sends the same retainedAl/Fe/Cu to cutoffscrap outlets, polymer/rubber to generictreatment, smallPGMcontent to hazardousresidue, anddrains6kg oil/7kg glycol once. These are mass-accounting collection/fateproxies, not measuredrecyclingrates or primary-secondaryshares; no recoveredmetal credit or market-for-metal substitution is claimed. Shredding0.1kWh/kgdry is an engineeringallowance; metallurgicalrecovery,pollutantfate and specificcomponenttreatment remain gaps. Do not buy nativewholeengineEOL again or disposefuel/commonstarterbattery. Keep perkg nativeassemblyenergy/factory/water as unvalidatedmanufacturingproxies; watercollectedat1000kg/m3. Rewire only passenger/hybrid vehicle buyers ofnativepassengercarICE to dedicateddryreference, preserving their suppliedkg. Their mechanicalmassparameter is interpreted as dryenergy-equipment kg: this is explicitengineeringboundaryassumption; source276.2019kgcomponentvehicle is not eachcurrentvehicle. Vehiclemass/consumption is not re-simulated; sourceyear/size/fueltechnologydifferences and mass-sizing compatibility remain sensitivitygaps. Existing dedicatedtruck/busengines and fixedBEVmechanicalreference remain. PerMJ copies regenerated fromcurrentvehicles inissue44. Numericmassbudget: {"dry_hardware_reference_kg":203.2019,"separate_initial_working_fluids_kg":13.0,"retained_material_kg":{"aluminium, cast alloy":49.5,"steel, low-alloyed, hot rolled":85.7,"polyphenylene sulfide":21.0,"reinforcing steel":28.0,"polyethylene, high density, granulate":14.0,"synthetic rubber":3.0,"copper, cathode":2.0,"platinum":0.0016,"palladium":0.0003},"gross_purchase_kg":{"aluminium, cast alloy":61.875,"steel, low-alloyed, hot rolled":108.375,"polyphenylene sulfide":23.1,"reinforcing steel":42.0,"polyethylene, high density, granulate":15.399999999999999,"synthetic rubber":3.0,"copper, cathode":2.0,"platinum":0.0016,"palladium":0.0003},"ferrous_fabrication_scrap_kg":36.675,"initial_fuel_excluded_kg":42,"common_starter_battery_excluded_kg":18}</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>end-of-life handling, dry combustion equipment engineering reference</t>
+        </is>
+      </c>
+      <c r="B310">
+        <v>1</v>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>end-of-life handling, dry combustion equipment engineering reference</t>
+        </is>
+      </c>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>end-of-life handling, dry combustion equipment engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>aluminium scrap, post-consumer, Recycled Content cut-off</t>
+        </is>
+      </c>
+      <c r="B311">
+        <v>-0.24360008444802927</v>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>aluminium scrap, post-consumer</t>
+        </is>
+      </c>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>aluminium scrap, post-consumer</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>iron scrap, unsorted, Recycled Content cut-off</t>
+        </is>
+      </c>
+      <c r="B312">
+        <v>-0.4217480249938608</v>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>iron scrap, unsorted</t>
+        </is>
+      </c>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>iron scrap, unsorted</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>market for waste plastic, mixture</t>
+        </is>
+      </c>
+      <c r="B313">
+        <v>-0.10334549037189121</v>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>waste plastic, mixture</t>
+        </is>
+      </c>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>waste plastic, mixture</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>iron scrap, unsorted, Recycled Content cut-off</t>
+        </is>
+      </c>
+      <c r="B314">
+        <v>-0.13779398716252161</v>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>iron scrap, unsorted</t>
+        </is>
+      </c>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t>iron scrap, unsorted</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>market for waste plastic, mixture</t>
+        </is>
+      </c>
+      <c r="B315">
+        <v>-0.06889699358126081</v>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>waste plastic, mixture</t>
+        </is>
+      </c>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>waste plastic, mixture</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>market for waste plastic, mixture</t>
+        </is>
+      </c>
+      <c r="B316">
+        <v>-0.014763641481698744</v>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>waste plastic, mixture</t>
+        </is>
+      </c>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>waste plastic, mixture</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>copper scrap, sorted, pressed, Recycled Content cut-off</t>
+        </is>
+      </c>
+      <c r="B317">
+        <v>-0.00984242765446583</v>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>copper scrap, sorted, pressed</t>
+        </is>
+      </c>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>copper scrap, sorted, pressed</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>market for hazardous waste, for incineration</t>
+        </is>
+      </c>
+      <c r="B318">
+        <v>-7.873942123572663e-06</v>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
+        </is>
+      </c>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>market for hazardous waste, for incineration</t>
+        </is>
+      </c>
+      <c r="B319">
+        <v>-1.4763641481698743e-06</v>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
+        </is>
+      </c>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>market for hazardous waste, for incineration</t>
+        </is>
+      </c>
+      <c r="B320">
+        <v>-0.02952728296339749</v>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
+        </is>
+      </c>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>market for hazardous waste, for incineration</t>
+        </is>
+      </c>
+      <c r="B321">
+        <v>-0.034448496790630403</v>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
+        </is>
+      </c>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B322">
+        <v>0.1</v>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>internal combustion engine, dry energy-equipment engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B327">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>internal combustion engine, dry energy-equipment engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>Notter et al.2010 Contribution of Li-ion batteries to the environmental impact of electric vehicles, DOI10.1021/es903729a, public SI TableS2 drivetrain detailed component rows https://pubs.acs.org/doi/suppl/10.1021/es903729a/suppl_file/es903729a_si_001.pdf ; native perkg manufacturing utilities retained only as process proxies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>APPROVED DRY COMBUSTION ENERGY-EQUIPMENT REFERENCE, issue51, 2026-10-18. Notter et al.2010 Contribution of Li-ion batteries to the environmental impact of electric vehicles, DOI10.1021/es903729a, public SI TableS2 drivetrain detailed component rows https://pubs.acs.org/doi/suppl/10.1021/es903729a/suppl_file/es903729a_si_001.pdf ; native perkg manufacturing utilities retained only as process proxies. Sum detailed source components, not rounded275kg fuel-inclusive aggregate. Exclude42kg initialpetrol because it is delivered/consumed fuel, and18kg common12Vstarterbattery because it is a common auxiliary function also needed by other powertrains, outside agreed energy-specific boundary. Retain combustion startermotor/alternator, engine,gearbox/clutch/differential, cooling, fuelpump/tank and exhaust/catalyst. These are combustion energy functions; no chassis, body,road added. Detailed dryhardware203.2019kg; initial6kg lubricant+7kg glycol are separately purchased workingfluids, not part of dry reference output or deliveredfuel. Existing fullvehicle/perkm maintenance fluid purchases remain; this only retains initialcharge, potential initial-versus-maintenance overlap remains a sourceboundary sensitivity. All hardware sourcegrossfeeds and losses derive from eachcomponent wastefactor, including1.25machinedsteel and1.5reinforcingsteel/exhaustfactor, not a uniform0.2 multiplier. Lowalloyretained85.7/gross108.375 andreinforcingretained28/gross42 imply36.675kg totalferrousfabricationloss after excluding starterbattery, which contains noferrous. Source Al49.5retained/61.875gross/12.375scrap is preserved; no repeat of former275kgAlrepair. Source products and ordinarycastalloy retain alloy-type proxies; no AlLi or source100%secondary mandate. Genericmetalworking purchases are services and do not add anotherkg of retainedmetal. Copper2kg, rubber3kg, PPS21kg,HDPE14kg and catalystPt1.6g/Pd0.3g retained explicitly; actual steelgrades/catalystsupport and modernemissionstandard remain gaps. Fabricationmetaloffcuts go once to existingcutoffscrapsinks; plasticloss goes towasteplastic. Dedicatedendoflife helper sends the same retainedAl/Fe/Cu to cutoffscrap outlets, polymer/rubber to generictreatment, smallPGMcontent to hazardousresidue, anddrains6kg oil/7kg glycol once. These are mass-accounting collection/fateproxies, not measuredrecyclingrates or primary-secondaryshares; no recoveredmetal credit or market-for-metal substitution is claimed. Shredding0.1kWh/kgdry is an engineeringallowance; metallurgicalrecovery,pollutantfate and specificcomponenttreatment remain gaps. Do not buy nativewholeengineEOL again or disposefuel/commonstarterbattery. Keep perkg nativeassemblyenergy/factory/water as unvalidatedmanufacturingproxies; watercollectedat1000kg/m3. Rewire only passenger/hybrid vehicle buyers ofnativepassengercarICE to dedicateddryreference, preserving their suppliedkg. Their mechanicalmassparameter is interpreted as dryenergy-equipment kg: this is explicitengineeringboundaryassumption; source276.2019kgcomponentvehicle is not eachcurrentvehicle. Vehiclemass/consumption is not re-simulated; sourceyear/size/fueltechnologydifferences and mass-sizing compatibility remain sensitivitygaps. Existing dedicatedtruck/busengines and fixedBEVmechanicalreference remain. PerMJ copies regenerated fromcurrentvehicles inissue44. Numericmassbudget: {"dry_hardware_reference_kg":203.2019,"separate_initial_working_fluids_kg":13.0,"retained_material_kg":{"aluminium, cast alloy":49.5,"steel, low-alloyed, hot rolled":85.7,"polyphenylene sulfide":21.0,"reinforcing steel":28.0,"polyethylene, high density, granulate":14.0,"synthetic rubber":3.0,"copper, cathode":2.0,"platinum":0.0016,"palladium":0.0003},"gross_purchase_kg":{"aluminium, cast alloy":61.875,"steel, low-alloyed, hot rolled":108.375,"polyphenylene sulfide":23.1,"reinforcing steel":42.0,"polyethylene, high density, granulate":15.399999999999999,"synthetic rubber":3.0,"copper, cathode":2.0,"platinum":0.0016,"palladium":0.0003},"ferrous_fabrication_scrap_kg":36.675,"initial_fuel_excluded_kg":42,"common_starter_battery_excluded_kg":18}</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I333" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>internal combustion engine, dry energy-equipment engineering reference</t>
+        </is>
+      </c>
+      <c r="B334">
+        <v>1</v>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>internal combustion engine, dry energy-equipment engineering reference</t>
+        </is>
+      </c>
+      <c r="I334" t="inlineStr">
+        <is>
+          <t>internal combustion engine, dry energy-equipment engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>market for aluminium, cast alloy</t>
+        </is>
+      </c>
+      <c r="B335">
+        <v>0.3045001055600366</v>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>aluminium, cast alloy</t>
+        </is>
+      </c>
+      <c r="I335" t="inlineStr">
+        <is>
+          <t>aluminium, cast alloy</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>aluminium scrap, new, Recycled Content cut-off</t>
+        </is>
+      </c>
+      <c r="B336">
+        <v>-0.06090002111200732</v>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>aluminium scrap, new</t>
+        </is>
+      </c>
+      <c r="I336" t="inlineStr">
+        <is>
+          <t>aluminium scrap, new</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>market for steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="B337">
+        <v>0.5333365485263671</v>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="I337" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>iron scrap, unsorted, Recycled Content cut-off</t>
+        </is>
+      </c>
+      <c r="B338">
+        <v>-0.11158852353250633</v>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>iron scrap, unsorted</t>
+        </is>
+      </c>
+      <c r="I338" t="inlineStr">
+        <is>
+          <t>iron scrap, unsorted</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>market for polyphenylene sulfide</t>
+        </is>
+      </c>
+      <c r="B339">
+        <v>0.11368003940908034</v>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>polyphenylene sulfide</t>
+        </is>
+      </c>
+      <c r="I339" t="inlineStr">
+        <is>
+          <t>polyphenylene sulfide</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>market for waste plastic, mixture</t>
+        </is>
+      </c>
+      <c r="B340">
+        <v>-0.010334549037189129</v>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>waste plastic, mixture</t>
+        </is>
+      </c>
+      <c r="I340" t="inlineStr">
+        <is>
+          <t>waste plastic, mixture</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>market for reinforcing steel</t>
+        </is>
+      </c>
+      <c r="B341">
+        <v>0.20669098074378242</v>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>reinforcing steel</t>
+        </is>
+      </c>
+      <c r="I341" t="inlineStr">
+        <is>
+          <t>reinforcing steel</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>iron scrap, unsorted, Recycled Content cut-off</t>
+        </is>
+      </c>
+      <c r="B342">
+        <v>-0.06889699358126081</v>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>iron scrap, unsorted</t>
+        </is>
+      </c>
+      <c r="I342" t="inlineStr">
+        <is>
+          <t>iron scrap, unsorted</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>market for polyethylene, high density, granulate</t>
+        </is>
+      </c>
+      <c r="B343">
+        <v>0.07578669293938688</v>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>polyethylene, high density, granulate</t>
+        </is>
+      </c>
+      <c r="I343" t="inlineStr">
+        <is>
+          <t>polyethylene, high density, granulate</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>market for waste plastic, mixture</t>
+        </is>
+      </c>
+      <c r="B344">
+        <v>-0.006889699358126074</v>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>waste plastic, mixture</t>
+        </is>
+      </c>
+      <c r="I344" t="inlineStr">
+        <is>
+          <t>waste plastic, mixture</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>market for synthetic rubber</t>
+        </is>
+      </c>
+      <c r="B345">
+        <v>0.014763641481698744</v>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>synthetic rubber</t>
+        </is>
+      </c>
+      <c r="I345" t="inlineStr">
+        <is>
+          <t>synthetic rubber</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>market for copper, cathode</t>
+        </is>
+      </c>
+      <c r="B346">
+        <v>0.00984242765446583</v>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+      <c r="I346" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>market for platinum</t>
+        </is>
+      </c>
+      <c r="B347">
+        <v>7.873942123572663e-06</v>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>platinum</t>
+        </is>
+      </c>
+      <c r="I347" t="inlineStr">
+        <is>
+          <t>platinum</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>market for palladium</t>
+        </is>
+      </c>
+      <c r="B348">
+        <v>1.4763641481698743e-06</v>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>palladium</t>
+        </is>
+      </c>
+      <c r="I348" t="inlineStr">
+        <is>
+          <t>palladium</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>market for lubricating oil</t>
+        </is>
+      </c>
+      <c r="B349">
+        <v>0.02952728296339749</v>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>lubricating oil</t>
+        </is>
+      </c>
+      <c r="I349" t="inlineStr">
+        <is>
+          <t>lubricating oil</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>ethylene glycols production, thermal hydrolysis of ethylene oxide</t>
+        </is>
+      </c>
+      <c r="B350">
+        <v>0.034448496790630403</v>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>ethylene glycol</t>
+        </is>
+      </c>
+      <c r="I350" t="inlineStr">
+        <is>
+          <t>ethylene glycol</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>metal working, average for aluminium product manufacturing</t>
+        </is>
+      </c>
+      <c r="B351">
+        <v>0.3045001055600366</v>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>metal working, average for aluminium product manufacturing</t>
+        </is>
+      </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>metal working, average for aluminium product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+      <c r="B352">
+        <v>0.7400275292701496</v>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+      <c r="I352" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>metal working, average for copper product manufacturing</t>
+        </is>
+      </c>
+      <c r="B353">
+        <v>0.00984242765446583</v>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>metal working, average for copper product manufacturing</t>
+        </is>
+      </c>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t>metal working, average for copper product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>end-of-life handling, dry combustion equipment engineering reference</t>
+        </is>
+      </c>
+      <c r="B354">
+        <v>1</v>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>end-of-life handling, dry combustion equipment engineering reference</t>
+        </is>
+      </c>
+      <c r="I354" t="inlineStr">
+        <is>
+          <t>end-of-life handling, dry combustion equipment engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B355">
+        <v>2.0281227</v>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I355" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>market for heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+      <c r="B356">
+        <v>2.1039402</v>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>megajoule</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+      <c r="I356" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>market for heat, district or industrial, other than natural gas</t>
+        </is>
+      </c>
+      <c r="B357">
+        <v>0.059706412</v>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>megajoule</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, other than natural gas</t>
+        </is>
+      </c>
+      <c r="I357" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, other than natural gas</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>market for road vehicle factory</t>
+        </is>
+      </c>
+      <c r="B358">
+        <v>2.7578692e-10</v>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>road vehicle factory</t>
+        </is>
+      </c>
+      <c r="I358" t="inlineStr">
+        <is>
+          <t>road vehicle factory</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>market group for tap water</t>
+        </is>
+      </c>
+      <c r="B359">
+        <v>3.051661</v>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>tap water</t>
+        </is>
+      </c>
+      <c r="I359" t="inlineStr">
+        <is>
+          <t>tap water</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>market for wastewater, average</t>
+        </is>
+      </c>
+      <c r="B360">
+        <v>-0.0030516610000000002</v>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>cubic meter</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>wastewater, average</t>
+        </is>
+      </c>
+      <c r="I360" t="inlineStr">
+        <is>
+          <t>wastewater, average</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/premise/data/additional_inventories/lci-electric-car-mechanical-powertrain.xlsx
+++ b/premise/data/additional_inventories/lci-electric-car-mechanical-powertrain.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I360"/>
+  <dimension ref="A1:I408"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9603,6 +9603,1188 @@
         </is>
       </c>
     </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>converter, heavy-duty auxiliary 400V to24V, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B365">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>converter, heavy-duty auxiliary 400V to24V, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>Bel Power Solutions2025 datasheets https://www.belfuse.com/resources/datasheets/powersolutions/ds-BPS-700DNG40-24-series.pdf and https://www.belfuse.com/media/datasheets/products/power-supplies/ds-BPS-350DNG40-24-8.pdf :4kW,4.5kg,28Vnominal/20-30Voutput,143A,450-900V or240-450Vinput,up to8parallel,liquidcooling10L/min minimum50/50glycolwater,94%ratedpoint/95%maximum efficiency.</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>APPROVED HEAVY-DUTY AUXILIARY DC/DC REFERENCE, issue62, 2026-10-18. Bel Power Solutions2025 datasheets https://www.belfuse.com/resources/datasheets/powersolutions/ds-BPS-700DNG40-24-series.pdf and https://www.belfuse.com/media/datasheets/products/power-supplies/ds-BPS-350DNG40-24-8.pdf :4kW,4.5kg,28Vnominal/20-30Voutput,143A,450-900V or240-450Vinput,up to8parallel,liquidcooling10L/min minimum50/50glycolwater,94%ratedpoint/95%maximum efficiency. Replace bus/truck car-derived220-450V14V BSC624 analogue by nominal24V HDVauxiliaryconverter; source350 or700V variants chosen for declared400Vsmalltruck /800VlargeHDV engineeringarchitecture;635VPULSEbus also fits450-900V. Sourcevehicle actualvoltage/SOCwindow is not documented,so these adoptedwindows are explicit assumptions,not certifiedcompatibility. Use400Vvariant for3.5/7.5t truckclasses;800V forlargertrucks andbuses except635VFCEVbus. LV28Vsetpoint is withincommon24Vchargingfunction; auxiliary24Vloads/battery notaddedtwice. Infer requiredcontinuouspower from priorallowance qkg/4.8*2.8kW,selectceil(required/4) integerunits&lt;=8,oneinstalledset; thispreserves impliedminimumauxpower whilemakingcountphysical,not measuredvehicledemand.4.5kgdryperunit,newtotalmassreplacesold25kgbusallowance with18kg/16kW. A different inferredload orredundancyduty requiresresizing. ManufacturerdoesnotpublishBOM:explicit4.5kgengineeringreferenceAlhousing/baseplate2.1,Cu0.65,ferrite0.55,auxiliaryinterfaceboard0.7,filmcapacitor0.15,steel0.15,PA0.1,silicone0.05,powertransistorpackage0.05kg. Sourceouterdimensions284x55x348mm andAlalloyhousing;2mmclosed-shell estimate1.44366kg,additional0.65634kgbaseplate/fins is anassumption. Interfaceboard includeslowpowerregulation/logiconly,powertransistors andbulkfilmcapacitors are separate,notsecondcompleteconverter. Genericbigwiredtransistor is an explicit power-device manufacturingproxy; actual Si/SiC/MOSFET topologyandsemiconductorpreciousmetalsremainunverified,not silentlyreplaced bylowpowerTIregulator. No manufacturercomponentdeclarationclaim.100%retainedassemblyreference,4.5kWhassemblyandgenericmetalworking; sensitivityboard/magnetics0.5-2xwithfixedmassboundary. Sharedvehiclecoolantloop retained,no secondpumporfluidcharge;10L/min isflow notconsumedfluidvolume. Do not addnewoperatinglosses on top ofexistingvehicleenergy budget; source94%isnotfullvehicleefficiency. Onevehiclelifeassumption needsactualconverterlife. Updateproductionassemblymass only; roadenergydemand/curbperformance notresimulated. Cars,railconverters,tractioninverters andAC/DCchargersunchanged. Endoflife remainsvehicleboundary,device-specificfate gap. Refresh affectedperMJ coefficients and supplierprovenance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H371" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I371" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>converter, heavy-duty auxiliary 400V to24V, engineering reference</t>
+        </is>
+      </c>
+      <c r="B372">
+        <v>1</v>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>converter, heavy-duty auxiliary 400V to24V, engineering reference</t>
+        </is>
+      </c>
+      <c r="I372" t="inlineStr">
+        <is>
+          <t>converter, heavy-duty auxiliary 400V to24V, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>market for aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="B373">
+        <v>2.1</v>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="I373" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>market for copper, cathode</t>
+        </is>
+      </c>
+      <c r="B374">
+        <v>0.65</v>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+      <c r="I374" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>market for ferrite</t>
+        </is>
+      </c>
+      <c r="B375">
+        <v>0.55</v>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>ferrite</t>
+        </is>
+      </c>
+      <c r="I375" t="inlineStr">
+        <is>
+          <t>ferrite</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>battery auxiliary interface and power conditioning, engineering reference</t>
+        </is>
+      </c>
+      <c r="B376">
+        <v>0.7</v>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>battery auxiliary interface and power conditioning, engineering reference</t>
+        </is>
+      </c>
+      <c r="I376" t="inlineStr">
+        <is>
+          <t>battery auxiliary interface and power conditioning, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>market for capacitor, film type, for through-hole mounting</t>
+        </is>
+      </c>
+      <c r="B377">
+        <v>0.15</v>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>capacitor, film type, for through-hole mounting</t>
+        </is>
+      </c>
+      <c r="I377" t="inlineStr">
+        <is>
+          <t>capacitor, film type, for through-hole mounting</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>market for steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="B378">
+        <v>0.15</v>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="I378" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>market for nylon 6</t>
+        </is>
+      </c>
+      <c r="B379">
+        <v>0.1</v>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G379" t="inlineStr">
+        <is>
+          <t>nylon 6</t>
+        </is>
+      </c>
+      <c r="I379" t="inlineStr">
+        <is>
+          <t>nylon 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>market for silicone product</t>
+        </is>
+      </c>
+      <c r="B380">
+        <v>0.05</v>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>silicone product</t>
+        </is>
+      </c>
+      <c r="I380" t="inlineStr">
+        <is>
+          <t>silicone product</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>market for transistor, wired, big size, through-hole mounting</t>
+        </is>
+      </c>
+      <c r="B381">
+        <v>0.05</v>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>transistor, wired, big size, through-hole mounting</t>
+        </is>
+      </c>
+      <c r="I381" t="inlineStr">
+        <is>
+          <t>transistor, wired, big size, through-hole mounting</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B382">
+        <v>4.5</v>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I382" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>metal working, average for aluminium product manufacturing</t>
+        </is>
+      </c>
+      <c r="B383">
+        <v>2.1</v>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>metal working, average for aluminium product manufacturing</t>
+        </is>
+      </c>
+      <c r="I383" t="inlineStr">
+        <is>
+          <t>metal working, average for aluminium product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>metal working, average for copper product manufacturing</t>
+        </is>
+      </c>
+      <c r="B384">
+        <v>0.65</v>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>metal working, average for copper product manufacturing</t>
+        </is>
+      </c>
+      <c r="I384" t="inlineStr">
+        <is>
+          <t>metal working, average for copper product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>converter, heavy-duty auxiliary 800V to24V, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B389">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>converter, heavy-duty auxiliary 800V to24V, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>Bel Power Solutions2025 datasheets https://www.belfuse.com/resources/datasheets/powersolutions/ds-BPS-700DNG40-24-series.pdf and https://www.belfuse.com/media/datasheets/products/power-supplies/ds-BPS-350DNG40-24-8.pdf :4kW,4.5kg,28Vnominal/20-30Voutput,143A,450-900V or240-450Vinput,up to8parallel,liquidcooling10L/min minimum50/50glycolwater,94%ratedpoint/95%maximum efficiency.</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>APPROVED HEAVY-DUTY AUXILIARY DC/DC REFERENCE, issue62, 2026-10-18. Bel Power Solutions2025 datasheets https://www.belfuse.com/resources/datasheets/powersolutions/ds-BPS-700DNG40-24-series.pdf and https://www.belfuse.com/media/datasheets/products/power-supplies/ds-BPS-350DNG40-24-8.pdf :4kW,4.5kg,28Vnominal/20-30Voutput,143A,450-900V or240-450Vinput,up to8parallel,liquidcooling10L/min minimum50/50glycolwater,94%ratedpoint/95%maximum efficiency. Replace bus/truck car-derived220-450V14V BSC624 analogue by nominal24V HDVauxiliaryconverter; source350 or700V variants chosen for declared400Vsmalltruck /800VlargeHDV engineeringarchitecture;635VPULSEbus also fits450-900V. Sourcevehicle actualvoltage/SOCwindow is not documented,so these adoptedwindows are explicit assumptions,not certifiedcompatibility. Use400Vvariant for3.5/7.5t truckclasses;800V forlargertrucks andbuses except635VFCEVbus. LV28Vsetpoint is withincommon24Vchargingfunction; auxiliary24Vloads/battery notaddedtwice. Infer requiredcontinuouspower from priorallowance qkg/4.8*2.8kW,selectceil(required/4) integerunits&lt;=8,oneinstalledset; thispreserves impliedminimumauxpower whilemakingcountphysical,not measuredvehicledemand.4.5kgdryperunit,newtotalmassreplacesold25kgbusallowance with18kg/16kW. A different inferredload orredundancyduty requiresresizing. ManufacturerdoesnotpublishBOM:explicit4.5kgengineeringreferenceAlhousing/baseplate2.1,Cu0.65,ferrite0.55,auxiliaryinterfaceboard0.7,filmcapacitor0.15,steel0.15,PA0.1,silicone0.05,powertransistorpackage0.05kg. Sourceouterdimensions284x55x348mm andAlalloyhousing;2mmclosed-shell estimate1.44366kg,additional0.65634kgbaseplate/fins is anassumption. Interfaceboard includeslowpowerregulation/logiconly,powertransistors andbulkfilmcapacitors are separate,notsecondcompleteconverter. Genericbigwiredtransistor is an explicit power-device manufacturingproxy; actual Si/SiC/MOSFET topologyandsemiconductorpreciousmetalsremainunverified,not silentlyreplaced bylowpowerTIregulator. No manufacturercomponentdeclarationclaim.100%retainedassemblyreference,4.5kWhassemblyandgenericmetalworking; sensitivityboard/magnetics0.5-2xwithfixedmassboundary. Sharedvehiclecoolantloop retained,no secondpumporfluidcharge;10L/min isflow notconsumedfluidvolume. Do not addnewoperatinglosses on top ofexistingvehicleenergy budget; source94%isnotfullvehicleefficiency. Onevehiclelifeassumption needsactualconverterlife. Updateproductionassemblymass only; roadenergydemand/curbperformance notresimulated. Cars,railconverters,tractioninverters andAC/DCchargersunchanged. Endoflife remainsvehicleboundary,device-specificfate gap. Refresh affectedperMJ coefficients and supplierprovenance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H395" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I395" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>converter, heavy-duty auxiliary 800V to24V, engineering reference</t>
+        </is>
+      </c>
+      <c r="B396">
+        <v>1</v>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>converter, heavy-duty auxiliary 800V to24V, engineering reference</t>
+        </is>
+      </c>
+      <c r="I396" t="inlineStr">
+        <is>
+          <t>converter, heavy-duty auxiliary 800V to24V, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>market for aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="B397">
+        <v>2.1</v>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="I397" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>market for copper, cathode</t>
+        </is>
+      </c>
+      <c r="B398">
+        <v>0.65</v>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+      <c r="I398" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>market for ferrite</t>
+        </is>
+      </c>
+      <c r="B399">
+        <v>0.55</v>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>ferrite</t>
+        </is>
+      </c>
+      <c r="I399" t="inlineStr">
+        <is>
+          <t>ferrite</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>battery auxiliary interface and power conditioning, engineering reference</t>
+        </is>
+      </c>
+      <c r="B400">
+        <v>0.7</v>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>battery auxiliary interface and power conditioning, engineering reference</t>
+        </is>
+      </c>
+      <c r="I400" t="inlineStr">
+        <is>
+          <t>battery auxiliary interface and power conditioning, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>market for capacitor, film type, for through-hole mounting</t>
+        </is>
+      </c>
+      <c r="B401">
+        <v>0.15</v>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>capacitor, film type, for through-hole mounting</t>
+        </is>
+      </c>
+      <c r="I401" t="inlineStr">
+        <is>
+          <t>capacitor, film type, for through-hole mounting</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>market for steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="B402">
+        <v>0.15</v>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="I402" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>market for nylon 6</t>
+        </is>
+      </c>
+      <c r="B403">
+        <v>0.1</v>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>nylon 6</t>
+        </is>
+      </c>
+      <c r="I403" t="inlineStr">
+        <is>
+          <t>nylon 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>market for silicone product</t>
+        </is>
+      </c>
+      <c r="B404">
+        <v>0.05</v>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>silicone product</t>
+        </is>
+      </c>
+      <c r="I404" t="inlineStr">
+        <is>
+          <t>silicone product</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>market for transistor, wired, big size, through-hole mounting</t>
+        </is>
+      </c>
+      <c r="B405">
+        <v>0.05</v>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>transistor, wired, big size, through-hole mounting</t>
+        </is>
+      </c>
+      <c r="I405" t="inlineStr">
+        <is>
+          <t>transistor, wired, big size, through-hole mounting</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B406">
+        <v>4.5</v>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I406" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>metal working, average for aluminium product manufacturing</t>
+        </is>
+      </c>
+      <c r="B407">
+        <v>2.1</v>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>metal working, average for aluminium product manufacturing</t>
+        </is>
+      </c>
+      <c r="I407" t="inlineStr">
+        <is>
+          <t>metal working, average for aluminium product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>metal working, average for copper product manufacturing</t>
+        </is>
+      </c>
+      <c r="B408">
+        <v>0.65</v>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>metal working, average for copper product manufacturing</t>
+        </is>
+      </c>
+      <c r="I408" t="inlineStr">
+        <is>
+          <t>metal working, average for copper product manufacturing</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/premise/data/additional_inventories/lci-electric-car-mechanical-powertrain.xlsx
+++ b/premise/data/additional_inventories/lci-electric-car-mechanical-powertrain.xlsx
@@ -1923,7 +1923,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>auxiliary battery production, passenger car, historical proxy</t>
+          <t xml:space="preserve">auxiliary battery production, passenger car</t>
         </is>
       </c>
     </row>
@@ -1993,7 +1993,8 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Provisional Notter S2 starter-battery material proxy, not an identified modern EV battery: retained 13 kg lead, 4 kg case proxy and 1 kg acid per historical 18 kg reference. Preserves prior full-vehicle direct lead when assigned 18/275 of the old ICE proxy mass. Case chemistry, assembly, voltage/capacity, sizing, calendar replacements and treatment remain unvalidated. Common equipment excluded from per-MJ energy inventory.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: auxiliary battery production, passenger car, historical proxy. Former reference product: auxiliary battery, passenger car, historical proxy. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+Provisional Notter S2 starter-battery material proxy, not an identified modern EV battery: retained 13 kg lead, 4 kg case proxy and 1 kg acid per historical 18 kg reference. Preserves prior full-vehicle direct lead when assigned 18/275 of the old ICE proxy mass. Case chemistry, assembly, voltage/capacity, sizing, calendar replacements and treatment remain unvalidated. Common equipment excluded from per-MJ energy inventory.</t>
         </is>
       </c>
     </row>
@@ -2049,7 +2050,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>auxiliary battery production, passenger car, historical proxy</t>
+          <t xml:space="preserve">auxiliary battery production, passenger car</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -2240,7 +2241,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>market for auxiliary battery, passenger car, historical proxy</t>
+          <t xml:space="preserve">market for auxiliary battery, passenger car</t>
         </is>
       </c>
     </row>
@@ -2310,7 +2311,8 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Provisional Notter S2 starter-battery material proxy, not an identified modern EV battery: retained 13 kg lead, 4 kg case proxy and 1 kg acid per historical 18 kg reference. Preserves prior full-vehicle direct lead when assigned 18/275 of the old ICE proxy mass. Case chemistry, assembly, voltage/capacity, sizing, calendar replacements and treatment remain unvalidated. Common equipment excluded from per-MJ energy inventory.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: market for auxiliary battery, passenger car, historical proxy. Former reference product: auxiliary battery, passenger car, historical proxy. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+Provisional Notter S2 starter-battery material proxy, not an identified modern EV battery: retained 13 kg lead, 4 kg case proxy and 1 kg acid per historical 18 kg reference. Preserves prior full-vehicle direct lead when assigned 18/275 of the old ICE proxy mass. Case chemistry, assembly, voltage/capacity, sizing, calendar replacements and treatment remain unvalidated. Common equipment excluded from per-MJ energy inventory.</t>
         </is>
       </c>
     </row>
@@ -2366,7 +2368,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>market for auxiliary battery, passenger car, historical proxy</t>
+          <t xml:space="preserve">market for auxiliary battery, passenger car</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -2397,7 +2399,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>auxiliary battery production, passenger car, historical proxy</t>
+          <t xml:space="preserve">auxiliary battery production, passenger car</t>
         </is>
       </c>
       <c r="B98" t="n">
@@ -2433,7 +2435,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>permanent magnet, measured B3 grade, engineering reference</t>
+          <t xml:space="preserve">permanent magnet production, neodymium-iron-boron, B3 grade</t>
         </is>
       </c>
     </row>
@@ -2467,7 +2469,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>permanent magnet, measured B3 grade, engineering reference</t>
+          <t xml:space="preserve">permanent magnet, neodymium-iron-boron, B3 grade</t>
         </is>
       </c>
     </row>
@@ -2503,7 +2505,8 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>APPROVED TRACTION MAGNET GRADE REFERENCES, issue36, 2026-10-18. Jones etal2025 DOI10.1021/jacs.5c04150 SI TableS2, samplesB3 andA1; Hsieh etal2026 DOI10.1007/s11367-026-02610-7 SI TableS11 PMSM bulk components. Select one measured B3 magnet as engineering composition reference, NOT fleet average from two rotors. B3 masspercent:Nd21.9,Pr7.4,Tb0.5,Ho1.7,Co2.2,B0.9,Al0.2,Ca0.2,Fe64.8,Cu0.2 (sum100);Dy not detected, not proof absolutezero. Separate A1 sensitivity:Nd26.6,Tb0.6,Dy0.5,Ho2.2,Co2.4,B0.9,Al0.2,Ca0.1,Ti0.2,Fe66.2,Cu0.2;rounded source100.1percent, divided by100.1 to resolve rounding. Grade choice has substantialNd/Pr/Dy/Tb/Ho/Co sensitivity; unknown fleet penetration,gradeevolution and coercivity requirements remain gaps. Purchase individual oxide suppliers at stoichiometric containedmetal equivalents Nd2O3,Pr6O11,Tb4O7,Ho2O3,Dy2O3,Coasmetal,othermetals explicitly; B usesboricoxide/Causesquicklime/TiusesTiO2 as supply proxies. Oxide-to-metal reduction/reagents,oxygen/byproduct fate,boron/calciumretention and magnet coating are unresolved manufacturing gaps, not a closed full metallurgical process. Assume95percent magnet-material retention, matching5percentfinishedoffcut treatmentproxy, no recyclingcredit; yield sensitivity85-100percent and15kWh/kgmagnetprocess sensitivity5-30. Wholeoxide feed mass can exceed finishedmagnet mass due to oxygen:do not normalize elementalshares by gross feed mass. New roadmotor uses public PMSM non-magnet proportions20.3kgelectricalsteel,4.8Cu,14.6Al,3.9balance allocatedordinary steel as explicit shaft/bearingproxy. Missing source3.9kg componentbreakdown is not a measured steelrecipe. Keep existing0.03735849kgfinishedmagnet/kgmotor and all vehicle motor masses rather than resize magnetdemand to1.3/44.9kg/kg from a differentmotor. Distribute remainingmass across public non-magnet proportions; electricalsteelexisting3.2percentSi reference. Genericmetalworking+1kWh/kgassembly,100percentmotorassemblyretention. Existing motorsteel/Algrades remainproxies; efficiency/torque/voltage not revalidated. Dedicated name outside genericEVmetaloverlay deliberately fixes this source design over time; avoids aluminum overlay doublecount and Nd-onlyoverwrite. No unsupported future gradelearning; future static-vs-learning comparison remains required. Rewire direct car/truck/bus roadmotor inputs and explicit roadperMJ copies; inductionrail/tram unchanged. Existing sourcevehicle life andMJallocation retained. Native backgroundmotor and genericmagnet supplies remain unchanged for other consumers. Individualoxideproviders keep REidentities visible to containedmetal accounting; no primary/secondary claim.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: permanent magnet, measured B3 grade, engineering reference. Former reference product: permanent magnet, measured B3 grade, engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED TRACTION MAGNET GRADE REFERENCES, issue36, 2026-10-18. Jones etal2025 DOI10.1021/jacs.5c04150 SI TableS2, samplesB3 andA1; Hsieh etal2026 DOI10.1007/s11367-026-02610-7 SI TableS11 PMSM bulk components. Select one measured B3 magnet as engineering composition reference, NOT fleet average from two rotors. B3 masspercent:Nd21.9,Pr7.4,Tb0.5,Ho1.7,Co2.2,B0.9,Al0.2,Ca0.2,Fe64.8,Cu0.2 (sum100);Dy not detected, not proof absolutezero. Separate A1 sensitivity:Nd26.6,Tb0.6,Dy0.5,Ho2.2,Co2.4,B0.9,Al0.2,Ca0.1,Ti0.2,Fe66.2,Cu0.2;rounded source100.1percent, divided by100.1 to resolve rounding. Grade choice has substantialNd/Pr/Dy/Tb/Ho/Co sensitivity; unknown fleet penetration,gradeevolution and coercivity requirements remain gaps. Purchase individual oxide suppliers at stoichiometric containedmetal equivalents Nd2O3,Pr6O11,Tb4O7,Ho2O3,Dy2O3,Coasmetal,othermetals explicitly; B usesboricoxide/Causesquicklime/TiusesTiO2 as supply proxies. Oxide-to-metal reduction/reagents,oxygen/byproduct fate,boron/calciumretention and magnet coating are unresolved manufacturing gaps, not a closed full metallurgical process. Assume95percent magnet-material retention, matching5percentfinishedoffcut treatmentproxy, no recyclingcredit; yield sensitivity85-100percent and15kWh/kgmagnetprocess sensitivity5-30. Wholeoxide feed mass can exceed finishedmagnet mass due to oxygen:do not normalize elementalshares by gross feed mass. New roadmotor uses public PMSM non-magnet proportions20.3kgelectricalsteel,4.8Cu,14.6Al,3.9balance allocatedordinary steel as explicit shaft/bearingproxy. Missing source3.9kg componentbreakdown is not a measured steelrecipe. Keep existing0.03735849kgfinishedmagnet/kgmotor and all vehicle motor masses rather than resize magnetdemand to1.3/44.9kg/kg from a differentmotor. Distribute remainingmass across public non-magnet proportions; electricalsteelexisting3.2percentSi reference. Genericmetalworking+1kWh/kgassembly,100percentmotorassemblyretention. Existing motorsteel/Algrades remainproxies; efficiency/torque/voltage not revalidated. Dedicated name outside genericEVmetaloverlay deliberately fixes this source design over time; avoids aluminum overlay doublecount and Nd-onlyoverwrite. No unsupported future gradelearning; future static-vs-learning comparison remains required. Rewire direct car/truck/bus roadmotor inputs and explicit roadperMJ copies; inductionrail/tram unchanged. Existing sourcevehicle life andMJallocation retained. Native backgroundmotor and genericmagnet supplies remain unchanged for other consumers. Individualoxideproviders keep REidentities visible to containedmetal accounting; no primary/secondary claim.</t>
         </is>
       </c>
     </row>
@@ -2564,7 +2567,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>permanent magnet, measured B3 grade, engineering reference</t>
+          <t xml:space="preserve">permanent magnet production, neodymium-iron-boron, B3 grade</t>
         </is>
       </c>
       <c r="B110">
@@ -2587,12 +2590,12 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>permanent magnet, measured B3 grade, engineering reference</t>
+          <t xml:space="preserve">permanent magnet, neodymium-iron-boron, B3 grade</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>permanent magnet, measured B3 grade, engineering reference</t>
+          <t xml:space="preserve">permanent magnet, neodymium-iron-boron, B3 grade</t>
         </is>
       </c>
     </row>
@@ -3024,7 +3027,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>permanent magnet, measured A1 grade, engineering reference</t>
+          <t xml:space="preserve">permanent magnet production, neodymium-iron-boron, A1 grade</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3061,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>permanent magnet, measured A1 grade, engineering reference</t>
+          <t xml:space="preserve">permanent magnet, neodymium-iron-boron, A1 grade</t>
         </is>
       </c>
     </row>
@@ -3094,7 +3097,8 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>APPROVED TRACTION MAGNET GRADE REFERENCES, issue36, 2026-10-18. Jones etal2025 DOI10.1021/jacs.5c04150 SI TableS2, samplesB3 andA1; Hsieh etal2026 DOI10.1007/s11367-026-02610-7 SI TableS11 PMSM bulk components. Select one measured B3 magnet as engineering composition reference, NOT fleet average from two rotors. B3 masspercent:Nd21.9,Pr7.4,Tb0.5,Ho1.7,Co2.2,B0.9,Al0.2,Ca0.2,Fe64.8,Cu0.2 (sum100);Dy not detected, not proof absolutezero. Separate A1 sensitivity:Nd26.6,Tb0.6,Dy0.5,Ho2.2,Co2.4,B0.9,Al0.2,Ca0.1,Ti0.2,Fe66.2,Cu0.2;rounded source100.1percent, divided by100.1 to resolve rounding. Grade choice has substantialNd/Pr/Dy/Tb/Ho/Co sensitivity; unknown fleet penetration,gradeevolution and coercivity requirements remain gaps. Purchase individual oxide suppliers at stoichiometric containedmetal equivalents Nd2O3,Pr6O11,Tb4O7,Ho2O3,Dy2O3,Coasmetal,othermetals explicitly; B usesboricoxide/Causesquicklime/TiusesTiO2 as supply proxies. Oxide-to-metal reduction/reagents,oxygen/byproduct fate,boron/calciumretention and magnet coating are unresolved manufacturing gaps, not a closed full metallurgical process. Assume95percent magnet-material retention, matching5percentfinishedoffcut treatmentproxy, no recyclingcredit; yield sensitivity85-100percent and15kWh/kgmagnetprocess sensitivity5-30. Wholeoxide feed mass can exceed finishedmagnet mass due to oxygen:do not normalize elementalshares by gross feed mass. New roadmotor uses public PMSM non-magnet proportions20.3kgelectricalsteel,4.8Cu,14.6Al,3.9balance allocatedordinary steel as explicit shaft/bearingproxy. Missing source3.9kg componentbreakdown is not a measured steelrecipe. Keep existing0.03735849kgfinishedmagnet/kgmotor and all vehicle motor masses rather than resize magnetdemand to1.3/44.9kg/kg from a differentmotor. Distribute remainingmass across public non-magnet proportions; electricalsteelexisting3.2percentSi reference. Genericmetalworking+1kWh/kgassembly,100percentmotorassemblyretention. Existing motorsteel/Algrades remainproxies; efficiency/torque/voltage not revalidated. Dedicated name outside genericEVmetaloverlay deliberately fixes this source design over time; avoids aluminum overlay doublecount and Nd-onlyoverwrite. No unsupported future gradelearning; future static-vs-learning comparison remains required. Rewire direct car/truck/bus roadmotor inputs and explicit roadperMJ copies; inductionrail/tram unchanged. Existing sourcevehicle life andMJallocation retained. Native backgroundmotor and genericmagnet supplies remain unchanged for other consumers. Individualoxideproviders keep REidentities visible to containedmetal accounting; no primary/secondary claim.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: permanent magnet, measured A1 grade, engineering reference. Former reference product: permanent magnet, measured A1 grade, engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED TRACTION MAGNET GRADE REFERENCES, issue36, 2026-10-18. Jones etal2025 DOI10.1021/jacs.5c04150 SI TableS2, samplesB3 andA1; Hsieh etal2026 DOI10.1007/s11367-026-02610-7 SI TableS11 PMSM bulk components. Select one measured B3 magnet as engineering composition reference, NOT fleet average from two rotors. B3 masspercent:Nd21.9,Pr7.4,Tb0.5,Ho1.7,Co2.2,B0.9,Al0.2,Ca0.2,Fe64.8,Cu0.2 (sum100);Dy not detected, not proof absolutezero. Separate A1 sensitivity:Nd26.6,Tb0.6,Dy0.5,Ho2.2,Co2.4,B0.9,Al0.2,Ca0.1,Ti0.2,Fe66.2,Cu0.2;rounded source100.1percent, divided by100.1 to resolve rounding. Grade choice has substantialNd/Pr/Dy/Tb/Ho/Co sensitivity; unknown fleet penetration,gradeevolution and coercivity requirements remain gaps. Purchase individual oxide suppliers at stoichiometric containedmetal equivalents Nd2O3,Pr6O11,Tb4O7,Ho2O3,Dy2O3,Coasmetal,othermetals explicitly; B usesboricoxide/Causesquicklime/TiusesTiO2 as supply proxies. Oxide-to-metal reduction/reagents,oxygen/byproduct fate,boron/calciumretention and magnet coating are unresolved manufacturing gaps, not a closed full metallurgical process. Assume95percent magnet-material retention, matching5percentfinishedoffcut treatmentproxy, no recyclingcredit; yield sensitivity85-100percent and15kWh/kgmagnetprocess sensitivity5-30. Wholeoxide feed mass can exceed finishedmagnet mass due to oxygen:do not normalize elementalshares by gross feed mass. New roadmotor uses public PMSM non-magnet proportions20.3kgelectricalsteel,4.8Cu,14.6Al,3.9balance allocatedordinary steel as explicit shaft/bearingproxy. Missing source3.9kg componentbreakdown is not a measured steelrecipe. Keep existing0.03735849kgfinishedmagnet/kgmotor and all vehicle motor masses rather than resize magnetdemand to1.3/44.9kg/kg from a differentmotor. Distribute remainingmass across public non-magnet proportions; electricalsteelexisting3.2percentSi reference. Genericmetalworking+1kWh/kgassembly,100percentmotorassemblyretention. Existing motorsteel/Algrades remainproxies; efficiency/torque/voltage not revalidated. Dedicated name outside genericEVmetaloverlay deliberately fixes this source design over time; avoids aluminum overlay doublecount and Nd-onlyoverwrite. No unsupported future gradelearning; future static-vs-learning comparison remains required. Rewire direct car/truck/bus roadmotor inputs and explicit roadperMJ copies; inductionrail/tram unchanged. Existing sourcevehicle life andMJallocation retained. Native backgroundmotor and genericmagnet supplies remain unchanged for other consumers. Individualoxideproviders keep REidentities visible to containedmetal accounting; no primary/secondary claim.</t>
         </is>
       </c>
     </row>
@@ -3155,7 +3159,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>permanent magnet, measured A1 grade, engineering reference</t>
+          <t xml:space="preserve">permanent magnet production, neodymium-iron-boron, A1 grade</t>
         </is>
       </c>
       <c r="B134">
@@ -3178,12 +3182,12 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>permanent magnet, measured A1 grade, engineering reference</t>
+          <t xml:space="preserve">permanent magnet, neodymium-iron-boron, A1 grade</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>permanent magnet, measured A1 grade, engineering reference</t>
+          <t xml:space="preserve">permanent magnet, neodymium-iron-boron, A1 grade</t>
         </is>
       </c>
     </row>
@@ -3650,7 +3654,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>traction powertrain, permanent-magnet motor engineering reference</t>
+          <t xml:space="preserve">traction powertrain production, permanent magnet motor</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3688,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>traction powertrain, permanent-magnet motor engineering reference</t>
+          <t xml:space="preserve">traction powertrain, permanent magnet motor</t>
         </is>
       </c>
     </row>
@@ -3720,7 +3724,8 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>APPROVED TRACTION MAGNET GRADE REFERENCES, issue36, 2026-10-18. Jones etal2025 DOI10.1021/jacs.5c04150 SI TableS2, samplesB3 andA1; Hsieh etal2026 DOI10.1007/s11367-026-02610-7 SI TableS11 PMSM bulk components. Select one measured B3 magnet as engineering composition reference, NOT fleet average from two rotors. B3 masspercent:Nd21.9,Pr7.4,Tb0.5,Ho1.7,Co2.2,B0.9,Al0.2,Ca0.2,Fe64.8,Cu0.2 (sum100);Dy not detected, not proof absolutezero. Separate A1 sensitivity:Nd26.6,Tb0.6,Dy0.5,Ho2.2,Co2.4,B0.9,Al0.2,Ca0.1,Ti0.2,Fe66.2,Cu0.2;rounded source100.1percent, divided by100.1 to resolve rounding. Grade choice has substantialNd/Pr/Dy/Tb/Ho/Co sensitivity; unknown fleet penetration,gradeevolution and coercivity requirements remain gaps. Purchase individual oxide suppliers at stoichiometric containedmetal equivalents Nd2O3,Pr6O11,Tb4O7,Ho2O3,Dy2O3,Coasmetal,othermetals explicitly; B usesboricoxide/Causesquicklime/TiusesTiO2 as supply proxies. Oxide-to-metal reduction/reagents,oxygen/byproduct fate,boron/calciumretention and magnet coating are unresolved manufacturing gaps, not a closed full metallurgical process. Assume95percent magnet-material retention, matching5percentfinishedoffcut treatmentproxy, no recyclingcredit; yield sensitivity85-100percent and15kWh/kgmagnetprocess sensitivity5-30. Wholeoxide feed mass can exceed finishedmagnet mass due to oxygen:do not normalize elementalshares by gross feed mass. New roadmotor uses public PMSM non-magnet proportions20.3kgelectricalsteel,4.8Cu,14.6Al,3.9balance allocatedordinary steel as explicit shaft/bearingproxy. Missing source3.9kg componentbreakdown is not a measured steelrecipe. Keep existing0.03735849kgfinishedmagnet/kgmotor and all vehicle motor masses rather than resize magnetdemand to1.3/44.9kg/kg from a differentmotor. Distribute remainingmass across public non-magnet proportions; electricalsteelexisting3.2percentSi reference. Genericmetalworking+1kWh/kgassembly,100percentmotorassemblyretention. Existing motorsteel/Algrades remainproxies; efficiency/torque/voltage not revalidated. Dedicated name outside genericEVmetaloverlay deliberately fixes this source design over time; avoids aluminum overlay doublecount and Nd-onlyoverwrite. No unsupported future gradelearning; future static-vs-learning comparison remains required. Rewire direct car/truck/bus roadmotor inputs and explicit roadperMJ copies; inductionrail/tram unchanged. Existing sourcevehicle life andMJallocation retained. Native backgroundmotor and genericmagnet supplies remain unchanged for other consumers. Individualoxideproviders keep REidentities visible to containedmetal accounting; no primary/secondary claim.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: traction powertrain, permanent-magnet motor engineering reference. Former reference product: traction powertrain, permanent-magnet motor engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED TRACTION MAGNET GRADE REFERENCES, issue36, 2026-10-18. Jones etal2025 DOI10.1021/jacs.5c04150 SI TableS2, samplesB3 andA1; Hsieh etal2026 DOI10.1007/s11367-026-02610-7 SI TableS11 PMSM bulk components. Select one measured B3 magnet as engineering composition reference, NOT fleet average from two rotors. B3 masspercent:Nd21.9,Pr7.4,Tb0.5,Ho1.7,Co2.2,B0.9,Al0.2,Ca0.2,Fe64.8,Cu0.2 (sum100);Dy not detected, not proof absolutezero. Separate A1 sensitivity:Nd26.6,Tb0.6,Dy0.5,Ho2.2,Co2.4,B0.9,Al0.2,Ca0.1,Ti0.2,Fe66.2,Cu0.2;rounded source100.1percent, divided by100.1 to resolve rounding. Grade choice has substantialNd/Pr/Dy/Tb/Ho/Co sensitivity; unknown fleet penetration,gradeevolution and coercivity requirements remain gaps. Purchase individual oxide suppliers at stoichiometric containedmetal equivalents Nd2O3,Pr6O11,Tb4O7,Ho2O3,Dy2O3,Coasmetal,othermetals explicitly; B usesboricoxide/Causesquicklime/TiusesTiO2 as supply proxies. Oxide-to-metal reduction/reagents,oxygen/byproduct fate,boron/calciumretention and magnet coating are unresolved manufacturing gaps, not a closed full metallurgical process. Assume95percent magnet-material retention, matching5percentfinishedoffcut treatmentproxy, no recyclingcredit; yield sensitivity85-100percent and15kWh/kgmagnetprocess sensitivity5-30. Wholeoxide feed mass can exceed finishedmagnet mass due to oxygen:do not normalize elementalshares by gross feed mass. New roadmotor uses public PMSM non-magnet proportions20.3kgelectricalsteel,4.8Cu,14.6Al,3.9balance allocatedordinary steel as explicit shaft/bearingproxy. Missing source3.9kg componentbreakdown is not a measured steelrecipe. Keep existing0.03735849kgfinishedmagnet/kgmotor and all vehicle motor masses rather than resize magnetdemand to1.3/44.9kg/kg from a differentmotor. Distribute remainingmass across public non-magnet proportions; electricalsteelexisting3.2percentSi reference. Genericmetalworking+1kWh/kgassembly,100percentmotorassemblyretention. Existing motorsteel/Algrades remainproxies; efficiency/torque/voltage not revalidated. Dedicated name outside genericEVmetaloverlay deliberately fixes this source design over time; avoids aluminum overlay doublecount and Nd-onlyoverwrite. No unsupported future gradelearning; future static-vs-learning comparison remains required. Rewire direct car/truck/bus roadmotor inputs and explicit roadperMJ copies; inductionrail/tram unchanged. Existing sourcevehicle life andMJallocation retained. Native backgroundmotor and genericmagnet supplies remain unchanged for other consumers. Individualoxideproviders keep REidentities visible to containedmetal accounting; no primary/secondary claim.</t>
         </is>
       </c>
     </row>
@@ -3781,7 +3786,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>traction powertrain, permanent-magnet motor engineering reference</t>
+          <t xml:space="preserve">traction powertrain production, permanent magnet motor</t>
         </is>
       </c>
       <c r="B159">
@@ -3804,19 +3809,19 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>traction powertrain, permanent-magnet motor engineering reference</t>
+          <t xml:space="preserve">traction powertrain, permanent magnet motor</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>traction powertrain, permanent-magnet motor engineering reference</t>
+          <t xml:space="preserve">traction powertrain, permanent magnet motor</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>permanent magnet, measured B3 grade, engineering reference</t>
+          <t xml:space="preserve">permanent magnet production, neodymium-iron-boron, B3 grade</t>
         </is>
       </c>
       <c r="B160">
@@ -3839,19 +3844,19 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>permanent magnet, measured B3 grade, engineering reference</t>
+          <t xml:space="preserve">permanent magnet, neodymium-iron-boron, B3 grade</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>permanent magnet, measured B3 grade, engineering reference</t>
+          <t xml:space="preserve">permanent magnet, neodymium-iron-boron, B3 grade</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>non-oriented electrical steel, engineering alloy reference</t>
+          <t xml:space="preserve">electrical steel production, non-oriented</t>
         </is>
       </c>
       <c r="B161">
@@ -3874,12 +3879,12 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>non-oriented electrical steel, engineering alloy reference</t>
+          <t xml:space="preserve">electrical steel, non-oriented</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>non-oriented electrical steel, engineering alloy reference</t>
+          <t xml:space="preserve">electrical steel, non-oriented</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4141,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>bare printed circuit board, power electronics engineering reference</t>
+          <t xml:space="preserve">printed circuit board production, power electronics, bare</t>
         </is>
       </c>
     </row>
@@ -4170,7 +4175,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>bare printed circuit board, power electronics engineering reference</t>
+          <t xml:space="preserve">printed circuit board, power electronics, bare</t>
         </is>
       </c>
     </row>
@@ -4206,7 +4211,8 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>APPROVED ROAD CHARGER/CONVERTER REFERENCE MASS ACCOUNTING, issue37, 2026-10-18. NewRide2013 public appendix p66 https://www.newride.ch/documents/Forschungsprojekt_E-Scooters_2013/Anhang_zu_Schlussbericht_E-Scooter_2013.pdf; BRUSA NLG513 Jan2013 datasheet6.2kgwatercooled/3.3kWDC(3.68kWAC); BRUSA2023 BSC624 https://www.brusahypower.com/wp-content/uploads/2023/08/Datasheet_BSC6xx_20230704_Rev.-2.pdf pp2-3. Historical partial9.43145percent/4.4542percent positive residuals are NOT proven overcounts. New explicit6.2kgwatercooled NLG513-class charger:public gross material purchases from p66, engineering95percentretention for nonmetalcomponent purchases,80percentCu/steel/brass retention; retain source grossAl3.812kg and calibrate only its finishedhousing mass as6.2kg minus separately declared retainedcomponents. This is a mass-budget housing ENGINEERING ASSUMPTION, not recovery of measured gross-to-net yields or uniform source normalization; housing thickness,fins and wastefactor need directteardown confirmation. Include source separate.164kgmountedboardproxy plus.263m2barethroughholeboard; their assumed distinct roles may be wrong and are a board-boundary sensitivity, not merged as duplicate without evidence. Bareboardreference1.6mm1850kg/m3FR4,4x35umCu,50percentCuarea;retained3.5872kg/m2. Manufacture95percentCu/FR4retention with matching scrap,10kWh/m2; chemicaletch/drilling/plating/finish gaps remain. Nonmetal/componentprocessloss uses hazardous-waste-incineration as an explicit unvalidated mixedcomponent fateproxy. Other filmcapacitors,ferrite,resin,stainless,Cu,brass,Al2O3,silicone,HIPS retained explicitly; processservices are not counted asproductmass. Source unsupported area-only ceramicresistorprocessing is not a retainedmaterial input;source.006kgresistors modeled by real surface-resistormanufacturingproxy. Source0.0269kWh+72.7MJheat retained as assemblyreference; no new measuredfactoryclaim. New auxiliary DC/DC reference4.8kgBSC624,220-450VHV,14V200Acontinuous =&gt;2.8kW,250Apeak=&gt;3.5kW. PDF continuous/maxpower rows conflict with these currentratings; adopt conservative current-derived2.8kWcontinuous. PUBLIC COMPONENT RECIPE NOT AVAILABLE:transfer corrected charger retained material proportions perkg as explicit DC/DC ANALOGUE,not manufacturer BSC624BOM. Sensitivityboardarea0.5-2x,componentfractions andhousingresidual; increasing a component reduceshousing withinfixedmass, not normalizeallinputs. This leaves topology-specificmagnetics/semiconductor/capacitor uncertainty, so convertermetalcoefficients are not certified. Keep existingvehiclekg/duty/replacementbudgets:chargernameplateequivalent=qkg/6.2*3.3kW;converter=qkg/4.8*2.8kW. Fractionaldeviceequivalence, thermaladequacy and voltageadaptation forbus/truck remain explicit gaps; no new inferredintegerunits or fastchargerpower.400/800Vbuscompatibility is not established by this450Vdevice reference. Separate offboard fastchargers and roadinverters unchanged; railconverters unchanged. ExistingperMJadapter retains renamedcharger/converterhardware. No chassis/road added, no sourceenergydemand or primary/secondary changes; EOL remains existingvehicle treatment boundary and dedicatedcomponentEOLgap.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: bare printed circuit board, power electronics engineering reference. Former reference product: bare printed circuit board, power electronics engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED ROAD CHARGER/CONVERTER REFERENCE MASS ACCOUNTING, issue37, 2026-10-18. NewRide2013 public appendix p66 https://www.newride.ch/documents/Forschungsprojekt_E-Scooters_2013/Anhang_zu_Schlussbericht_E-Scooter_2013.pdf; BRUSA NLG513 Jan2013 datasheet6.2kgwatercooled/3.3kWDC(3.68kWAC); BRUSA2023 BSC624 https://www.brusahypower.com/wp-content/uploads/2023/08/Datasheet_BSC6xx_20230704_Rev.-2.pdf pp2-3. Historical partial9.43145percent/4.4542percent positive residuals are NOT proven overcounts. New explicit6.2kgwatercooled NLG513-class charger:public gross material purchases from p66, engineering95percentretention for nonmetalcomponent purchases,80percentCu/steel/brass retention; retain source grossAl3.812kg and calibrate only its finishedhousing mass as6.2kg minus separately declared retainedcomponents. This is a mass-budget housing ENGINEERING ASSUMPTION, not recovery of measured gross-to-net yields or uniform source normalization; housing thickness,fins and wastefactor need directteardown confirmation. Include source separate.164kgmountedboardproxy plus.263m2barethroughholeboard; their assumed distinct roles may be wrong and are a board-boundary sensitivity, not merged as duplicate without evidence. Bareboardreference1.6mm1850kg/m3FR4,4x35umCu,50percentCuarea;retained3.5872kg/m2. Manufacture95percentCu/FR4retention with matching scrap,10kWh/m2; chemicaletch/drilling/plating/finish gaps remain. Nonmetal/componentprocessloss uses hazardous-waste-incineration as an explicit unvalidated mixedcomponent fateproxy. Other filmcapacitors,ferrite,resin,stainless,Cu,brass,Al2O3,silicone,HIPS retained explicitly; processservices are not counted asproductmass. Source unsupported area-only ceramicresistorprocessing is not a retainedmaterial input;source.006kgresistors modeled by real surface-resistormanufacturingproxy. Source0.0269kWh+72.7MJheat retained as assemblyreference; no new measuredfactoryclaim. New auxiliary DC/DC reference4.8kgBSC624,220-450VHV,14V200Acontinuous =&gt;2.8kW,250Apeak=&gt;3.5kW. PDF continuous/maxpower rows conflict with these currentratings; adopt conservative current-derived2.8kWcontinuous. PUBLIC COMPONENT RECIPE NOT AVAILABLE:transfer corrected charger retained material proportions perkg as explicit DC/DC ANALOGUE,not manufacturer BSC624BOM. Sensitivityboardarea0.5-2x,componentfractions andhousingresidual; increasing a component reduceshousing withinfixedmass, not normalizeallinputs. This leaves topology-specificmagnetics/semiconductor/capacitor uncertainty, so convertermetalcoefficients are not certified. Keep existingvehiclekg/duty/replacementbudgets:chargernameplateequivalent=qkg/6.2*3.3kW;converter=qkg/4.8*2.8kW. Fractionaldeviceequivalence, thermaladequacy and voltageadaptation forbus/truck remain explicit gaps; no new inferredintegerunits or fastchargerpower.400/800Vbuscompatibility is not established by this450Vdevice reference. Separate offboard fastchargers and roadinverters unchanged; railconverters unchanged. ExistingperMJadapter retains renamedcharger/converterhardware. No chassis/road added, no sourceenergydemand or primary/secondary changes; EOL remains existingvehicle treatment boundary and dedicatedcomponentEOLgap.</t>
         </is>
       </c>
     </row>
@@ -4267,7 +4273,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>bare printed circuit board, power electronics engineering reference</t>
+          <t xml:space="preserve">printed circuit board production, power electronics, bare</t>
         </is>
       </c>
       <c r="B180">
@@ -4290,12 +4296,12 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>bare printed circuit board, power electronics engineering reference</t>
+          <t xml:space="preserve">printed circuit board, power electronics, bare</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>bare printed circuit board, power electronics engineering reference</t>
+          <t xml:space="preserve">printed circuit board, power electronics, bare</t>
         </is>
       </c>
     </row>
@@ -4517,7 +4523,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>charger, road onboard engineering reference</t>
+          <t xml:space="preserve">charger production, road vehicle, onboard</t>
         </is>
       </c>
     </row>
@@ -4551,7 +4557,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>charger, road onboard engineering reference</t>
+          <t xml:space="preserve">charger, road vehicle, onboard</t>
         </is>
       </c>
     </row>
@@ -4587,7 +4593,8 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>APPROVED ROAD CHARGER/CONVERTER REFERENCE MASS ACCOUNTING, issue37, 2026-10-18. NewRide2013 public appendix p66 https://www.newride.ch/documents/Forschungsprojekt_E-Scooters_2013/Anhang_zu_Schlussbericht_E-Scooter_2013.pdf; BRUSA NLG513 Jan2013 datasheet6.2kgwatercooled/3.3kWDC(3.68kWAC); BRUSA2023 BSC624 https://www.brusahypower.com/wp-content/uploads/2023/08/Datasheet_BSC6xx_20230704_Rev.-2.pdf pp2-3. Historical partial9.43145percent/4.4542percent positive residuals are NOT proven overcounts. New explicit6.2kgwatercooled NLG513-class charger:public gross material purchases from p66, engineering95percentretention for nonmetalcomponent purchases,80percentCu/steel/brass retention; retain source grossAl3.812kg and calibrate only its finishedhousing mass as6.2kg minus separately declared retainedcomponents. This is a mass-budget housing ENGINEERING ASSUMPTION, not recovery of measured gross-to-net yields or uniform source normalization; housing thickness,fins and wastefactor need directteardown confirmation. Include source separate.164kgmountedboardproxy plus.263m2barethroughholeboard; their assumed distinct roles may be wrong and are a board-boundary sensitivity, not merged as duplicate without evidence. Bareboardreference1.6mm1850kg/m3FR4,4x35umCu,50percentCuarea;retained3.5872kg/m2. Manufacture95percentCu/FR4retention with matching scrap,10kWh/m2; chemicaletch/drilling/plating/finish gaps remain. Nonmetal/componentprocessloss uses hazardous-waste-incineration as an explicit unvalidated mixedcomponent fateproxy. Other filmcapacitors,ferrite,resin,stainless,Cu,brass,Al2O3,silicone,HIPS retained explicitly; processservices are not counted asproductmass. Source unsupported area-only ceramicresistorprocessing is not a retainedmaterial input;source.006kgresistors modeled by real surface-resistormanufacturingproxy. Source0.0269kWh+72.7MJheat retained as assemblyreference; no new measuredfactoryclaim. New auxiliary DC/DC reference4.8kgBSC624,220-450VHV,14V200Acontinuous =&gt;2.8kW,250Apeak=&gt;3.5kW. PDF continuous/maxpower rows conflict with these currentratings; adopt conservative current-derived2.8kWcontinuous. PUBLIC COMPONENT RECIPE NOT AVAILABLE:transfer corrected charger retained material proportions perkg as explicit DC/DC ANALOGUE,not manufacturer BSC624BOM. Sensitivityboardarea0.5-2x,componentfractions andhousingresidual; increasing a component reduceshousing withinfixedmass, not normalizeallinputs. This leaves topology-specificmagnetics/semiconductor/capacitor uncertainty, so convertermetalcoefficients are not certified. Keep existingvehiclekg/duty/replacementbudgets:chargernameplateequivalent=qkg/6.2*3.3kW;converter=qkg/4.8*2.8kW. Fractionaldeviceequivalence, thermaladequacy and voltageadaptation forbus/truck remain explicit gaps; no new inferredintegerunits or fastchargerpower.400/800Vbuscompatibility is not established by this450Vdevice reference. Separate offboard fastchargers and roadinverters unchanged; railconverters unchanged. ExistingperMJadapter retains renamedcharger/converterhardware. No chassis/road added, no sourceenergydemand or primary/secondary changes; EOL remains existingvehicle treatment boundary and dedicatedcomponentEOLgap.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: charger, road onboard engineering reference. Former reference product: charger, road onboard engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED ROAD CHARGER/CONVERTER REFERENCE MASS ACCOUNTING, issue37, 2026-10-18. NewRide2013 public appendix p66 https://www.newride.ch/documents/Forschungsprojekt_E-Scooters_2013/Anhang_zu_Schlussbericht_E-Scooter_2013.pdf; BRUSA NLG513 Jan2013 datasheet6.2kgwatercooled/3.3kWDC(3.68kWAC); BRUSA2023 BSC624 https://www.brusahypower.com/wp-content/uploads/2023/08/Datasheet_BSC6xx_20230704_Rev.-2.pdf pp2-3. Historical partial9.43145percent/4.4542percent positive residuals are NOT proven overcounts. New explicit6.2kgwatercooled NLG513-class charger:public gross material purchases from p66, engineering95percentretention for nonmetalcomponent purchases,80percentCu/steel/brass retention; retain source grossAl3.812kg and calibrate only its finishedhousing mass as6.2kg minus separately declared retainedcomponents. This is a mass-budget housing ENGINEERING ASSUMPTION, not recovery of measured gross-to-net yields or uniform source normalization; housing thickness,fins and wastefactor need directteardown confirmation. Include source separate.164kgmountedboardproxy plus.263m2barethroughholeboard; their assumed distinct roles may be wrong and are a board-boundary sensitivity, not merged as duplicate without evidence. Bareboardreference1.6mm1850kg/m3FR4,4x35umCu,50percentCuarea;retained3.5872kg/m2. Manufacture95percentCu/FR4retention with matching scrap,10kWh/m2; chemicaletch/drilling/plating/finish gaps remain. Nonmetal/componentprocessloss uses hazardous-waste-incineration as an explicit unvalidated mixedcomponent fateproxy. Other filmcapacitors,ferrite,resin,stainless,Cu,brass,Al2O3,silicone,HIPS retained explicitly; processservices are not counted asproductmass. Source unsupported area-only ceramicresistorprocessing is not a retainedmaterial input;source.006kgresistors modeled by real surface-resistormanufacturingproxy. Source0.0269kWh+72.7MJheat retained as assemblyreference; no new measuredfactoryclaim. New auxiliary DC/DC reference4.8kgBSC624,220-450VHV,14V200Acontinuous =&gt;2.8kW,250Apeak=&gt;3.5kW. PDF continuous/maxpower rows conflict with these currentratings; adopt conservative current-derived2.8kWcontinuous. PUBLIC COMPONENT RECIPE NOT AVAILABLE:transfer corrected charger retained material proportions perkg as explicit DC/DC ANALOGUE,not manufacturer BSC624BOM. Sensitivityboardarea0.5-2x,componentfractions andhousingresidual; increasing a component reduceshousing withinfixedmass, not normalizeallinputs. This leaves topology-specificmagnetics/semiconductor/capacitor uncertainty, so convertermetalcoefficients are not certified. Keep existingvehiclekg/duty/replacementbudgets:chargernameplateequivalent=qkg/6.2*3.3kW;converter=qkg/4.8*2.8kW. Fractionaldeviceequivalence, thermaladequacy and voltageadaptation forbus/truck remain explicit gaps; no new inferredintegerunits or fastchargerpower.400/800Vbuscompatibility is not established by this450Vdevice reference. Separate offboard fastchargers and roadinverters unchanged; railconverters unchanged. ExistingperMJadapter retains renamedcharger/converterhardware. No chassis/road added, no sourceenergydemand or primary/secondary changes; EOL remains existingvehicle treatment boundary and dedicatedcomponentEOLgap.</t>
         </is>
       </c>
     </row>
@@ -4648,7 +4655,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>charger, road onboard engineering reference</t>
+          <t xml:space="preserve">charger production, road vehicle, onboard</t>
         </is>
       </c>
       <c r="B198">
@@ -4671,12 +4678,12 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>charger, road onboard engineering reference</t>
+          <t xml:space="preserve">charger, road vehicle, onboard</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>charger, road onboard engineering reference</t>
+          <t xml:space="preserve">charger, road vehicle, onboard</t>
         </is>
       </c>
     </row>
@@ -5103,7 +5110,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>bare printed circuit board, power electronics engineering reference</t>
+          <t xml:space="preserve">printed circuit board production, power electronics, bare</t>
         </is>
       </c>
       <c r="B211">
@@ -5126,12 +5133,12 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>bare printed circuit board, power electronics engineering reference</t>
+          <t xml:space="preserve">printed circuit board, power electronics, bare</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>bare printed circuit board, power electronics engineering reference</t>
+          <t xml:space="preserve">printed circuit board, power electronics, bare</t>
         </is>
       </c>
     </row>
@@ -6228,7 +6235,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>converter, road auxiliary DC engineering analogue</t>
+          <t xml:space="preserve">converter production, road vehicle, auxiliary DC</t>
         </is>
       </c>
     </row>
@@ -6262,7 +6269,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>converter, road auxiliary DC engineering analogue</t>
+          <t xml:space="preserve">converter, road vehicle, auxiliary DC</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6305,8 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>APPROVED ROAD CHARGER/CONVERTER REFERENCE MASS ACCOUNTING, issue37, 2026-10-18. NewRide2013 public appendix p66 https://www.newride.ch/documents/Forschungsprojekt_E-Scooters_2013/Anhang_zu_Schlussbericht_E-Scooter_2013.pdf; BRUSA NLG513 Jan2013 datasheet6.2kgwatercooled/3.3kWDC(3.68kWAC); BRUSA2023 BSC624 https://www.brusahypower.com/wp-content/uploads/2023/08/Datasheet_BSC6xx_20230704_Rev.-2.pdf pp2-3. Historical partial9.43145percent/4.4542percent positive residuals are NOT proven overcounts. New explicit6.2kgwatercooled NLG513-class charger:public gross material purchases from p66, engineering95percentretention for nonmetalcomponent purchases,80percentCu/steel/brass retention; retain source grossAl3.812kg and calibrate only its finishedhousing mass as6.2kg minus separately declared retainedcomponents. This is a mass-budget housing ENGINEERING ASSUMPTION, not recovery of measured gross-to-net yields or uniform source normalization; housing thickness,fins and wastefactor need directteardown confirmation. Include source separate.164kgmountedboardproxy plus.263m2barethroughholeboard; their assumed distinct roles may be wrong and are a board-boundary sensitivity, not merged as duplicate without evidence. Bareboardreference1.6mm1850kg/m3FR4,4x35umCu,50percentCuarea;retained3.5872kg/m2. Manufacture95percentCu/FR4retention with matching scrap,10kWh/m2; chemicaletch/drilling/plating/finish gaps remain. Nonmetal/componentprocessloss uses hazardous-waste-incineration as an explicit unvalidated mixedcomponent fateproxy. Other filmcapacitors,ferrite,resin,stainless,Cu,brass,Al2O3,silicone,HIPS retained explicitly; processservices are not counted asproductmass. Source unsupported area-only ceramicresistorprocessing is not a retainedmaterial input;source.006kgresistors modeled by real surface-resistormanufacturingproxy. Source0.0269kWh+72.7MJheat retained as assemblyreference; no new measuredfactoryclaim. New auxiliary DC/DC reference4.8kgBSC624,220-450VHV,14V200Acontinuous =&gt;2.8kW,250Apeak=&gt;3.5kW. PDF continuous/maxpower rows conflict with these currentratings; adopt conservative current-derived2.8kWcontinuous. PUBLIC COMPONENT RECIPE NOT AVAILABLE:transfer corrected charger retained material proportions perkg as explicit DC/DC ANALOGUE,not manufacturer BSC624BOM. Sensitivityboardarea0.5-2x,componentfractions andhousingresidual; increasing a component reduceshousing withinfixedmass, not normalizeallinputs. This leaves topology-specificmagnetics/semiconductor/capacitor uncertainty, so convertermetalcoefficients are not certified. Keep existingvehiclekg/duty/replacementbudgets:chargernameplateequivalent=qkg/6.2*3.3kW;converter=qkg/4.8*2.8kW. Fractionaldeviceequivalence, thermaladequacy and voltageadaptation forbus/truck remain explicit gaps; no new inferredintegerunits or fastchargerpower.400/800Vbuscompatibility is not established by this450Vdevice reference. Separate offboard fastchargers and roadinverters unchanged; railconverters unchanged. ExistingperMJadapter retains renamedcharger/converterhardware. No chassis/road added, no sourceenergydemand or primary/secondary changes; EOL remains existingvehicle treatment boundary and dedicatedcomponentEOLgap.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: converter, road auxiliary DC engineering analogue. Former reference product: converter, road auxiliary DC engineering analogue. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED ROAD CHARGER/CONVERTER REFERENCE MASS ACCOUNTING, issue37, 2026-10-18. NewRide2013 public appendix p66 https://www.newride.ch/documents/Forschungsprojekt_E-Scooters_2013/Anhang_zu_Schlussbericht_E-Scooter_2013.pdf; BRUSA NLG513 Jan2013 datasheet6.2kgwatercooled/3.3kWDC(3.68kWAC); BRUSA2023 BSC624 https://www.brusahypower.com/wp-content/uploads/2023/08/Datasheet_BSC6xx_20230704_Rev.-2.pdf pp2-3. Historical partial9.43145percent/4.4542percent positive residuals are NOT proven overcounts. New explicit6.2kgwatercooled NLG513-class charger:public gross material purchases from p66, engineering95percentretention for nonmetalcomponent purchases,80percentCu/steel/brass retention; retain source grossAl3.812kg and calibrate only its finishedhousing mass as6.2kg minus separately declared retainedcomponents. This is a mass-budget housing ENGINEERING ASSUMPTION, not recovery of measured gross-to-net yields or uniform source normalization; housing thickness,fins and wastefactor need directteardown confirmation. Include source separate.164kgmountedboardproxy plus.263m2barethroughholeboard; their assumed distinct roles may be wrong and are a board-boundary sensitivity, not merged as duplicate without evidence. Bareboardreference1.6mm1850kg/m3FR4,4x35umCu,50percentCuarea;retained3.5872kg/m2. Manufacture95percentCu/FR4retention with matching scrap,10kWh/m2; chemicaletch/drilling/plating/finish gaps remain. Nonmetal/componentprocessloss uses hazardous-waste-incineration as an explicit unvalidated mixedcomponent fateproxy. Other filmcapacitors,ferrite,resin,stainless,Cu,brass,Al2O3,silicone,HIPS retained explicitly; processservices are not counted asproductmass. Source unsupported area-only ceramicresistorprocessing is not a retainedmaterial input;source.006kgresistors modeled by real surface-resistormanufacturingproxy. Source0.0269kWh+72.7MJheat retained as assemblyreference; no new measuredfactoryclaim. New auxiliary DC/DC reference4.8kgBSC624,220-450VHV,14V200Acontinuous =&gt;2.8kW,250Apeak=&gt;3.5kW. PDF continuous/maxpower rows conflict with these currentratings; adopt conservative current-derived2.8kWcontinuous. PUBLIC COMPONENT RECIPE NOT AVAILABLE:transfer corrected charger retained material proportions perkg as explicit DC/DC ANALOGUE,not manufacturer BSC624BOM. Sensitivityboardarea0.5-2x,componentfractions andhousingresidual; increasing a component reduceshousing withinfixedmass, not normalizeallinputs. This leaves topology-specificmagnetics/semiconductor/capacitor uncertainty, so convertermetalcoefficients are not certified. Keep existingvehiclekg/duty/replacementbudgets:chargernameplateequivalent=qkg/6.2*3.3kW;converter=qkg/4.8*2.8kW. Fractionaldeviceequivalence, thermaladequacy and voltageadaptation forbus/truck remain explicit gaps; no new inferredintegerunits or fastchargerpower.400/800Vbuscompatibility is not established by this450Vdevice reference. Separate offboard fastchargers and roadinverters unchanged; railconverters unchanged. ExistingperMJadapter retains renamedcharger/converterhardware. No chassis/road added, no sourceenergydemand or primary/secondary changes; EOL remains existingvehicle treatment boundary and dedicatedcomponentEOLgap.</t>
         </is>
       </c>
     </row>
@@ -6359,7 +6367,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>converter, road auxiliary DC engineering analogue</t>
+          <t xml:space="preserve">converter production, road vehicle, auxiliary DC</t>
         </is>
       </c>
       <c r="B254">
@@ -6382,12 +6390,12 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>converter, road auxiliary DC engineering analogue</t>
+          <t xml:space="preserve">converter, road vehicle, auxiliary DC</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>converter, road auxiliary DC engineering analogue</t>
+          <t xml:space="preserve">converter, road vehicle, auxiliary DC</t>
         </is>
       </c>
     </row>
@@ -6814,7 +6822,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>bare printed circuit board, power electronics engineering reference</t>
+          <t xml:space="preserve">printed circuit board production, power electronics, bare</t>
         </is>
       </c>
       <c r="B267">
@@ -6837,12 +6845,12 @@
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>bare printed circuit board, power electronics engineering reference</t>
+          <t xml:space="preserve">printed circuit board, power electronics, bare</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t>bare printed circuit board, power electronics engineering reference</t>
+          <t xml:space="preserve">printed circuit board, power electronics, bare</t>
         </is>
       </c>
     </row>
@@ -7939,7 +7947,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>end-of-life handling, dry combustion equipment engineering reference</t>
+          <t xml:space="preserve">treatment of used combustion equipment</t>
         </is>
       </c>
     </row>
@@ -7973,7 +7981,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>end-of-life handling, dry combustion equipment engineering reference</t>
+          <t xml:space="preserve">used combustion equipment</t>
         </is>
       </c>
     </row>
@@ -8009,7 +8017,8 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>APPROVED DRY COMBUSTION ENERGY-EQUIPMENT REFERENCE, issue51, 2026-10-18. Notter et al.2010 Contribution of Li-ion batteries to the environmental impact of electric vehicles, DOI10.1021/es903729a, public SI TableS2 drivetrain detailed component rows https://pubs.acs.org/doi/suppl/10.1021/es903729a/suppl_file/es903729a_si_001.pdf ; native perkg manufacturing utilities retained only as process proxies. Sum detailed source components, not rounded275kg fuel-inclusive aggregate. Exclude42kg initialpetrol because it is delivered/consumed fuel, and18kg common12Vstarterbattery because it is a common auxiliary function also needed by other powertrains, outside agreed energy-specific boundary. Retain combustion startermotor/alternator, engine,gearbox/clutch/differential, cooling, fuelpump/tank and exhaust/catalyst. These are combustion energy functions; no chassis, body,road added. Detailed dryhardware203.2019kg; initial6kg lubricant+7kg glycol are separately purchased workingfluids, not part of dry reference output or deliveredfuel. Existing fullvehicle/perkm maintenance fluid purchases remain; this only retains initialcharge, potential initial-versus-maintenance overlap remains a sourceboundary sensitivity. All hardware sourcegrossfeeds and losses derive from eachcomponent wastefactor, including1.25machinedsteel and1.5reinforcingsteel/exhaustfactor, not a uniform0.2 multiplier. Lowalloyretained85.7/gross108.375 andreinforcingretained28/gross42 imply36.675kg totalferrousfabricationloss after excluding starterbattery, which contains noferrous. Source Al49.5retained/61.875gross/12.375scrap is preserved; no repeat of former275kgAlrepair. Source products and ordinarycastalloy retain alloy-type proxies; no AlLi or source100%secondary mandate. Genericmetalworking purchases are services and do not add anotherkg of retainedmetal. Copper2kg, rubber3kg, PPS21kg,HDPE14kg and catalystPt1.6g/Pd0.3g retained explicitly; actual steelgrades/catalystsupport and modernemissionstandard remain gaps. Fabricationmetaloffcuts go once to existingcutoffscrapsinks; plasticloss goes towasteplastic. Dedicatedendoflife helper sends the same retainedAl/Fe/Cu to cutoffscrap outlets, polymer/rubber to generictreatment, smallPGMcontent to hazardousresidue, anddrains6kg oil/7kg glycol once. These are mass-accounting collection/fateproxies, not measuredrecyclingrates or primary-secondaryshares; no recoveredmetal credit or market-for-metal substitution is claimed. Shredding0.1kWh/kgdry is an engineeringallowance; metallurgicalrecovery,pollutantfate and specificcomponenttreatment remain gaps. Do not buy nativewholeengineEOL again or disposefuel/commonstarterbattery. Keep perkg nativeassemblyenergy/factory/water as unvalidatedmanufacturingproxies; watercollectedat1000kg/m3. Rewire only passenger/hybrid vehicle buyers ofnativepassengercarICE to dedicateddryreference, preserving their suppliedkg. Their mechanicalmassparameter is interpreted as dryenergy-equipment kg: this is explicitengineeringboundaryassumption; source276.2019kgcomponentvehicle is not eachcurrentvehicle. Vehiclemass/consumption is not re-simulated; sourceyear/size/fueltechnologydifferences and mass-sizing compatibility remain sensitivitygaps. Existing dedicatedtruck/busengines and fixedBEVmechanicalreference remain. PerMJ copies regenerated fromcurrentvehicles inissue44. Numericmassbudget: {"dry_hardware_reference_kg":203.2019,"separate_initial_working_fluids_kg":13.0,"retained_material_kg":{"aluminium, cast alloy":49.5,"steel, low-alloyed, hot rolled":85.7,"polyphenylene sulfide":21.0,"reinforcing steel":28.0,"polyethylene, high density, granulate":14.0,"synthetic rubber":3.0,"copper, cathode":2.0,"platinum":0.0016,"palladium":0.0003},"gross_purchase_kg":{"aluminium, cast alloy":61.875,"steel, low-alloyed, hot rolled":108.375,"polyphenylene sulfide":23.1,"reinforcing steel":42.0,"polyethylene, high density, granulate":15.399999999999999,"synthetic rubber":3.0,"copper, cathode":2.0,"platinum":0.0016,"palladium":0.0003},"ferrous_fabrication_scrap_kg":36.675,"initial_fuel_excluded_kg":42,"common_starter_battery_excluded_kg":18}</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: end-of-life handling, dry combustion equipment engineering reference. Former reference product: end-of-life handling, dry combustion equipment engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED DRY COMBUSTION ENERGY-EQUIPMENT REFERENCE, issue51, 2026-10-18. Notter et al.2010 Contribution of Li-ion batteries to the environmental impact of electric vehicles, DOI10.1021/es903729a, public SI TableS2 drivetrain detailed component rows https://pubs.acs.org/doi/suppl/10.1021/es903729a/suppl_file/es903729a_si_001.pdf ; native perkg manufacturing utilities retained only as process proxies. Sum detailed source components, not rounded275kg fuel-inclusive aggregate. Exclude42kg initialpetrol because it is delivered/consumed fuel, and18kg common12Vstarterbattery because it is a common auxiliary function also needed by other powertrains, outside agreed energy-specific boundary. Retain combustion startermotor/alternator, engine,gearbox/clutch/differential, cooling, fuelpump/tank and exhaust/catalyst. These are combustion energy functions; no chassis, body,road added. Detailed dryhardware203.2019kg; initial6kg lubricant+7kg glycol are separately purchased workingfluids, not part of dry reference output or deliveredfuel. Existing fullvehicle/perkm maintenance fluid purchases remain; this only retains initialcharge, potential initial-versus-maintenance overlap remains a sourceboundary sensitivity. All hardware sourcegrossfeeds and losses derive from eachcomponent wastefactor, including1.25machinedsteel and1.5reinforcingsteel/exhaustfactor, not a uniform0.2 multiplier. Lowalloyretained85.7/gross108.375 andreinforcingretained28/gross42 imply36.675kg totalferrousfabricationloss after excluding starterbattery, which contains noferrous. Source Al49.5retained/61.875gross/12.375scrap is preserved; no repeat of former275kgAlrepair. Source products and ordinarycastalloy retain alloy-type proxies; no AlLi or source100%secondary mandate. Genericmetalworking purchases are services and do not add anotherkg of retainedmetal. Copper2kg, rubber3kg, PPS21kg,HDPE14kg and catalystPt1.6g/Pd0.3g retained explicitly; actual steelgrades/catalystsupport and modernemissionstandard remain gaps. Fabricationmetaloffcuts go once to existingcutoffscrapsinks; plasticloss goes towasteplastic. Dedicatedendoflife helper sends the same retainedAl/Fe/Cu to cutoffscrap outlets, polymer/rubber to generictreatment, smallPGMcontent to hazardousresidue, anddrains6kg oil/7kg glycol once. These are mass-accounting collection/fateproxies, not measuredrecyclingrates or primary-secondaryshares; no recoveredmetal credit or market-for-metal substitution is claimed. Shredding0.1kWh/kgdry is an engineeringallowance; metallurgicalrecovery,pollutantfate and specificcomponenttreatment remain gaps. Do not buy nativewholeengineEOL again or disposefuel/commonstarterbattery. Keep perkg nativeassemblyenergy/factory/water as unvalidatedmanufacturingproxies; watercollectedat1000kg/m3. Rewire only passenger/hybrid vehicle buyers ofnativepassengercarICE to dedicateddryreference, preserving their suppliedkg. Their mechanicalmassparameter is interpreted as dryenergy-equipment kg: this is explicitengineeringboundaryassumption; source276.2019kgcomponentvehicle is not eachcurrentvehicle. Vehiclemass/consumption is not re-simulated; sourceyear/size/fueltechnologydifferences and mass-sizing compatibility remain sensitivitygaps. Existing dedicatedtruck/busengines and fixedBEVmechanicalreference remain. PerMJ copies regenerated fromcurrentvehicles inissue44. Numericmassbudget: {"dry_hardware_reference_kg":203.2019,"separate_initial_working_fluids_kg":13.0,"retained_material_kg":{"aluminium, cast alloy":49.5,"steel, low-alloyed, hot rolled":85.7,"polyphenylene sulfide":21.0,"reinforcing steel":28.0,"polyethylene, high density, granulate":14.0,"synthetic rubber":3.0,"copper, cathode":2.0,"platinum":0.0016,"palladium":0.0003},"gross_purchase_kg":{"aluminium, cast alloy":61.875,"steel, low-alloyed, hot rolled":108.375,"polyphenylene sulfide":23.1,"reinforcing steel":42.0,"polyethylene, high density, granulate":15.399999999999999,"synthetic rubber":3.0,"copper, cathode":2.0,"platinum":0.0016,"palladium":0.0003},"ferrous_fabrication_scrap_kg":36.675,"initial_fuel_excluded_kg":42,"common_starter_battery_excluded_kg":18}</t>
         </is>
       </c>
     </row>
@@ -8070,7 +8079,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>end-of-life handling, dry combustion equipment engineering reference</t>
+          <t xml:space="preserve">treatment of used combustion equipment</t>
         </is>
       </c>
       <c r="B310">
@@ -8093,12 +8102,12 @@
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>end-of-life handling, dry combustion equipment engineering reference</t>
+          <t xml:space="preserve">used combustion equipment</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
         <is>
-          <t>end-of-life handling, dry combustion equipment engineering reference</t>
+          <t xml:space="preserve">used combustion equipment</t>
         </is>
       </c>
     </row>
@@ -8530,7 +8539,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>internal combustion engine, dry energy-equipment engineering reference</t>
+          <t xml:space="preserve">internal combustion engine equipment production, without working fluids</t>
         </is>
       </c>
     </row>
@@ -8564,7 +8573,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>internal combustion engine, dry energy-equipment engineering reference</t>
+          <t xml:space="preserve">internal combustion engine equipment, without working fluids</t>
         </is>
       </c>
     </row>
@@ -8600,7 +8609,8 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>APPROVED DRY COMBUSTION ENERGY-EQUIPMENT REFERENCE, issue51, 2026-10-18. Notter et al.2010 Contribution of Li-ion batteries to the environmental impact of electric vehicles, DOI10.1021/es903729a, public SI TableS2 drivetrain detailed component rows https://pubs.acs.org/doi/suppl/10.1021/es903729a/suppl_file/es903729a_si_001.pdf ; native perkg manufacturing utilities retained only as process proxies. Sum detailed source components, not rounded275kg fuel-inclusive aggregate. Exclude42kg initialpetrol because it is delivered/consumed fuel, and18kg common12Vstarterbattery because it is a common auxiliary function also needed by other powertrains, outside agreed energy-specific boundary. Retain combustion startermotor/alternator, engine,gearbox/clutch/differential, cooling, fuelpump/tank and exhaust/catalyst. These are combustion energy functions; no chassis, body,road added. Detailed dryhardware203.2019kg; initial6kg lubricant+7kg glycol are separately purchased workingfluids, not part of dry reference output or deliveredfuel. Existing fullvehicle/perkm maintenance fluid purchases remain; this only retains initialcharge, potential initial-versus-maintenance overlap remains a sourceboundary sensitivity. All hardware sourcegrossfeeds and losses derive from eachcomponent wastefactor, including1.25machinedsteel and1.5reinforcingsteel/exhaustfactor, not a uniform0.2 multiplier. Lowalloyretained85.7/gross108.375 andreinforcingretained28/gross42 imply36.675kg totalferrousfabricationloss after excluding starterbattery, which contains noferrous. Source Al49.5retained/61.875gross/12.375scrap is preserved; no repeat of former275kgAlrepair. Source products and ordinarycastalloy retain alloy-type proxies; no AlLi or source100%secondary mandate. Genericmetalworking purchases are services and do not add anotherkg of retainedmetal. Copper2kg, rubber3kg, PPS21kg,HDPE14kg and catalystPt1.6g/Pd0.3g retained explicitly; actual steelgrades/catalystsupport and modernemissionstandard remain gaps. Fabricationmetaloffcuts go once to existingcutoffscrapsinks; plasticloss goes towasteplastic. Dedicatedendoflife helper sends the same retainedAl/Fe/Cu to cutoffscrap outlets, polymer/rubber to generictreatment, smallPGMcontent to hazardousresidue, anddrains6kg oil/7kg glycol once. These are mass-accounting collection/fateproxies, not measuredrecyclingrates or primary-secondaryshares; no recoveredmetal credit or market-for-metal substitution is claimed. Shredding0.1kWh/kgdry is an engineeringallowance; metallurgicalrecovery,pollutantfate and specificcomponenttreatment remain gaps. Do not buy nativewholeengineEOL again or disposefuel/commonstarterbattery. Keep perkg nativeassemblyenergy/factory/water as unvalidatedmanufacturingproxies; watercollectedat1000kg/m3. Rewire only passenger/hybrid vehicle buyers ofnativepassengercarICE to dedicateddryreference, preserving their suppliedkg. Their mechanicalmassparameter is interpreted as dryenergy-equipment kg: this is explicitengineeringboundaryassumption; source276.2019kgcomponentvehicle is not eachcurrentvehicle. Vehiclemass/consumption is not re-simulated; sourceyear/size/fueltechnologydifferences and mass-sizing compatibility remain sensitivitygaps. Existing dedicatedtruck/busengines and fixedBEVmechanicalreference remain. PerMJ copies regenerated fromcurrentvehicles inissue44. Numericmassbudget: {"dry_hardware_reference_kg":203.2019,"separate_initial_working_fluids_kg":13.0,"retained_material_kg":{"aluminium, cast alloy":49.5,"steel, low-alloyed, hot rolled":85.7,"polyphenylene sulfide":21.0,"reinforcing steel":28.0,"polyethylene, high density, granulate":14.0,"synthetic rubber":3.0,"copper, cathode":2.0,"platinum":0.0016,"palladium":0.0003},"gross_purchase_kg":{"aluminium, cast alloy":61.875,"steel, low-alloyed, hot rolled":108.375,"polyphenylene sulfide":23.1,"reinforcing steel":42.0,"polyethylene, high density, granulate":15.399999999999999,"synthetic rubber":3.0,"copper, cathode":2.0,"platinum":0.0016,"palladium":0.0003},"ferrous_fabrication_scrap_kg":36.675,"initial_fuel_excluded_kg":42,"common_starter_battery_excluded_kg":18}</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: internal combustion engine, dry energy-equipment engineering reference. Former reference product: internal combustion engine, dry energy-equipment engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED DRY COMBUSTION ENERGY-EQUIPMENT REFERENCE, issue51, 2026-10-18. Notter et al.2010 Contribution of Li-ion batteries to the environmental impact of electric vehicles, DOI10.1021/es903729a, public SI TableS2 drivetrain detailed component rows https://pubs.acs.org/doi/suppl/10.1021/es903729a/suppl_file/es903729a_si_001.pdf ; native perkg manufacturing utilities retained only as process proxies. Sum detailed source components, not rounded275kg fuel-inclusive aggregate. Exclude42kg initialpetrol because it is delivered/consumed fuel, and18kg common12Vstarterbattery because it is a common auxiliary function also needed by other powertrains, outside agreed energy-specific boundary. Retain combustion startermotor/alternator, engine,gearbox/clutch/differential, cooling, fuelpump/tank and exhaust/catalyst. These are combustion energy functions; no chassis, body,road added. Detailed dryhardware203.2019kg; initial6kg lubricant+7kg glycol are separately purchased workingfluids, not part of dry reference output or deliveredfuel. Existing fullvehicle/perkm maintenance fluid purchases remain; this only retains initialcharge, potential initial-versus-maintenance overlap remains a sourceboundary sensitivity. All hardware sourcegrossfeeds and losses derive from eachcomponent wastefactor, including1.25machinedsteel and1.5reinforcingsteel/exhaustfactor, not a uniform0.2 multiplier. Lowalloyretained85.7/gross108.375 andreinforcingretained28/gross42 imply36.675kg totalferrousfabricationloss after excluding starterbattery, which contains noferrous. Source Al49.5retained/61.875gross/12.375scrap is preserved; no repeat of former275kgAlrepair. Source products and ordinarycastalloy retain alloy-type proxies; no AlLi or source100%secondary mandate. Genericmetalworking purchases are services and do not add anotherkg of retainedmetal. Copper2kg, rubber3kg, PPS21kg,HDPE14kg and catalystPt1.6g/Pd0.3g retained explicitly; actual steelgrades/catalystsupport and modernemissionstandard remain gaps. Fabricationmetaloffcuts go once to existingcutoffscrapsinks; plasticloss goes towasteplastic. Dedicatedendoflife helper sends the same retainedAl/Fe/Cu to cutoffscrap outlets, polymer/rubber to generictreatment, smallPGMcontent to hazardousresidue, anddrains6kg oil/7kg glycol once. These are mass-accounting collection/fateproxies, not measuredrecyclingrates or primary-secondaryshares; no recoveredmetal credit or market-for-metal substitution is claimed. Shredding0.1kWh/kgdry is an engineeringallowance; metallurgicalrecovery,pollutantfate and specificcomponenttreatment remain gaps. Do not buy nativewholeengineEOL again or disposefuel/commonstarterbattery. Keep perkg nativeassemblyenergy/factory/water as unvalidatedmanufacturingproxies; watercollectedat1000kg/m3. Rewire only passenger/hybrid vehicle buyers ofnativepassengercarICE to dedicateddryreference, preserving their suppliedkg. Their mechanicalmassparameter is interpreted as dryenergy-equipment kg: this is explicitengineeringboundaryassumption; source276.2019kgcomponentvehicle is not eachcurrentvehicle. Vehiclemass/consumption is not re-simulated; sourceyear/size/fueltechnologydifferences and mass-sizing compatibility remain sensitivitygaps. Existing dedicatedtruck/busengines and fixedBEVmechanicalreference remain. PerMJ copies regenerated fromcurrentvehicles inissue44. Numericmassbudget: {"dry_hardware_reference_kg":203.2019,"separate_initial_working_fluids_kg":13.0,"retained_material_kg":{"aluminium, cast alloy":49.5,"steel, low-alloyed, hot rolled":85.7,"polyphenylene sulfide":21.0,"reinforcing steel":28.0,"polyethylene, high density, granulate":14.0,"synthetic rubber":3.0,"copper, cathode":2.0,"platinum":0.0016,"palladium":0.0003},"gross_purchase_kg":{"aluminium, cast alloy":61.875,"steel, low-alloyed, hot rolled":108.375,"polyphenylene sulfide":23.1,"reinforcing steel":42.0,"polyethylene, high density, granulate":15.399999999999999,"synthetic rubber":3.0,"copper, cathode":2.0,"platinum":0.0016,"palladium":0.0003},"ferrous_fabrication_scrap_kg":36.675,"initial_fuel_excluded_kg":42,"common_starter_battery_excluded_kg":18}</t>
         </is>
       </c>
     </row>
@@ -8661,7 +8671,7 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>internal combustion engine, dry energy-equipment engineering reference</t>
+          <t xml:space="preserve">internal combustion engine equipment production, without working fluids</t>
         </is>
       </c>
       <c r="B334">
@@ -8684,12 +8694,12 @@
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>internal combustion engine, dry energy-equipment engineering reference</t>
+          <t xml:space="preserve">internal combustion engine equipment, without working fluids</t>
         </is>
       </c>
       <c r="I334" t="inlineStr">
         <is>
-          <t>internal combustion engine, dry energy-equipment engineering reference</t>
+          <t xml:space="preserve">internal combustion engine equipment, without working fluids</t>
         </is>
       </c>
     </row>
@@ -9361,7 +9371,7 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>end-of-life handling, dry combustion equipment engineering reference</t>
+          <t xml:space="preserve">treatment of used combustion equipment</t>
         </is>
       </c>
       <c r="B354">
@@ -9384,12 +9394,12 @@
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>end-of-life handling, dry combustion equipment engineering reference</t>
+          <t xml:space="preserve">used combustion equipment</t>
         </is>
       </c>
       <c r="I354" t="inlineStr">
         <is>
-          <t>end-of-life handling, dry combustion equipment engineering reference</t>
+          <t xml:space="preserve">used combustion equipment</t>
         </is>
       </c>
     </row>
@@ -9611,7 +9621,7 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>converter, heavy-duty auxiliary 400V to24V, engineering reference</t>
+          <t xml:space="preserve">converter production, heavy-duty vehicle, auxiliary DC, 400 V to 24 V</t>
         </is>
       </c>
     </row>
@@ -9645,7 +9655,7 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>converter, heavy-duty auxiliary 400V to24V, engineering reference</t>
+          <t xml:space="preserve">converter, heavy-duty vehicle, auxiliary DC, 400 V to 24 V</t>
         </is>
       </c>
     </row>
@@ -9681,7 +9691,8 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>APPROVED HEAVY-DUTY AUXILIARY DC/DC REFERENCE, issue62, 2026-10-18. Bel Power Solutions2025 datasheets https://www.belfuse.com/resources/datasheets/powersolutions/ds-BPS-700DNG40-24-series.pdf and https://www.belfuse.com/media/datasheets/products/power-supplies/ds-BPS-350DNG40-24-8.pdf :4kW,4.5kg,28Vnominal/20-30Voutput,143A,450-900V or240-450Vinput,up to8parallel,liquidcooling10L/min minimum50/50glycolwater,94%ratedpoint/95%maximum efficiency. Replace bus/truck car-derived220-450V14V BSC624 analogue by nominal24V HDVauxiliaryconverter; source350 or700V variants chosen for declared400Vsmalltruck /800VlargeHDV engineeringarchitecture;635VPULSEbus also fits450-900V. Sourcevehicle actualvoltage/SOCwindow is not documented,so these adoptedwindows are explicit assumptions,not certifiedcompatibility. Use400Vvariant for3.5/7.5t truckclasses;800V forlargertrucks andbuses except635VFCEVbus. LV28Vsetpoint is withincommon24Vchargingfunction; auxiliary24Vloads/battery notaddedtwice. Infer requiredcontinuouspower from priorallowance qkg/4.8*2.8kW,selectceil(required/4) integerunits&lt;=8,oneinstalledset; thispreserves impliedminimumauxpower whilemakingcountphysical,not measuredvehicledemand.4.5kgdryperunit,newtotalmassreplacesold25kgbusallowance with18kg/16kW. A different inferredload orredundancyduty requiresresizing. ManufacturerdoesnotpublishBOM:explicit4.5kgengineeringreferenceAlhousing/baseplate2.1,Cu0.65,ferrite0.55,auxiliaryinterfaceboard0.7,filmcapacitor0.15,steel0.15,PA0.1,silicone0.05,powertransistorpackage0.05kg. Sourceouterdimensions284x55x348mm andAlalloyhousing;2mmclosed-shell estimate1.44366kg,additional0.65634kgbaseplate/fins is anassumption. Interfaceboard includeslowpowerregulation/logiconly,powertransistors andbulkfilmcapacitors are separate,notsecondcompleteconverter. Genericbigwiredtransistor is an explicit power-device manufacturingproxy; actual Si/SiC/MOSFET topologyandsemiconductorpreciousmetalsremainunverified,not silentlyreplaced bylowpowerTIregulator. No manufacturercomponentdeclarationclaim.100%retainedassemblyreference,4.5kWhassemblyandgenericmetalworking; sensitivityboard/magnetics0.5-2xwithfixedmassboundary. Sharedvehiclecoolantloop retained,no secondpumporfluidcharge;10L/min isflow notconsumedfluidvolume. Do not addnewoperatinglosses on top ofexistingvehicleenergy budget; source94%isnotfullvehicleefficiency. Onevehiclelifeassumption needsactualconverterlife. Updateproductionassemblymass only; roadenergydemand/curbperformance notresimulated. Cars,railconverters,tractioninverters andAC/DCchargersunchanged. Endoflife remainsvehicleboundary,device-specificfate gap. Refresh affectedperMJ coefficients and supplierprovenance.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: converter, heavy-duty auxiliary 400V to24V, engineering reference. Former reference product: converter, heavy-duty auxiliary 400V to24V, engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED HEAVY-DUTY AUXILIARY DC/DC REFERENCE, issue62, 2026-10-18. Bel Power Solutions2025 datasheets https://www.belfuse.com/resources/datasheets/powersolutions/ds-BPS-700DNG40-24-series.pdf and https://www.belfuse.com/media/datasheets/products/power-supplies/ds-BPS-350DNG40-24-8.pdf :4kW,4.5kg,28Vnominal/20-30Voutput,143A,450-900V or240-450Vinput,up to8parallel,liquidcooling10L/min minimum50/50glycolwater,94%ratedpoint/95%maximum efficiency. Replace bus/truck car-derived220-450V14V BSC624 analogue by nominal24V HDVauxiliaryconverter; source350 or700V variants chosen for declared400Vsmalltruck /800VlargeHDV engineeringarchitecture;635VPULSEbus also fits450-900V. Sourcevehicle actualvoltage/SOCwindow is not documented,so these adoptedwindows are explicit assumptions,not certifiedcompatibility. Use400Vvariant for3.5/7.5t truckclasses;800V forlargertrucks andbuses except635VFCEVbus. LV28Vsetpoint is withincommon24Vchargingfunction; auxiliary24Vloads/battery notaddedtwice. Infer requiredcontinuouspower from priorallowance qkg/4.8*2.8kW,selectceil(required/4) integerunits&lt;=8,oneinstalledset; thispreserves impliedminimumauxpower whilemakingcountphysical,not measuredvehicledemand.4.5kgdryperunit,newtotalmassreplacesold25kgbusallowance with18kg/16kW. A different inferredload orredundancyduty requiresresizing. ManufacturerdoesnotpublishBOM:explicit4.5kgengineeringreferenceAlhousing/baseplate2.1,Cu0.65,ferrite0.55,auxiliaryinterfaceboard0.7,filmcapacitor0.15,steel0.15,PA0.1,silicone0.05,powertransistorpackage0.05kg. Sourceouterdimensions284x55x348mm andAlalloyhousing;2mmclosed-shell estimate1.44366kg,additional0.65634kgbaseplate/fins is anassumption. Interfaceboard includeslowpowerregulation/logiconly,powertransistors andbulkfilmcapacitors are separate,notsecondcompleteconverter. Genericbigwiredtransistor is an explicit power-device manufacturingproxy; actual Si/SiC/MOSFET topologyandsemiconductorpreciousmetalsremainunverified,not silentlyreplaced bylowpowerTIregulator. No manufacturercomponentdeclarationclaim.100%retainedassemblyreference,4.5kWhassemblyandgenericmetalworking; sensitivityboard/magnetics0.5-2xwithfixedmassboundary. Sharedvehiclecoolantloop retained,no secondpumporfluidcharge;10L/min isflow notconsumedfluidvolume. Do not addnewoperatinglosses on top ofexistingvehicleenergy budget; source94%isnotfullvehicleefficiency. Onevehiclelifeassumption needsactualconverterlife. Updateproductionassemblymass only; roadenergydemand/curbperformance notresimulated. Cars,railconverters,tractioninverters andAC/DCchargersunchanged. Endoflife remainsvehicleboundary,device-specificfate gap. Refresh affectedperMJ coefficients and supplierprovenance.</t>
         </is>
       </c>
     </row>
@@ -9742,7 +9753,7 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>converter, heavy-duty auxiliary 400V to24V, engineering reference</t>
+          <t xml:space="preserve">converter production, heavy-duty vehicle, auxiliary DC, 400 V to 24 V</t>
         </is>
       </c>
       <c r="B372">
@@ -9765,12 +9776,12 @@
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>converter, heavy-duty auxiliary 400V to24V, engineering reference</t>
+          <t xml:space="preserve">converter, heavy-duty vehicle, auxiliary DC, 400 V to 24 V</t>
         </is>
       </c>
       <c r="I372" t="inlineStr">
         <is>
-          <t>converter, heavy-duty auxiliary 400V to24V, engineering reference</t>
+          <t xml:space="preserve">converter, heavy-duty vehicle, auxiliary DC, 400 V to 24 V</t>
         </is>
       </c>
     </row>
@@ -9882,7 +9893,7 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>battery auxiliary interface and power conditioning, engineering reference</t>
+          <t xml:space="preserve">battery auxiliary interface and power conditioning unit production</t>
         </is>
       </c>
       <c r="B376">
@@ -9905,12 +9916,12 @@
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>battery auxiliary interface and power conditioning, engineering reference</t>
+          <t xml:space="preserve">battery auxiliary interface and power conditioning unit</t>
         </is>
       </c>
       <c r="I376" t="inlineStr">
         <is>
-          <t>battery auxiliary interface and power conditioning, engineering reference</t>
+          <t xml:space="preserve">battery auxiliary interface and power conditioning unit</t>
         </is>
       </c>
     </row>
@@ -10202,7 +10213,7 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>converter, heavy-duty auxiliary 800V to24V, engineering reference</t>
+          <t xml:space="preserve">converter production, heavy-duty vehicle, auxiliary DC, 800 V to 24 V</t>
         </is>
       </c>
     </row>
@@ -10236,7 +10247,7 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>converter, heavy-duty auxiliary 800V to24V, engineering reference</t>
+          <t xml:space="preserve">converter, heavy-duty vehicle, auxiliary DC, 800 V to 24 V</t>
         </is>
       </c>
     </row>
@@ -10272,7 +10283,8 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>APPROVED HEAVY-DUTY AUXILIARY DC/DC REFERENCE, issue62, 2026-10-18. Bel Power Solutions2025 datasheets https://www.belfuse.com/resources/datasheets/powersolutions/ds-BPS-700DNG40-24-series.pdf and https://www.belfuse.com/media/datasheets/products/power-supplies/ds-BPS-350DNG40-24-8.pdf :4kW,4.5kg,28Vnominal/20-30Voutput,143A,450-900V or240-450Vinput,up to8parallel,liquidcooling10L/min minimum50/50glycolwater,94%ratedpoint/95%maximum efficiency. Replace bus/truck car-derived220-450V14V BSC624 analogue by nominal24V HDVauxiliaryconverter; source350 or700V variants chosen for declared400Vsmalltruck /800VlargeHDV engineeringarchitecture;635VPULSEbus also fits450-900V. Sourcevehicle actualvoltage/SOCwindow is not documented,so these adoptedwindows are explicit assumptions,not certifiedcompatibility. Use400Vvariant for3.5/7.5t truckclasses;800V forlargertrucks andbuses except635VFCEVbus. LV28Vsetpoint is withincommon24Vchargingfunction; auxiliary24Vloads/battery notaddedtwice. Infer requiredcontinuouspower from priorallowance qkg/4.8*2.8kW,selectceil(required/4) integerunits&lt;=8,oneinstalledset; thispreserves impliedminimumauxpower whilemakingcountphysical,not measuredvehicledemand.4.5kgdryperunit,newtotalmassreplacesold25kgbusallowance with18kg/16kW. A different inferredload orredundancyduty requiresresizing. ManufacturerdoesnotpublishBOM:explicit4.5kgengineeringreferenceAlhousing/baseplate2.1,Cu0.65,ferrite0.55,auxiliaryinterfaceboard0.7,filmcapacitor0.15,steel0.15,PA0.1,silicone0.05,powertransistorpackage0.05kg. Sourceouterdimensions284x55x348mm andAlalloyhousing;2mmclosed-shell estimate1.44366kg,additional0.65634kgbaseplate/fins is anassumption. Interfaceboard includeslowpowerregulation/logiconly,powertransistors andbulkfilmcapacitors are separate,notsecondcompleteconverter. Genericbigwiredtransistor is an explicit power-device manufacturingproxy; actual Si/SiC/MOSFET topologyandsemiconductorpreciousmetalsremainunverified,not silentlyreplaced bylowpowerTIregulator. No manufacturercomponentdeclarationclaim.100%retainedassemblyreference,4.5kWhassemblyandgenericmetalworking; sensitivityboard/magnetics0.5-2xwithfixedmassboundary. Sharedvehiclecoolantloop retained,no secondpumporfluidcharge;10L/min isflow notconsumedfluidvolume. Do not addnewoperatinglosses on top ofexistingvehicleenergy budget; source94%isnotfullvehicleefficiency. Onevehiclelifeassumption needsactualconverterlife. Updateproductionassemblymass only; roadenergydemand/curbperformance notresimulated. Cars,railconverters,tractioninverters andAC/DCchargersunchanged. Endoflife remainsvehicleboundary,device-specificfate gap. Refresh affectedperMJ coefficients and supplierprovenance.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: converter, heavy-duty auxiliary 800V to24V, engineering reference. Former reference product: converter, heavy-duty auxiliary 800V to24V, engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED HEAVY-DUTY AUXILIARY DC/DC REFERENCE, issue62, 2026-10-18. Bel Power Solutions2025 datasheets https://www.belfuse.com/resources/datasheets/powersolutions/ds-BPS-700DNG40-24-series.pdf and https://www.belfuse.com/media/datasheets/products/power-supplies/ds-BPS-350DNG40-24-8.pdf :4kW,4.5kg,28Vnominal/20-30Voutput,143A,450-900V or240-450Vinput,up to8parallel,liquidcooling10L/min minimum50/50glycolwater,94%ratedpoint/95%maximum efficiency. Replace bus/truck car-derived220-450V14V BSC624 analogue by nominal24V HDVauxiliaryconverter; source350 or700V variants chosen for declared400Vsmalltruck /800VlargeHDV engineeringarchitecture;635VPULSEbus also fits450-900V. Sourcevehicle actualvoltage/SOCwindow is not documented,so these adoptedwindows are explicit assumptions,not certifiedcompatibility. Use400Vvariant for3.5/7.5t truckclasses;800V forlargertrucks andbuses except635VFCEVbus. LV28Vsetpoint is withincommon24Vchargingfunction; auxiliary24Vloads/battery notaddedtwice. Infer requiredcontinuouspower from priorallowance qkg/4.8*2.8kW,selectceil(required/4) integerunits&lt;=8,oneinstalledset; thispreserves impliedminimumauxpower whilemakingcountphysical,not measuredvehicledemand.4.5kgdryperunit,newtotalmassreplacesold25kgbusallowance with18kg/16kW. A different inferredload orredundancyduty requiresresizing. ManufacturerdoesnotpublishBOM:explicit4.5kgengineeringreferenceAlhousing/baseplate2.1,Cu0.65,ferrite0.55,auxiliaryinterfaceboard0.7,filmcapacitor0.15,steel0.15,PA0.1,silicone0.05,powertransistorpackage0.05kg. Sourceouterdimensions284x55x348mm andAlalloyhousing;2mmclosed-shell estimate1.44366kg,additional0.65634kgbaseplate/fins is anassumption. Interfaceboard includeslowpowerregulation/logiconly,powertransistors andbulkfilmcapacitors are separate,notsecondcompleteconverter. Genericbigwiredtransistor is an explicit power-device manufacturingproxy; actual Si/SiC/MOSFET topologyandsemiconductorpreciousmetalsremainunverified,not silentlyreplaced bylowpowerTIregulator. No manufacturercomponentdeclarationclaim.100%retainedassemblyreference,4.5kWhassemblyandgenericmetalworking; sensitivityboard/magnetics0.5-2xwithfixedmassboundary. Sharedvehiclecoolantloop retained,no secondpumporfluidcharge;10L/min isflow notconsumedfluidvolume. Do not addnewoperatinglosses on top ofexistingvehicleenergy budget; source94%isnotfullvehicleefficiency. Onevehiclelifeassumption needsactualconverterlife. Updateproductionassemblymass only; roadenergydemand/curbperformance notresimulated. Cars,railconverters,tractioninverters andAC/DCchargersunchanged. Endoflife remainsvehicleboundary,device-specificfate gap. Refresh affectedperMJ coefficients and supplierprovenance.</t>
         </is>
       </c>
     </row>
@@ -10333,7 +10345,7 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>converter, heavy-duty auxiliary 800V to24V, engineering reference</t>
+          <t xml:space="preserve">converter production, heavy-duty vehicle, auxiliary DC, 800 V to 24 V</t>
         </is>
       </c>
       <c r="B396">
@@ -10356,12 +10368,12 @@
       </c>
       <c r="G396" t="inlineStr">
         <is>
-          <t>converter, heavy-duty auxiliary 800V to24V, engineering reference</t>
+          <t xml:space="preserve">converter, heavy-duty vehicle, auxiliary DC, 800 V to 24 V</t>
         </is>
       </c>
       <c r="I396" t="inlineStr">
         <is>
-          <t>converter, heavy-duty auxiliary 800V to24V, engineering reference</t>
+          <t xml:space="preserve">converter, heavy-duty vehicle, auxiliary DC, 800 V to 24 V</t>
         </is>
       </c>
     </row>
@@ -10473,7 +10485,7 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>battery auxiliary interface and power conditioning, engineering reference</t>
+          <t xml:space="preserve">battery auxiliary interface and power conditioning unit production</t>
         </is>
       </c>
       <c r="B400">
@@ -10496,12 +10508,12 @@
       </c>
       <c r="G400" t="inlineStr">
         <is>
-          <t>battery auxiliary interface and power conditioning, engineering reference</t>
+          <t xml:space="preserve">battery auxiliary interface and power conditioning unit</t>
         </is>
       </c>
       <c r="I400" t="inlineStr">
         <is>
-          <t>battery auxiliary interface and power conditioning, engineering reference</t>
+          <t xml:space="preserve">battery auxiliary interface and power conditioning unit</t>
         </is>
       </c>
     </row>

--- a/premise/data/additional_inventories/lci-electric-car-mechanical-powertrain.xlsx
+++ b/premise/data/additional_inventories/lci-electric-car-mechanical-powertrain.xlsx
@@ -7981,7 +7981,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t xml:space="preserve">used combustion equipment</t>
+          <t xml:space="preserve">treatment of used combustion equipment</t>
         </is>
       </c>
     </row>
@@ -7993,7 +7993,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t xml:space="preserve">kilogram</t>
         </is>
       </c>
     </row>
@@ -8017,7 +8017,8 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: end-of-life handling, dry combustion equipment engineering reference. Former reference product: end-of-life handling, dry combustion equipment engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+          <t xml:space="preserve">APPROVED REFERENCE-UNIT CORRECTION, 2026-10-19. Current reference: Treatment associated with one kilogram of dry combustion equipment, including its attributed initial working fluids. Unit field: kilogram. Former reference: 1 unit = 1 kilogram on the current basis. All supplier/product references and direct purchasers are updated together. Recipes are divided by this conversion factor and consumer doses multiplied by it; physical inputs, emissions and waste per original functional unit are preserved. Dry equipment is the denominator; initial working fluids of 13/203.2019 kg per kg dry equipment remain additional attributed waste. No new unit vocabulary, design, lifetime, manufacturing yield, recycling credit, primary/secondary share or runtime code change. Earlier source notes below retain their historical normalization; the current reference and amounts above supersede that normalization.
+Nomenclature revision, 2026-10-19. Former activity name: end-of-life handling, dry combustion equipment engineering reference. Former reference product: end-of-life handling, dry combustion equipment engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
 APPROVED DRY COMBUSTION ENERGY-EQUIPMENT REFERENCE, issue51, 2026-10-18. Notter et al.2010 Contribution of Li-ion batteries to the environmental impact of electric vehicles, DOI10.1021/es903729a, public SI TableS2 drivetrain detailed component rows https://pubs.acs.org/doi/suppl/10.1021/es903729a/suppl_file/es903729a_si_001.pdf ; native perkg manufacturing utilities retained only as process proxies. Sum detailed source components, not rounded275kg fuel-inclusive aggregate. Exclude42kg initialpetrol because it is delivered/consumed fuel, and18kg common12Vstarterbattery because it is a common auxiliary function also needed by other powertrains, outside agreed energy-specific boundary. Retain combustion startermotor/alternator, engine,gearbox/clutch/differential, cooling, fuelpump/tank and exhaust/catalyst. These are combustion energy functions; no chassis, body,road added. Detailed dryhardware203.2019kg; initial6kg lubricant+7kg glycol are separately purchased workingfluids, not part of dry reference output or deliveredfuel. Existing fullvehicle/perkm maintenance fluid purchases remain; this only retains initialcharge, potential initial-versus-maintenance overlap remains a sourceboundary sensitivity. All hardware sourcegrossfeeds and losses derive from eachcomponent wastefactor, including1.25machinedsteel and1.5reinforcingsteel/exhaustfactor, not a uniform0.2 multiplier. Lowalloyretained85.7/gross108.375 andreinforcingretained28/gross42 imply36.675kg totalferrousfabricationloss after excluding starterbattery, which contains noferrous. Source Al49.5retained/61.875gross/12.375scrap is preserved; no repeat of former275kgAlrepair. Source products and ordinarycastalloy retain alloy-type proxies; no AlLi or source100%secondary mandate. Genericmetalworking purchases are services and do not add anotherkg of retainedmetal. Copper2kg, rubber3kg, PPS21kg,HDPE14kg and catalystPt1.6g/Pd0.3g retained explicitly; actual steelgrades/catalystsupport and modernemissionstandard remain gaps. Fabricationmetaloffcuts go once to existingcutoffscrapsinks; plasticloss goes towasteplastic. Dedicatedendoflife helper sends the same retainedAl/Fe/Cu to cutoffscrap outlets, polymer/rubber to generictreatment, smallPGMcontent to hazardousresidue, anddrains6kg oil/7kg glycol once. These are mass-accounting collection/fateproxies, not measuredrecyclingrates or primary-secondaryshares; no recoveredmetal credit or market-for-metal substitution is claimed. Shredding0.1kWh/kgdry is an engineeringallowance; metallurgicalrecovery,pollutantfate and specificcomponenttreatment remain gaps. Do not buy nativewholeengineEOL again or disposefuel/commonstarterbattery. Keep perkg nativeassemblyenergy/factory/water as unvalidatedmanufacturingproxies; watercollectedat1000kg/m3. Rewire only passenger/hybrid vehicle buyers ofnativepassengercarICE to dedicateddryreference, preserving their suppliedkg. Their mechanicalmassparameter is interpreted as dryenergy-equipment kg: this is explicitengineeringboundaryassumption; source276.2019kgcomponentvehicle is not eachcurrentvehicle. Vehiclemass/consumption is not re-simulated; sourceyear/size/fueltechnologydifferences and mass-sizing compatibility remain sensitivitygaps. Existing dedicatedtruck/busengines and fixedBEVmechanicalreference remain. PerMJ copies regenerated fromcurrentvehicles inissue44. Numericmassbudget: {"dry_hardware_reference_kg":203.2019,"separate_initial_working_fluids_kg":13.0,"retained_material_kg":{"aluminium, cast alloy":49.5,"steel, low-alloyed, hot rolled":85.7,"polyphenylene sulfide":21.0,"reinforcing steel":28.0,"polyethylene, high density, granulate":14.0,"synthetic rubber":3.0,"copper, cathode":2.0,"platinum":0.0016,"palladium":0.0003},"gross_purchase_kg":{"aluminium, cast alloy":61.875,"steel, low-alloyed, hot rolled":108.375,"polyphenylene sulfide":23.1,"reinforcing steel":42.0,"polyethylene, high density, granulate":15.399999999999999,"synthetic rubber":3.0,"copper, cathode":2.0,"platinum":0.0016,"palladium":0.0003},"ferrous_fabrication_scrap_kg":36.675,"initial_fuel_excluded_kg":42,"common_starter_battery_excluded_kg":18}</t>
         </is>
       </c>
@@ -8092,7 +8093,7 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t xml:space="preserve">kilogram</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
@@ -8102,12 +8103,12 @@
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t xml:space="preserve">used combustion equipment</t>
+          <t xml:space="preserve">treatment of used combustion equipment</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
         <is>
-          <t xml:space="preserve">used combustion equipment</t>
+          <t xml:space="preserve">treatment of used combustion equipment</t>
         </is>
       </c>
     </row>
@@ -9384,7 +9385,7 @@
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t xml:space="preserve">kilogram</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
@@ -9394,12 +9395,18 @@
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t xml:space="preserve">used combustion equipment</t>
+          <t xml:space="preserve">treatment of used combustion equipment</t>
+        </is>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t xml:space="preserve">APPROVED REFERENCE-UNIT CORRECTION, 2026-10-19. Current reference: Treatment associated with one kilogram of dry combustion equipment, including its attributed initial working fluids. Unit field: kilogram. Former reference: 1 unit = 1 kilogram on the current basis. All supplier/product references and direct purchasers are updated together. Recipes are divided by this conversion factor and consumer doses multiplied by it; physical inputs, emissions and waste per original functional unit are preserved. Dry equipment is the denominator; initial working fluids of 13/203.2019 kg per kg dry equipment remain additional attributed waste. No new unit vocabulary, design, lifetime, manufacturing yield, recycling credit, primary/secondary share or runtime code change. Earlier source notes below retain their historical normalization; the current reference and amounts above supersede that normalization.
+</t>
         </is>
       </c>
       <c r="I354" t="inlineStr">
         <is>
-          <t xml:space="preserve">used combustion equipment</t>
+          <t xml:space="preserve">treatment of used combustion equipment</t>
         </is>
       </c>
     </row>

--- a/premise/data/additional_inventories/lci-electric-car-mechanical-powertrain.xlsx
+++ b/premise/data/additional_inventories/lci-electric-car-mechanical-powertrain.xlsx
@@ -2505,7 +2505,9 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: permanent magnet, measured B3 grade, engineering reference. Former reference product: permanent magnet, measured B3 grade, engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+          <t>NEODYMIUM REDUCTION COVERAGE, 2026-10-20. Replace only the Nd2O3-equivalent feed by equal contained Nd metal from neodymium production, molten salt electrolysis. The provider has explicit oxide/electrode/fluoride/gas/waste balances and documented engineering assumptions. Existing magnet fractions,95%fabrication retention,15kWh/kg downstream fabrication,other precursors and finalEOL are unchanged. Pr/Tb/Dy/Ho and B/Ca/Ti precursor reduction,alloy/powder process specificity and coating remain separate gaps; this is not a complete industrial magnet inventory.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+Nomenclature revision, 2026-10-19. Former activity name: permanent magnet, measured B3 grade, engineering reference. Former reference product: permanent magnet, measured B3 grade, engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
 APPROVED TRACTION MAGNET GRADE REFERENCES, issue36, 2026-10-18. Jones etal2025 DOI10.1021/jacs.5c04150 SI TableS2, samplesB3 andA1; Hsieh etal2026 DOI10.1007/s11367-026-02610-7 SI TableS11 PMSM bulk components. Select one measured B3 magnet as engineering composition reference, NOT fleet average from two rotors. B3 masspercent:Nd21.9,Pr7.4,Tb0.5,Ho1.7,Co2.2,B0.9,Al0.2,Ca0.2,Fe64.8,Cu0.2 (sum100);Dy not detected, not proof absolutezero. Separate A1 sensitivity:Nd26.6,Tb0.6,Dy0.5,Ho2.2,Co2.4,B0.9,Al0.2,Ca0.1,Ti0.2,Fe66.2,Cu0.2;rounded source100.1percent, divided by100.1 to resolve rounding. Grade choice has substantialNd/Pr/Dy/Tb/Ho/Co sensitivity; unknown fleet penetration,gradeevolution and coercivity requirements remain gaps. Purchase individual oxide suppliers at stoichiometric containedmetal equivalents Nd2O3,Pr6O11,Tb4O7,Ho2O3,Dy2O3,Coasmetal,othermetals explicitly; B usesboricoxide/Causesquicklime/TiusesTiO2 as supply proxies. Oxide-to-metal reduction/reagents,oxygen/byproduct fate,boron/calciumretention and magnet coating are unresolved manufacturing gaps, not a closed full metallurgical process. Assume95percent magnet-material retention, matching5percentfinishedoffcut treatmentproxy, no recyclingcredit; yield sensitivity85-100percent and15kWh/kgmagnetprocess sensitivity5-30. Wholeoxide feed mass can exceed finishedmagnet mass due to oxygen:do not normalize elementalshares by gross feed mass. New roadmotor uses public PMSM non-magnet proportions20.3kgelectricalsteel,4.8Cu,14.6Al,3.9balance allocatedordinary steel as explicit shaft/bearingproxy. Missing source3.9kg componentbreakdown is not a measured steelrecipe. Keep existing0.03735849kgfinishedmagnet/kgmotor and all vehicle motor masses rather than resize magnetdemand to1.3/44.9kg/kg from a differentmotor. Distribute remainingmass across public non-magnet proportions; electricalsteelexisting3.2percentSi reference. Genericmetalworking+1kWh/kgassembly,100percentmotorassemblyretention. Existing motorsteel/Algrades remainproxies; efficiency/torque/voltage not revalidated. Dedicated name outside genericEVmetaloverlay deliberately fixes this source design over time; avoids aluminum overlay doublecount and Nd-onlyoverwrite. No unsupported future gradelearning; future static-vs-learning comparison remains required. Rewire direct car/truck/bus roadmotor inputs and explicit roadperMJ copies; inductionrail/tram unchanged. Existing sourcevehicle life andMJallocation retained. Native backgroundmotor and genericmagnet supplies remain unchanged for other consumers. Individualoxideproviders keep REidentities visible to containedmetal accounting; no primary/secondary claim.</t>
         </is>
       </c>
@@ -2602,15 +2604,15 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>market for neodymium oxide</t>
+          <t>neodymium production, molten salt electrolysis</t>
         </is>
       </c>
       <c r="B111">
-        <v>0.26888051074984365</v>
+        <v>0.2305263157894737</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -2625,12 +2627,17 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>neodymium oxide</t>
+          <t>neodymium</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Nd metal at exactly the former contained-Nd-equivalent dose. Reduction and fluoride/consumable preparation are supplied by the dedicated process once; do not keep the replaced oxide purchase on top. Source magnet fraction and95%fabrication retention unchanged.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>neodymium oxide</t>
+          <t>neodymium</t>
         </is>
       </c>
     </row>
@@ -3097,7 +3104,9 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: permanent magnet, measured A1 grade, engineering reference. Former reference product: permanent magnet, measured A1 grade, engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+          <t>NEODYMIUM REDUCTION COVERAGE, 2026-10-20. Replace only the Nd2O3-equivalent feed by equal contained Nd metal from neodymium production, molten salt electrolysis. The provider has explicit oxide/electrode/fluoride/gas/waste balances and documented engineering assumptions. Existing magnet fractions,95%fabrication retention,15kWh/kg downstream fabrication,other precursors and finalEOL are unchanged. Pr/Tb/Dy/Ho and B/Ca/Ti precursor reduction,alloy/powder process specificity and coating remain separate gaps; this is not a complete industrial magnet inventory.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+Nomenclature revision, 2026-10-19. Former activity name: permanent magnet, measured A1 grade, engineering reference. Former reference product: permanent magnet, measured A1 grade, engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
 APPROVED TRACTION MAGNET GRADE REFERENCES, issue36, 2026-10-18. Jones etal2025 DOI10.1021/jacs.5c04150 SI TableS2, samplesB3 andA1; Hsieh etal2026 DOI10.1007/s11367-026-02610-7 SI TableS11 PMSM bulk components. Select one measured B3 magnet as engineering composition reference, NOT fleet average from two rotors. B3 masspercent:Nd21.9,Pr7.4,Tb0.5,Ho1.7,Co2.2,B0.9,Al0.2,Ca0.2,Fe64.8,Cu0.2 (sum100);Dy not detected, not proof absolutezero. Separate A1 sensitivity:Nd26.6,Tb0.6,Dy0.5,Ho2.2,Co2.4,B0.9,Al0.2,Ca0.1,Ti0.2,Fe66.2,Cu0.2;rounded source100.1percent, divided by100.1 to resolve rounding. Grade choice has substantialNd/Pr/Dy/Tb/Ho/Co sensitivity; unknown fleet penetration,gradeevolution and coercivity requirements remain gaps. Purchase individual oxide suppliers at stoichiometric containedmetal equivalents Nd2O3,Pr6O11,Tb4O7,Ho2O3,Dy2O3,Coasmetal,othermetals explicitly; B usesboricoxide/Causesquicklime/TiusesTiO2 as supply proxies. Oxide-to-metal reduction/reagents,oxygen/byproduct fate,boron/calciumretention and magnet coating are unresolved manufacturing gaps, not a closed full metallurgical process. Assume95percent magnet-material retention, matching5percentfinishedoffcut treatmentproxy, no recyclingcredit; yield sensitivity85-100percent and15kWh/kgmagnetprocess sensitivity5-30. Wholeoxide feed mass can exceed finishedmagnet mass due to oxygen:do not normalize elementalshares by gross feed mass. New roadmotor uses public PMSM non-magnet proportions20.3kgelectricalsteel,4.8Cu,14.6Al,3.9balance allocatedordinary steel as explicit shaft/bearingproxy. Missing source3.9kg componentbreakdown is not a measured steelrecipe. Keep existing0.03735849kgfinishedmagnet/kgmotor and all vehicle motor masses rather than resize magnetdemand to1.3/44.9kg/kg from a differentmotor. Distribute remainingmass across public non-magnet proportions; electricalsteelexisting3.2percentSi reference. Genericmetalworking+1kWh/kgassembly,100percentmotorassemblyretention. Existing motorsteel/Algrades remainproxies; efficiency/torque/voltage not revalidated. Dedicated name outside genericEVmetaloverlay deliberately fixes this source design over time; avoids aluminum overlay doublecount and Nd-onlyoverwrite. No unsupported future gradelearning; future static-vs-learning comparison remains required. Rewire direct car/truck/bus roadmotor inputs and explicit roadperMJ copies; inductionrail/tram unchanged. Existing sourcevehicle life andMJallocation retained. Native backgroundmotor and genericmagnet supplies remain unchanged for other consumers. Individualoxideproviders keep REidentities visible to containedmetal accounting; no primary/secondary claim.</t>
         </is>
       </c>
@@ -3194,15 +3203,15 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>market for neodymium oxide</t>
+          <t>neodymium production, molten salt electrolysis</t>
         </is>
       </c>
       <c r="B135">
-        <v>0.32625920134412806</v>
+        <v>0.2797202797202797</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -3217,12 +3226,17 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>neodymium oxide</t>
+          <t>neodymium</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Nd metal at exactly the former contained-Nd-equivalent dose. Reduction and fluoride/consumable preparation are supplied by the dedicated process once; do not keep the replaced oxide purchase on top. Source magnet fraction and95%fabrication retention unchanged.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>neodymium oxide</t>
+          <t>neodymium</t>
         </is>
       </c>
     </row>

--- a/premise/data/additional_inventories/lci-electric-car-mechanical-powertrain.xlsx
+++ b/premise/data/additional_inventories/lci-electric-car-mechanical-powertrain.xlsx
@@ -3104,7 +3104,9 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>NEODYMIUM REDUCTION COVERAGE, 2026-10-20. Replace only the Nd2O3-equivalent feed by equal contained Nd metal from neodymium production, molten salt electrolysis. The provider has explicit oxide/electrode/fluoride/gas/waste balances and documented engineering assumptions. Existing magnet fractions,95%fabrication retention,15kWh/kg downstream fabrication,other precursors and finalEOL are unchanged. Pr/Tb/Dy/Ho and B/Ca/Ti precursor reduction,alloy/powder process specificity and coating remain separate gaps; this is not a complete industrial magnet inventory.
+          <t>TITANIUM PRECURSOR MANUFACTURE, 2026-10-20. The measured A1 grade contains0.2mass%Ti in its rounded100.1%source ledger. Existing TiO2 feed represented elemental equivalence but omitted oxide-to-metal reduction. Replace that feed by market for titanium,GLO,kilogram at TiO2kg*47.867/(47.867+2*15.999). The native market describes titanium metal made via chlorination to TiCl4 and magnesium reduction/vacuumdistillation in the Kroll process; its background manufacture includes the reduction reagents and wastes. It is a commodity-metal feed reference, not measured A1 manufacturer procurement or extra finished-magnet supply. Do not buy an additional oxide,chloride,Mg charge or aerospace triple-melting route on top. New nominal Ti feed0.00210315999789684kg/kgmagnet, leaving0.001998001998002kgTi after the existing95%magnet retention, exactly0.2/100.1. Keep all other A1 constituents,Ndreduction,15kWh/kgdownstream fabrication and finalEOL unchanged. Default B3 contains no Ti; its recipe,motor/vehicle doses and all per-MJ quantities remain unchanged. This resolves Ti reduction coverage for the A1 sensitivity only; other precursor reduction,alloy/powder/coating and actual-grade/process qualification remain open. Existing supplemental workbook only. All original user scrap-market edits remain unstaged and unchanged.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+NEODYMIUM REDUCTION COVERAGE, 2026-10-20. Replace only the Nd2O3-equivalent feed by equal contained Nd metal from neodymium production, molten salt electrolysis. The provider has explicit oxide/electrode/fluoride/gas/waste balances and documented engineering assumptions. Existing magnet fractions,95%fabrication retention,15kWh/kg downstream fabrication,other precursors and finalEOL are unchanged. Pr/Tb/Dy/Ho and B/Ca/Ti precursor reduction,alloy/powder process specificity and coating remain separate gaps; this is not a complete industrial magnet inventory.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 Nomenclature revision, 2026-10-19. Former activity name: permanent magnet, measured A1 grade, engineering reference. Former reference product: permanent magnet, measured A1 grade, engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
 APPROVED TRACTION MAGNET GRADE REFERENCES, issue36, 2026-10-18. Jones etal2025 DOI10.1021/jacs.5c04150 SI TableS2, samplesB3 andA1; Hsieh etal2026 DOI10.1007/s11367-026-02610-7 SI TableS11 PMSM bulk components. Select one measured B3 magnet as engineering composition reference, NOT fleet average from two rotors. B3 masspercent:Nd21.9,Pr7.4,Tb0.5,Ho1.7,Co2.2,B0.9,Al0.2,Ca0.2,Fe64.8,Cu0.2 (sum100);Dy not detected, not proof absolutezero. Separate A1 sensitivity:Nd26.6,Tb0.6,Dy0.5,Ho2.2,Co2.4,B0.9,Al0.2,Ca0.1,Ti0.2,Fe66.2,Cu0.2;rounded source100.1percent, divided by100.1 to resolve rounding. Grade choice has substantialNd/Pr/Dy/Tb/Ho/Co sensitivity; unknown fleet penetration,gradeevolution and coercivity requirements remain gaps. Purchase individual oxide suppliers at stoichiometric containedmetal equivalents Nd2O3,Pr6O11,Tb4O7,Ho2O3,Dy2O3,Coasmetal,othermetals explicitly; B usesboricoxide/Causesquicklime/TiusesTiO2 as supply proxies. Oxide-to-metal reduction/reagents,oxygen/byproduct fate,boron/calciumretention and magnet coating are unresolved manufacturing gaps, not a closed full metallurgical process. Assume95percent magnet-material retention, matching5percentfinishedoffcut treatmentproxy, no recyclingcredit; yield sensitivity85-100percent and15kWh/kgmagnetprocess sensitivity5-30. Wholeoxide feed mass can exceed finishedmagnet mass due to oxygen:do not normalize elementalshares by gross feed mass. New roadmotor uses public PMSM non-magnet proportions20.3kgelectricalsteel,4.8Cu,14.6Al,3.9balance allocatedordinary steel as explicit shaft/bearingproxy. Missing source3.9kg componentbreakdown is not a measured steelrecipe. Keep existing0.03735849kgfinishedmagnet/kgmotor and all vehicle motor masses rather than resize magnetdemand to1.3/44.9kg/kg from a differentmotor. Distribute remainingmass across public non-magnet proportions; electricalsteelexisting3.2percentSi reference. Genericmetalworking+1kWh/kgassembly,100percentmotorassemblyretention. Existing motorsteel/Algrades remainproxies; efficiency/torque/voltage not revalidated. Dedicated name outside genericEVmetaloverlay deliberately fixes this source design over time; avoids aluminum overlay doublecount and Nd-onlyoverwrite. No unsupported future gradelearning; future static-vs-learning comparison remains required. Rewire direct car/truck/bus roadmotor inputs and explicit roadperMJ copies; inductionrail/tram unchanged. Existing sourcevehicle life andMJallocation retained. Native backgroundmotor and genericmagnet supplies remain unchanged for other consumers. Individualoxideproviders keep REidentities visible to containedmetal accounting; no primary/secondary claim.</t>
@@ -3488,15 +3490,15 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>market for titanium dioxide</t>
+          <t>market for titanium</t>
         </is>
       </c>
       <c r="B143">
-        <v>0.0035090745865007443</v>
+        <v>0.00210315999789684</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>RER</t>
+          <t>GLO</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -3511,12 +3513,17 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>titanium dioxide</t>
+          <t>titanium</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Nominal titanium metal at the former TiO2 contained-Ti-equivalent dose. The native market includes Kroll reduction via TiCl4/Mg; no duplicate oxide or triple-melting purchase. Retained0.2/100.1massfraction and95%magnet fabrication retention are unchanged.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>titanium dioxide</t>
+          <t>titanium</t>
         </is>
       </c>
     </row>

--- a/premise/data/additional_inventories/lci-electric-car-mechanical-powertrain.xlsx
+++ b/premise/data/additional_inventories/lci-electric-car-mechanical-powertrain.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I408"/>
+  <dimension ref="A1:I429"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2505,7 +2505,9 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>NEODYMIUM REDUCTION COVERAGE, 2026-10-20. Replace only the Nd2O3-equivalent feed by equal contained Nd metal from neodymium production, molten salt electrolysis. The provider has explicit oxide/electrode/fluoride/gas/waste balances and documented engineering assumptions. Existing magnet fractions,95%fabrication retention,15kWh/kg downstream fabrication,other precursors and finalEOL are unchanged. Pr/Tb/Dy/Ho and B/Ca/Ti precursor reduction,alloy/powder process specificity and coating remain separate gaps; this is not a complete industrial magnet inventory.
+          <t>FERROBORON COVERAGE, 2026-10-20. Replace unreduced boric oxide by ferroboron production, carbothermic reduction, 19.6% boron at equal contained-B dose; deduct its iron from the separate Fe-equivalent steel. Nominal retained B/Fe fractions,95%fabrication retention,all other constituents, 15kWh/kg downstream fabrication and finalEOL remain unchanged. The dedicated provider documents source transfers, element/mass closure and remaining industrial qualification. Native steel is still an Fe-equivalent proxy,not an actual purity certificate. Active indicators are unchanged; neither the old boric oxide nor the new ferroboron is covered by the current B definition. Retain the already-added Ndreduction and A1titanium metal. Other rare-earth/Ca reduction and magnet powder, alloy-process specificity and coating remain open.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+NEODYMIUM REDUCTION COVERAGE, 2026-10-20. Replace only the Nd2O3-equivalent feed by equal contained Nd metal from neodymium production, molten salt electrolysis. The provider has explicit oxide/electrode/fluoride/gas/waste balances and documented engineering assumptions. Existing magnet fractions,95%fabrication retention,15kWh/kg downstream fabrication,other precursors and finalEOL are unchanged. Pr/Tb/Dy/Ho and B/Ca/Ti precursor reduction,alloy/powder process specificity and coating remain separate gaps; this is not a complete industrial magnet inventory.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 Nomenclature revision, 2026-10-19. Former activity name: permanent magnet, measured B3 grade, engineering reference. Former reference product: permanent magnet, measured B3 grade, engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
 APPROVED TRACTION MAGNET GRADE REFERENCES, issue36, 2026-10-18. Jones etal2025 DOI10.1021/jacs.5c04150 SI TableS2, samplesB3 andA1; Hsieh etal2026 DOI10.1007/s11367-026-02610-7 SI TableS11 PMSM bulk components. Select one measured B3 magnet as engineering composition reference, NOT fleet average from two rotors. B3 masspercent:Nd21.9,Pr7.4,Tb0.5,Ho1.7,Co2.2,B0.9,Al0.2,Ca0.2,Fe64.8,Cu0.2 (sum100);Dy not detected, not proof absolutezero. Separate A1 sensitivity:Nd26.6,Tb0.6,Dy0.5,Ho2.2,Co2.4,B0.9,Al0.2,Ca0.1,Ti0.2,Fe66.2,Cu0.2;rounded source100.1percent, divided by100.1 to resolve rounding. Grade choice has substantialNd/Pr/Dy/Tb/Ho/Co sensitivity; unknown fleet penetration,gradeevolution and coercivity requirements remain gaps. Purchase individual oxide suppliers at stoichiometric containedmetal equivalents Nd2O3,Pr6O11,Tb4O7,Ho2O3,Dy2O3,Coasmetal,othermetals explicitly; B usesboricoxide/Causesquicklime/TiusesTiO2 as supply proxies. Oxide-to-metal reduction/reagents,oxygen/byproduct fate,boron/calciumretention and magnet coating are unresolved manufacturing gaps, not a closed full metallurgical process. Assume95percent magnet-material retention, matching5percentfinishedoffcut treatmentproxy, no recyclingcredit; yield sensitivity85-100percent and15kWh/kgmagnetprocess sensitivity5-30. Wholeoxide feed mass can exceed finishedmagnet mass due to oxygen:do not normalize elementalshares by gross feed mass. New roadmotor uses public PMSM non-magnet proportions20.3kgelectricalsteel,4.8Cu,14.6Al,3.9balance allocatedordinary steel as explicit shaft/bearingproxy. Missing source3.9kg componentbreakdown is not a measured steelrecipe. Keep existing0.03735849kgfinishedmagnet/kgmotor and all vehicle motor masses rather than resize magnetdemand to1.3/44.9kg/kg from a differentmotor. Distribute remainingmass across public non-magnet proportions; electricalsteelexisting3.2percentSi reference. Genericmetalworking+1kWh/kgassembly,100percentmotorassemblyretention. Existing motorsteel/Algrades remainproxies; efficiency/torque/voltage not revalidated. Dedicated name outside genericEVmetaloverlay deliberately fixes this source design over time; avoids aluminum overlay doublecount and Nd-onlyoverwrite. No unsupported future gradelearning; future static-vs-learning comparison remains required. Rewire direct car/truck/bus roadmotor inputs and explicit roadperMJ copies; inductionrail/tram unchanged. Existing sourcevehicle life andMJallocation retained. Native backgroundmotor and genericmagnet supplies remain unchanged for other consumers. Individualoxideproviders keep REidentities visible to containedmetal accounting; no primary/secondary claim.</t>
@@ -2784,11 +2786,11 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>market for boric oxide</t>
+          <t>ferroboron production, carbothermic reduction, 19.6% boron</t>
         </is>
       </c>
       <c r="B116">
-        <v>0.030505526072350162</v>
+        <v>0.04833512352309345</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -2807,12 +2809,17 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>boric oxide</t>
+          <t>ferroboron, 19.6% boron</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Manufactured ferroboron supplies the former contained-B dose. Its accompanying80.4%Fe is deducted from the separate steel input; B/Fe fractions and95%magnet retention unchanged.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>boric oxide</t>
+          <t>ferroboron, 19.6% boron</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2900,7 @@
         </is>
       </c>
       <c r="B119">
-        <v>0.6821052631578948</v>
+        <v>0.6432438238453276</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -2913,6 +2920,11 @@
       <c r="G119" t="inlineStr">
         <is>
           <t>steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Remaining nominal Fe-equivalent supply after deducting Fe delivered by ferroboron. The low-alloyed-steel proxy and its grade qualification are retained. No double purchase of the ferroboron iron.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -3104,7 +3116,9 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>TITANIUM PRECURSOR MANUFACTURE, 2026-10-20. The measured A1 grade contains0.2mass%Ti in its rounded100.1%source ledger. Existing TiO2 feed represented elemental equivalence but omitted oxide-to-metal reduction. Replace that feed by market for titanium,GLO,kilogram at TiO2kg*47.867/(47.867+2*15.999). The native market describes titanium metal made via chlorination to TiCl4 and magnesium reduction/vacuumdistillation in the Kroll process; its background manufacture includes the reduction reagents and wastes. It is a commodity-metal feed reference, not measured A1 manufacturer procurement or extra finished-magnet supply. Do not buy an additional oxide,chloride,Mg charge or aerospace triple-melting route on top. New nominal Ti feed0.00210315999789684kg/kgmagnet, leaving0.001998001998002kgTi after the existing95%magnet retention, exactly0.2/100.1. Keep all other A1 constituents,Ndreduction,15kWh/kgdownstream fabrication and finalEOL unchanged. Default B3 contains no Ti; its recipe,motor/vehicle doses and all per-MJ quantities remain unchanged. This resolves Ti reduction coverage for the A1 sensitivity only; other precursor reduction,alloy/powder/coating and actual-grade/process qualification remain open. Existing supplemental workbook only. All original user scrap-market edits remain unstaged and unchanged.
+          <t>FERROBORON COVERAGE, 2026-10-20. Replace unreduced boric oxide by ferroboron production, carbothermic reduction, 19.6% boron at equal contained-B dose; deduct its iron from the separate Fe-equivalent steel. Nominal retained B/Fe fractions,95%fabrication retention,all other constituents, 15kWh/kg downstream fabrication and finalEOL remain unchanged. The dedicated provider documents source transfers, element/mass closure and remaining industrial qualification. Native steel is still an Fe-equivalent proxy,not an actual purity certificate. Active indicators are unchanged; neither the old boric oxide nor the new ferroboron is covered by the current B definition. Retain the already-added Ndreduction and A1titanium metal. Other rare-earth/Ca reduction and magnet powder, alloy-process specificity and coating remain open.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+TITANIUM PRECURSOR MANUFACTURE, 2026-10-20. The measured A1 grade contains0.2mass%Ti in its rounded100.1%source ledger. Existing TiO2 feed represented elemental equivalence but omitted oxide-to-metal reduction. Replace that feed by market for titanium,GLO,kilogram at TiO2kg*47.867/(47.867+2*15.999). The native market describes titanium metal made via chlorination to TiCl4 and magnesium reduction/vacuumdistillation in the Kroll process; its background manufacture includes the reduction reagents and wastes. It is a commodity-metal feed reference, not measured A1 manufacturer procurement or extra finished-magnet supply. Do not buy an additional oxide,chloride,Mg charge or aerospace triple-melting route on top. New nominal Ti feed0.00210315999789684kg/kgmagnet, leaving0.001998001998002kgTi after the existing95%magnet retention, exactly0.2/100.1. Keep all other A1 constituents,Ndreduction,15kWh/kgdownstream fabrication and finalEOL unchanged. Default B3 contains no Ti; its recipe,motor/vehicle doses and all per-MJ quantities remain unchanged. This resolves Ti reduction coverage for the A1 sensitivity only; other precursor reduction,alloy/powder/coating and actual-grade/process qualification remain open. Existing supplemental workbook only. All original user scrap-market edits remain unstaged and unchanged.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 NEODYMIUM REDUCTION COVERAGE, 2026-10-20. Replace only the Nd2O3-equivalent feed by equal contained Nd metal from neodymium production, molten salt electrolysis. The provider has explicit oxide/electrode/fluoride/gas/waste balances and documented engineering assumptions. Existing magnet fractions,95%fabrication retention,15kWh/kg downstream fabrication,other precursors and finalEOL are unchanged. Pr/Tb/Dy/Ho and B/Ca/Ti precursor reduction,alloy/powder process specificity and coating remain separate gaps; this is not a complete industrial magnet inventory.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
@@ -3385,11 +3399,11 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>market for boric oxide</t>
+          <t>ferroboron production, carbothermic reduction, 19.6% boron</t>
         </is>
       </c>
       <c r="B140">
-        <v>0.03047505102132883</v>
+        <v>0.048286836686407035</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -3408,12 +3422,17 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>boric oxide</t>
+          <t>ferroboron, 19.6% boron</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Manufactured ferroboron supplies the former contained-B dose. Its accompanying80.4%Fe is deducted from the separate steel input; B/Fe fractions and95%magnet retention unchanged.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>boric oxide</t>
+          <t>ferroboron, 19.6% boron</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3553,7 @@
         </is>
       </c>
       <c r="B144">
-        <v>0.696145959303854</v>
+        <v>0.6573233426079828</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -3554,6 +3573,11 @@
       <c r="G144" t="inlineStr">
         <is>
           <t>steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Remaining nominal Fe-equivalent supply after deducting Fe delivered by ferroboron. The low-alloyed-steel proxy and its grade qualification are retained. No double purchase of the ferroboron iron.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -10822,6 +10846,427 @@
       <c r="I408" t="inlineStr">
         <is>
           <t>metal working, average for copper product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>ferroboron production, carbothermic reduction, 19.6% boron</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>ferroboron, 19.6% boron</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B415">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov/sites/default/files/2022-02/Neodymium%20Magnets%20Supply%20Chain%20Report%20-%20Final_0.pdf ; https://patents.google.com/patent/GB2155494A/en ; https://patents.google.com/patent/US7704450B2/en ; https://www.pyrometallurgy.co.za/InfaconVI/1285-Yucel.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>FERROBORON REDUCTION COVERAGE, 2026-10-20. One kg nominal binary Fe-B alloy, 19.6 wt% B and 80.4 wt% Fe, supplies alloying boron rather than unreduced oxide. DOE2022 section2.2.1.3 identifies ferroboron as the NdFeB feed (usual17-20%B). This is a reconstructed engineering reference, NOT a measured magnet supplier. GB2155494A reports19.6%B ferroboron and9463kWh for1358kg from an oxide/wood/charcoal furnace trial: use9463/1358kWh/kg as an explicit utility transfer. Its approximate95%B recovery is selected as a nominal net collection assumption. Do not copy its raw blend: the illustrative blend, average grade and approximate recovery are not a complete mutually closing production ledger. US7704450B2 Example6 establishes a boron-oxide plus metallic-iron/carbon route; its4.3kWh/kg belongs to15-16%B, not this19.6%grade. The present metallic-feed route deliberately differs from the first trial and keeps the original low-alloyed-steel Fe-equivalent proxy. Its actual low-carbon/impurity suitability remains unqualified; it is NOT asserted to be pure iron. Trace C/Si/Mn/Al assays of commercial ferroboron are not inferred from the nominal binary grade. B2O3+3C-&gt;2B+3CO supplies reactive carbon. Buy pure-carbon-equivalent native graphite with10%excess, an explicit fossil-carbon reductant/electrode proxy instead of an unassayed wood/charcoal mixture. Total graphite includes electrode carbon; do not add another consumed electrode on top. Grade-specific electrode fabrication remains unqualified. Select100%Fe collection and99%capture of uncollectedB as oxide; captured oxide has matched negative underground disposal. Uncaptured oxide uses generic finePM as a diagnostic particle proxy; size/speciation and compound toxicity are unknown. Select complete CO postcombustion with ambient air; neither liquidO2 nor an energy recovery credit is purchased. Excess graphite remains spent solid in the reference. Add0.005kg/kg unspecified basic refractory and matched spent treatment with excess graphite through inert disposal. Capture, Fe/Bcollection, refractory, carbon fate, postcombustion, electricity and disposal are tested alternatives, not measured controls or hazard classifications. Actual cooling, infrastructure, gas treatment, feed assays and industrial qualification remain evidence gaps. Native boric oxide already includes its upstream manufacture; no second boric-acid calcination is added. Nominal B/Fe/C/O and aggregate mass close, including ambient oxygen and spent refractory. At each magnet, dose=formeroxidekg*containedBfraction/0.196; subtract dose*0.804 from its separate Fe-equivalent steel. This preserves both measured retained B and Fe after the existing95%fabrication retention, all other ingredients,15kWh/kg downstream fabrication, finished-magnet/EOL and vehicle/per-MJ doses. No second complete magnet is purchased. Existing supplemental workbook only; active B/Fe indicators are unchanged. The current B definition covers neither boric oxide nor ferroboron: its pre-existing coverage gap is reported separately and no corrected system-level B total is claimed. Rare-earth/Ca reduction, powder/alloy process specificity and coating remain open.</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H419" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>ferroboron production, carbothermic reduction, 19.6% boron</t>
+        </is>
+      </c>
+      <c r="B420">
+        <v>1.0</v>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>ferroboron, 19.6% boron</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>market for boric oxide</t>
+        </is>
+      </c>
+      <c r="B421">
+        <v>0.6643425677978481</v>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>boric oxide</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>market for steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="B422">
+        <v>0.804</v>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>market for graphite</t>
+        </is>
+      </c>
+      <c r="B423">
+        <v>0.3593300092506938</v>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>graphite</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B424">
+        <v>6.968335787923417</v>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>market for refractory, basic, packed</t>
+        </is>
+      </c>
+      <c r="B425">
+        <v>0.005</v>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>refractory, basic, packed</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>market for hazardous waste, for underground deposit</t>
+        </is>
+      </c>
+      <c r="B426">
+        <v>-0.03288495710599351</v>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>hazardous waste, for underground deposit</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>market for inert waste, for final disposal</t>
+        </is>
+      </c>
+      <c r="B427">
+        <v>-0.03766636447733584</v>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>inert waste, for final disposal</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>Carbon dioxide, fossil</t>
+        </is>
+      </c>
+      <c r="B428">
+        <v>1.196914523589269</v>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>biosphere</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>Particulate Matter, &lt; 2.5 um</t>
+        </is>
+      </c>
+      <c r="B429">
+        <v>0.00033217128389892463</v>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>biosphere</t>
         </is>
       </c>
     </row>

--- a/premise/data/additional_inventories/lci-electric-car-mechanical-powertrain.xlsx
+++ b/premise/data/additional_inventories/lci-electric-car-mechanical-powertrain.xlsx
@@ -2505,7 +2505,9 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>FERROBORON COVERAGE, 2026-10-20. Replace unreduced boric oxide by ferroboron production, carbothermic reduction, 19.6% boron at equal contained-B dose; deduct its iron from the separate Fe-equivalent steel. Nominal retained B/Fe fractions,95%fabrication retention,all other constituents, 15kWh/kg downstream fabrication and finalEOL remain unchanged. The dedicated provider documents source transfers, element/mass closure and remaining industrial qualification. Native steel is still an Fe-equivalent proxy,not an actual purity certificate. Active indicators are unchanged; neither the old boric oxide nor the new ferroboron is covered by the current B definition. Retain the already-added Ndreduction and A1titanium metal. Other rare-earth/Ca reduction and magnet powder, alloy-process specificity and coating remain open.
+          <t>PRASEODYMIUM REDUCTION COVERAGE, 2026-10-20. Replace Pr6O11-equivalent feed by equal contained Pr metal from praseodymium production, molten salt electrolysis. Its source-informed reference has a Pr-specific oxygen/fluorination balance and explicit Nd-based process transfers/sensitivities,not measured commercial qualification. Keep retained7.4%Pr,95%magnet retention,all other inputs,15kWh/kg downstream fabrication,magnet/motor/vehicle/per-MJ doses and finalEOL unchanged. A1 contains noPr. Retain Nd/ferroboron reduction and A1nativeTi. RemainingTb/Dy/Ho/Ca reduction,magnet alloy/powder/coating and actual-grade qualification are separate gaps. ActivePrindicator remains oxide-only under workbook-only scope; no delivered-Pr system total is certified.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+FERROBORON COVERAGE, 2026-10-20. Replace unreduced boric oxide by ferroboron production, carbothermic reduction, 19.6% boron at equal contained-B dose; deduct its iron from the separate Fe-equivalent steel. Nominal retained B/Fe fractions,95%fabrication retention,all other constituents, 15kWh/kg downstream fabrication and finalEOL remain unchanged. The dedicated provider documents source transfers, element/mass closure and remaining industrial qualification. Native steel is still an Fe-equivalent proxy,not an actual purity certificate. Active indicators are unchanged; neither the old boric oxide nor the new ferroboron is covered by the current B definition. Retain the already-added Ndreduction and A1titanium metal. Other rare-earth/Ca reduction and magnet powder, alloy-process specificity and coating remain open.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 NEODYMIUM REDUCTION COVERAGE, 2026-10-20. Replace only the Nd2O3-equivalent feed by equal contained Nd metal from neodymium production, molten salt electrolysis. The provider has explicit oxide/electrode/fluoride/gas/waste balances and documented engineering assumptions. Existing magnet fractions,95%fabrication retention,15kWh/kg downstream fabrication,other precursors and finalEOL are unchanged. Pr/Tb/Dy/Ho and B/Ca/Ti precursor reduction,alloy/powder process specificity and coating remain separate gaps; this is not a complete industrial magnet inventory.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
@@ -2646,15 +2648,15 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>market for praseodymium oxide</t>
+          <t>praseodymium production, molten salt electrolysis</t>
         </is>
       </c>
       <c r="B112">
-        <v>0.09410939453838814</v>
+        <v>0.07789473684210525</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -2669,12 +2671,17 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>praseodymium oxide</t>
+          <t>praseodymium</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Pr metal at exactly the former contained-Pr-equivalent dose under the existingPr6O11convention. Dedicated manufacture supplies reduction and fluoride preparation once. Retained7.4%Pr and95%magnet retention unchanged.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>praseodymium oxide</t>
+          <t>praseodymium</t>
         </is>
       </c>
     </row>

--- a/premise/data/additional_inventories/lci-electric-car-mechanical-powertrain.xlsx
+++ b/premise/data/additional_inventories/lci-electric-car-mechanical-powertrain.xlsx
@@ -2505,7 +2505,9 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>PRASEODYMIUM REDUCTION COVERAGE, 2026-10-20. Replace Pr6O11-equivalent feed by equal contained Pr metal from praseodymium production, molten salt electrolysis. Its source-informed reference has a Pr-specific oxygen/fluorination balance and explicit Nd-based process transfers/sensitivities,not measured commercial qualification. Keep retained7.4%Pr,95%magnet retention,all other inputs,15kWh/kg downstream fabrication,magnet/motor/vehicle/per-MJ doses and finalEOL unchanged. A1 contains noPr. Retain Nd/ferroboron reduction and A1nativeTi. RemainingTb/Dy/Ho/Ca reduction,magnet alloy/powder/coating and actual-grade qualification are separate gaps. ActivePrindicator remains oxide-only under workbook-only scope; no delivered-Pr system total is certified.
+          <t>HOLMIUM REDUCTION COVERAGE, 2026-10-20. Replace Ho2O3-equivalent feed by equal containedHo from holmium production, calcium reduction. It uses an explicit heavy-REE calcium/fluoride route and a separate calcium-manufacture activity,not Nd/Pr electrolysis. Source classes and engineering recovery,utilities,vessel life and waste assumptions are documented/tested. Keep measuredHo fraction,95%magnet retention,other ingredients,downstream energy,vehicle/per-MJ doses and EOL unchanged. The existing CaO constituent is unchanged: elemental composition alone does not establish that it was added asCa metal. Tb/Dy reduction,industrial qualification and magnet alloy/powder/coating remain gaps. Active Ho/Ca indicators unchanged under workbook-only scope.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+PRASEODYMIUM REDUCTION COVERAGE, 2026-10-20. Replace Pr6O11-equivalent feed by equal contained Pr metal from praseodymium production, molten salt electrolysis. Its source-informed reference has a Pr-specific oxygen/fluorination balance and explicit Nd-based process transfers/sensitivities,not measured commercial qualification. Keep retained7.4%Pr,95%magnet retention,all other inputs,15kWh/kg downstream fabrication,magnet/motor/vehicle/per-MJ doses and finalEOL unchanged. A1 contains noPr. Retain Nd/ferroboron reduction and A1nativeTi. RemainingTb/Dy/Ho/Ca reduction,magnet alloy/powder/coating and actual-grade qualification are separate gaps. ActivePrindicator remains oxide-only under workbook-only scope; no delivered-Pr system total is certified.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 FERROBORON COVERAGE, 2026-10-20. Replace unreduced boric oxide by ferroboron production, carbothermic reduction, 19.6% boron at equal contained-B dose; deduct its iron from the separate Fe-equivalent steel. Nominal retained B/Fe fractions,95%fabrication retention,all other constituents, 15kWh/kg downstream fabrication and finalEOL remain unchanged. The dedicated provider documents source transfers, element/mass closure and remaining industrial qualification. Native steel is still an Fe-equivalent proxy,not an actual purity certificate. Active indicators are unchanged; neither the old boric oxide nor the new ferroboron is covered by the current B definition. Retain the already-added Ndreduction and A1titanium metal. Other rare-earth/Ca reduction and magnet powder, alloy-process specificity and coating remain open.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
@@ -2723,11 +2725,11 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>market for holmium oxide</t>
+          <t>holmium production, calcium reduction</t>
         </is>
       </c>
       <c r="B114">
-        <v>0.020498544414098017</v>
+        <v>0.017894736842105265</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -2746,12 +2748,17 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>holmium oxide</t>
+          <t>holmium</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Ho metal at the former contained-Ho-equivalent dose. Dedicated fluoride/calcium reduction includes Ca manufacture once; measuredHo fraction and95%magnet retention unchanged.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>holmium oxide</t>
+          <t>holmium</t>
         </is>
       </c>
     </row>
@@ -3123,7 +3130,9 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>FERROBORON COVERAGE, 2026-10-20. Replace unreduced boric oxide by ferroboron production, carbothermic reduction, 19.6% boron at equal contained-B dose; deduct its iron from the separate Fe-equivalent steel. Nominal retained B/Fe fractions,95%fabrication retention,all other constituents, 15kWh/kg downstream fabrication and finalEOL remain unchanged. The dedicated provider documents source transfers, element/mass closure and remaining industrial qualification. Native steel is still an Fe-equivalent proxy,not an actual purity certificate. Active indicators are unchanged; neither the old boric oxide nor the new ferroboron is covered by the current B definition. Retain the already-added Ndreduction and A1titanium metal. Other rare-earth/Ca reduction and magnet powder, alloy-process specificity and coating remain open.
+          <t>HOLMIUM REDUCTION COVERAGE, 2026-10-20. Replace Ho2O3-equivalent feed by equal containedHo from holmium production, calcium reduction. It uses an explicit heavy-REE calcium/fluoride route and a separate calcium-manufacture activity,not Nd/Pr electrolysis. Source classes and engineering recovery,utilities,vessel life and waste assumptions are documented/tested. Keep measuredHo fraction,95%magnet retention,other ingredients,downstream energy,vehicle/per-MJ doses and EOL unchanged. The existing CaO constituent is unchanged: elemental composition alone does not establish that it was added asCa metal. Tb/Dy reduction,industrial qualification and magnet alloy/powder/coating remain gaps. Active Ho/Ca indicators unchanged under workbook-only scope.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+FERROBORON COVERAGE, 2026-10-20. Replace unreduced boric oxide by ferroboron production, carbothermic reduction, 19.6% boron at equal contained-B dose; deduct its iron from the separate Fe-equivalent steel. Nominal retained B/Fe fractions,95%fabrication retention,all other constituents, 15kWh/kg downstream fabrication and finalEOL remain unchanged. The dedicated provider documents source transfers, element/mass closure and remaining industrial qualification. Native steel is still an Fe-equivalent proxy,not an actual purity certificate. Active indicators are unchanged; neither the old boric oxide nor the new ferroboron is covered by the current B definition. Retain the already-added Ndreduction and A1titanium metal. Other rare-earth/Ca reduction and magnet powder, alloy-process specificity and coating remain open.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 TITANIUM PRECURSOR MANUFACTURE, 2026-10-20. The measured A1 grade contains0.2mass%Ti in its rounded100.1%source ledger. Existing TiO2 feed represented elemental equivalence but omitted oxide-to-metal reduction. Replace that feed by market for titanium,GLO,kilogram at TiO2kg*47.867/(47.867+2*15.999). The native market describes titanium metal made via chlorination to TiCl4 and magnesium reduction/vacuumdistillation in the Kroll process; its background manufacture includes the reduction reagents and wastes. It is a commodity-metal feed reference, not measured A1 manufacturer procurement or extra finished-magnet supply. Do not buy an additional oxide,chloride,Mg charge or aerospace triple-melting route on top. New nominal Ti feed0.00210315999789684kg/kgmagnet, leaving0.001998001998002kgTi after the existing95%magnet retention, exactly0.2/100.1. Keep all other A1 constituents,Ndreduction,15kWh/kgdownstream fabrication and finalEOL unchanged. Default B3 contains no Ti; its recipe,motor/vehicle doses and all per-MJ quantities remain unchanged. This resolves Ti reduction coverage for the A1 sensitivity only; other precursor reduction,alloy/powder/coating and actual-grade/process qualification remain open. Existing supplemental workbook only. All original user scrap-market edits remain unstaged and unchanged.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
@@ -3336,11 +3345,11 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>market for holmium oxide</t>
+          <t>holmium production, calcium reduction</t>
         </is>
       </c>
       <c r="B138">
-        <v>0.026501027038265044</v>
+        <v>0.023134759976865236</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -3359,12 +3368,17 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>holmium oxide</t>
+          <t>holmium</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Ho metal at the former contained-Ho-equivalent dose. Dedicated fluoride/calcium reduction includes Ca manufacture once; measuredHo fraction and95%magnet retention unchanged.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>holmium oxide</t>
+          <t>holmium</t>
         </is>
       </c>
     </row>

--- a/premise/data/additional_inventories/lci-electric-car-mechanical-powertrain.xlsx
+++ b/premise/data/additional_inventories/lci-electric-car-mechanical-powertrain.xlsx
@@ -2505,7 +2505,9 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>HOLMIUM REDUCTION COVERAGE, 2026-10-20. Replace Ho2O3-equivalent feed by equal containedHo from holmium production, calcium reduction. It uses an explicit heavy-REE calcium/fluoride route and a separate calcium-manufacture activity,not Nd/Pr electrolysis. Source classes and engineering recovery,utilities,vessel life and waste assumptions are documented/tested. Keep measuredHo fraction,95%magnet retention,other ingredients,downstream energy,vehicle/per-MJ doses and EOL unchanged. The existing CaO constituent is unchanged: elemental composition alone does not establish that it was added asCa metal. Tb/Dy reduction,industrial qualification and magnet alloy/powder/coating remain gaps. Active Ho/Ca indicators unchanged under workbook-only scope.
+          <t>TERBIUM REDUCTION COVERAGE, 2026-10-20. Replace Tb4O7-equivalent feed by equal containedTb from terbium production, calcium reduction. Explicit H2pre-reduction handles mixed-valence oxygen beforeHF/calcium reduction; engineering recovery,utilities,vessel and treatment assumptions are documented/tested,not commercial qualification. Keep Tb fraction,95%magnet retention,other ingredients,energy,equipment/per-MJ doses and EOL unchanged. Keep existing magnetCaO constituent pending speciation. Dy reduction and alloy/powder/coating remain open. ActiveTb/Ca indicators unchanged under workbook-only scope.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+HOLMIUM REDUCTION COVERAGE, 2026-10-20. Replace Ho2O3-equivalent feed by equal containedHo from holmium production, calcium reduction. It uses an explicit heavy-REE calcium/fluoride route and a separate calcium-manufacture activity,not Nd/Pr electrolysis. Source classes and engineering recovery,utilities,vessel life and waste assumptions are documented/tested. Keep measuredHo fraction,95%magnet retention,other ingredients,downstream energy,vehicle/per-MJ doses and EOL unchanged. The existing CaO constituent is unchanged: elemental composition alone does not establish that it was added asCa metal. Tb/Dy reduction,industrial qualification and magnet alloy/powder/coating remain gaps. Active Ho/Ca indicators unchanged under workbook-only scope.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 PRASEODYMIUM REDUCTION COVERAGE, 2026-10-20. Replace Pr6O11-equivalent feed by equal contained Pr metal from praseodymium production, molten salt electrolysis. Its source-informed reference has a Pr-specific oxygen/fluorination balance and explicit Nd-based process transfers/sensitivities,not measured commercial qualification. Keep retained7.4%Pr,95%magnet retention,all other inputs,15kWh/kg downstream fabrication,magnet/motor/vehicle/per-MJ doses and finalEOL unchanged. A1 contains noPr. Retain Nd/ferroboron reduction and A1nativeTi. RemainingTb/Dy/Ho/Ca reduction,magnet alloy/powder/coating and actual-grade qualification are separate gaps. ActivePrindicator remains oxide-only under workbook-only scope; no delivered-Pr system total is certified.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
@@ -2690,11 +2692,11 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>market for terbium oxide</t>
+          <t>terbium production, calcium reduction</t>
         </is>
       </c>
       <c r="B113">
-        <v>0.00619038071051995</v>
+        <v>0.005263157894736842</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -2713,12 +2715,17 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>terbium oxide</t>
+          <t>terbium</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Tb metal at the former contained-Tb-equivalent dose. Dedicated H2/HF/calcium reduction includes Ca manufacture once. ExistingTb fraction and95%magnet retention unchanged.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>terbium oxide</t>
+          <t>terbium</t>
         </is>
       </c>
     </row>
@@ -3130,7 +3137,9 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>HOLMIUM REDUCTION COVERAGE, 2026-10-20. Replace Ho2O3-equivalent feed by equal containedHo from holmium production, calcium reduction. It uses an explicit heavy-REE calcium/fluoride route and a separate calcium-manufacture activity,not Nd/Pr electrolysis. Source classes and engineering recovery,utilities,vessel life and waste assumptions are documented/tested. Keep measuredHo fraction,95%magnet retention,other ingredients,downstream energy,vehicle/per-MJ doses and EOL unchanged. The existing CaO constituent is unchanged: elemental composition alone does not establish that it was added asCa metal. Tb/Dy reduction,industrial qualification and magnet alloy/powder/coating remain gaps. Active Ho/Ca indicators unchanged under workbook-only scope.
+          <t>TERBIUM REDUCTION COVERAGE, 2026-10-20. Replace Tb4O7-equivalent feed by equal containedTb from terbium production, calcium reduction. Explicit H2pre-reduction handles mixed-valence oxygen beforeHF/calcium reduction; engineering recovery,utilities,vessel and treatment assumptions are documented/tested,not commercial qualification. Keep Tb fraction,95%magnet retention,other ingredients,energy,equipment/per-MJ doses and EOL unchanged. Keep existing magnetCaO constituent pending speciation. Dy reduction and alloy/powder/coating remain open. ActiveTb/Ca indicators unchanged under workbook-only scope.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+HOLMIUM REDUCTION COVERAGE, 2026-10-20. Replace Ho2O3-equivalent feed by equal containedHo from holmium production, calcium reduction. It uses an explicit heavy-REE calcium/fluoride route and a separate calcium-manufacture activity,not Nd/Pr electrolysis. Source classes and engineering recovery,utilities,vessel life and waste assumptions are documented/tested. Keep measuredHo fraction,95%magnet retention,other ingredients,downstream energy,vehicle/per-MJ doses and EOL unchanged. The existing CaO constituent is unchanged: elemental composition alone does not establish that it was added asCa metal. Tb/Dy reduction,industrial qualification and magnet alloy/powder/coating remain gaps. Active Ho/Ca indicators unchanged under workbook-only scope.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 FERROBORON COVERAGE, 2026-10-20. Replace unreduced boric oxide by ferroboron production, carbothermic reduction, 19.6% boron at equal contained-B dose; deduct its iron from the separate Fe-equivalent steel. Nominal retained B/Fe fractions,95%fabrication retention,all other constituents, 15kWh/kg downstream fabrication and finalEOL remain unchanged. The dedicated provider documents source transfers, element/mass closure and remaining industrial qualification. Native steel is still an Fe-equivalent proxy,not an actual purity certificate. Active indicators are unchanged; neither the old boric oxide nor the new ferroboron is covered by the current B definition. Retain the already-added Ndreduction and A1titanium metal. Other rare-earth/Ca reduction and magnet powder, alloy-process specificity and coating remain open.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
@@ -3275,11 +3284,11 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>market for terbium oxide</t>
+          <t>terbium production, calcium reduction</t>
         </is>
       </c>
       <c r="B136">
-        <v>0.007421035816807132</v>
+        <v>0.006309479993690519</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -3298,12 +3307,17 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>terbium oxide</t>
+          <t>terbium</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Tb metal at the former contained-Tb-equivalent dose. Dedicated H2/HF/calcium reduction includes Ca manufacture once. ExistingTb fraction and95%magnet retention unchanged.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>terbium oxide</t>
+          <t>terbium</t>
         </is>
       </c>
     </row>

--- a/premise/data/additional_inventories/lci-electric-car-mechanical-powertrain.xlsx
+++ b/premise/data/additional_inventories/lci-electric-car-mechanical-powertrain.xlsx
@@ -3137,7 +3137,9 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>TERBIUM REDUCTION COVERAGE, 2026-10-20. Replace Tb4O7-equivalent feed by equal containedTb from terbium production, calcium reduction. Explicit H2pre-reduction handles mixed-valence oxygen beforeHF/calcium reduction; engineering recovery,utilities,vessel and treatment assumptions are documented/tested,not commercial qualification. Keep Tb fraction,95%magnet retention,other ingredients,energy,equipment/per-MJ doses and EOL unchanged. Keep existing magnetCaO constituent pending speciation. Dy reduction and alloy/powder/coating remain open. ActiveTb/Ca indicators unchanged under workbook-only scope.
+          <t>DYSPROSIUM REDUCTION COVERAGE, 2026-10-20. Replace Dy2O3-equivalent feed by equal containedDy from dysprosium production, calcium reduction. Dy-specific reported reduction response and Ca/DyF3 charge inform an explicit engineering ledger,not a commercial-purity claim. HF preparation,utilities,passivation and vessellife are tested assumptions. Retain A1Dy0.5/100.1,95%fabricationretention,otheringredients,downstreamenergy,allequipment/per-MJ doses and EOL. B3 has noDy and is unchanged. ExistingCaO constituent pending speciation; alloy/powder/coating and industrialqualification remain open. ActiveDy/Ca indicators unchanged under workbook-only scope.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+TERBIUM REDUCTION COVERAGE, 2026-10-20. Replace Tb4O7-equivalent feed by equal containedTb from terbium production, calcium reduction. Explicit H2pre-reduction handles mixed-valence oxygen beforeHF/calcium reduction; engineering recovery,utilities,vessel and treatment assumptions are documented/tested,not commercial qualification. Keep Tb fraction,95%magnet retention,other ingredients,energy,equipment/per-MJ doses and EOL unchanged. Keep existing magnetCaO constituent pending speciation. Dy reduction and alloy/powder/coating remain open. ActiveTb/Ca indicators unchanged under workbook-only scope.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 HOLMIUM REDUCTION COVERAGE, 2026-10-20. Replace Ho2O3-equivalent feed by equal containedHo from holmium production, calcium reduction. It uses an explicit heavy-REE calcium/fluoride route and a separate calcium-manufacture activity,not Nd/Pr electrolysis. Source classes and engineering recovery,utilities,vessel life and waste assumptions are documented/tested. Keep measuredHo fraction,95%magnet retention,other ingredients,downstream energy,vehicle/per-MJ doses and EOL unchanged. The existing CaO constituent is unchanged: elemental composition alone does not establish that it was added asCa metal. Tb/Dy reduction,industrial qualification and magnet alloy/powder/coating remain gaps. Active Ho/Ca indicators unchanged under workbook-only scope.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
@@ -3324,11 +3326,11 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>market for dysprosium oxide</t>
+          <t>dysprosium production, calcium reduction</t>
         </is>
       </c>
       <c r="B137">
-        <v>0.006034402844119443</v>
+        <v>0.005257899994742099</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -3347,12 +3349,17 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>dysprosium oxide</t>
+          <t>dysprosium</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Dy metal at the former contained-Dy-equivalent dose. Dedicated fluoride/calcium reduction reuses Ca manufacture once. ExistingA1 Dy fraction and95%magnetretention unchanged. DefaultB3 contains noDy.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>dysprosium oxide</t>
+          <t>dysprosium</t>
         </is>
       </c>
     </row>

--- a/premise/data/additional_inventories/lci-electric-car-mechanical-powertrain.xlsx
+++ b/premise/data/additional_inventories/lci-electric-car-mechanical-powertrain.xlsx
@@ -2505,7 +2505,9 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>TERBIUM REDUCTION COVERAGE, 2026-10-20. Replace Tb4O7-equivalent feed by equal containedTb from terbium production, calcium reduction. Explicit H2pre-reduction handles mixed-valence oxygen beforeHF/calcium reduction; engineering recovery,utilities,vessel and treatment assumptions are documented/tested,not commercial qualification. Keep Tb fraction,95%magnet retention,other ingredients,energy,equipment/per-MJ doses and EOL unchanged. Keep existing magnetCaO constituent pending speciation. Dy reduction and alloy/powder/coating remain open. ActiveTb/Ca indicators unchanged under workbook-only scope.
+          <t>HYDROGEN DECREPITATION COVERAGE, 2026-10-20. Sprecher etal2014 DOI10.1021/es404596q, SI spreadsheet Hydrogen decrepitation!C13, supplies0.0043kgH2 per1kgalloy; SI prose0.43wt% confirms percentage conversion. Add0.0043*(1/0.95)=0.00452631578947368kgH2/kgfinishedmagnet at the existing95%fabrication retention. This source uptake is a process-class transfer to the measured B3/A1 compositions,not a grade-specific factory measurement; test uptake and rare-earth-mole scaling. Source assumes no gas recovery. Select full release of the temporary hydride hydrogen after vacuum sintering through canonicalHydrogen,air,kg; no extra metalmass or retained hydrogen is added to the finishedmagnet. Equal external input/release closes Hmass; release versus oxidized/recovered fate remains an explicit process assumption. Source2014electrolysis supply is not asserted as a current worldmix: use nativeRERmerchantH2 reference with official legacy migrations. Preserve15kWh/kg combinedmanufacturingelectricity; it already covers the electricity allowance for decrepitation/milling/pressing/sintering/finishing and is not evidence that H2was purchased. Do not add the source0.1kWh stage on top. Keep metalfeeds,95%retention,scrap,EOL,motor/vehicle/perMJ doses unchanged. NETL2014derived workbook Hydrogen Decrepitation!A4=0.43 is labelledwt% but passed as a fraction inB9/B11; do not copy its100foldH2overstatement. OriginalSI0.0043kg/kg is authoritative. Original source0.43wt%hydrogen and processing data refer to an olderNdFeB design,not commercial qualification of these grades. Ca speciation,coatingchemistry/mass,industrialprocess utilities and remaining manufacturing evidence remain open. Existing sourceJones2025SI reports any undissolved resin coating filtered before ICP-OES; it does not identifyCa phase or prove nickel plating. No numerical Ca or coating change follows solely from that elemental assay. Workbook-only correction; active indicators unchanged.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+TERBIUM REDUCTION COVERAGE, 2026-10-20. Replace Tb4O7-equivalent feed by equal containedTb from terbium production, calcium reduction. Explicit H2pre-reduction handles mixed-valence oxygen beforeHF/calcium reduction; engineering recovery,utilities,vessel and treatment assumptions are documented/tested,not commercial qualification. Keep Tb fraction,95%magnet retention,other ingredients,energy,equipment/per-MJ doses and EOL unchanged. Keep existing magnetCaO constituent pending speciation. Dy reduction and alloy/powder/coating remain open. ActiveTb/Ca indicators unchanged under workbook-only scope.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 HOLMIUM REDUCTION COVERAGE, 2026-10-20. Replace Ho2O3-equivalent feed by equal containedHo from holmium production, calcium reduction. It uses an explicit heavy-REE calcium/fluoride route and a separate calcium-manufacture activity,not Nd/Pr electrolysis. Source classes and engineering recovery,utilities,vessel life and waste assumptions are documented/tested. Keep measuredHo fraction,95%magnet retention,other ingredients,downstream energy,vehicle/per-MJ doses and EOL unchanged. The existing CaO constituent is unchanged: elemental composition alone does not establish that it was added asCa metal. Tb/Dy reduction,industrial qualification and magnet alloy/powder/coating remain gaps. Active Ho/Ca indicators unchanged under workbook-only scope.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
@@ -3059,6 +3061,76 @@
         </is>
       </c>
     </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>market for hydrogen, gaseous, medium pressure, merchant</t>
+        </is>
+      </c>
+      <c r="B123">
+        <v>0.004526315789473684</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>hydrogen, gaseous, medium pressure, merchant</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Source0.43wt%=0.0043kgH2/kgalloy times existing1/0.95fabricationthroughput. Native merchant-H2 supply reference. No second processing-electricity purchase.</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>hydrogen, gaseous, medium pressure, merchant</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Hydrogen</t>
+        </is>
+      </c>
+      <c r="B124">
+        <v>0.004526315789473684</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>biosphere</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Selected no-recovery/no-oxidation fate:temporary hydride uptake released at sintering. Equal externalH2input/output; not a measured stack factor. Alternative recovery evaluated separately.</t>
+        </is>
+      </c>
+    </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
@@ -3137,7 +3209,9 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>DYSPROSIUM REDUCTION COVERAGE, 2026-10-20. Replace Dy2O3-equivalent feed by equal containedDy from dysprosium production, calcium reduction. Dy-specific reported reduction response and Ca/DyF3 charge inform an explicit engineering ledger,not a commercial-purity claim. HF preparation,utilities,passivation and vessellife are tested assumptions. Retain A1Dy0.5/100.1,95%fabricationretention,otheringredients,downstreamenergy,allequipment/per-MJ doses and EOL. B3 has noDy and is unchanged. ExistingCaO constituent pending speciation; alloy/powder/coating and industrialqualification remain open. ActiveDy/Ca indicators unchanged under workbook-only scope.
+          <t>HYDROGEN DECREPITATION COVERAGE, 2026-10-20. Sprecher etal2014 DOI10.1021/es404596q, SI spreadsheet Hydrogen decrepitation!C13, supplies0.0043kgH2 per1kgalloy; SI prose0.43wt% confirms percentage conversion. Add0.0043*(1/0.95)=0.00452631578947368kgH2/kgfinishedmagnet at the existing95%fabrication retention. This source uptake is a process-class transfer to the measured B3/A1 compositions,not a grade-specific factory measurement; test uptake and rare-earth-mole scaling. Source assumes no gas recovery. Select full release of the temporary hydride hydrogen after vacuum sintering through canonicalHydrogen,air,kg; no extra metalmass or retained hydrogen is added to the finishedmagnet. Equal external input/release closes Hmass; release versus oxidized/recovered fate remains an explicit process assumption. Source2014electrolysis supply is not asserted as a current worldmix: use nativeRERmerchantH2 reference with official legacy migrations. Preserve15kWh/kg combinedmanufacturingelectricity; it already covers the electricity allowance for decrepitation/milling/pressing/sintering/finishing and is not evidence that H2was purchased. Do not add the source0.1kWh stage on top. Keep metalfeeds,95%retention,scrap,EOL,motor/vehicle/perMJ doses unchanged. NETL2014derived workbook Hydrogen Decrepitation!A4=0.43 is labelledwt% but passed as a fraction inB9/B11; do not copy its100foldH2overstatement. OriginalSI0.0043kg/kg is authoritative. Original source0.43wt%hydrogen and processing data refer to an olderNdFeB design,not commercial qualification of these grades. Ca speciation,coatingchemistry/mass,industrialprocess utilities and remaining manufacturing evidence remain open. Existing sourceJones2025SI reports any undissolved resin coating filtered before ICP-OES; it does not identifyCa phase or prove nickel plating. No numerical Ca or coating change follows solely from that elemental assay. Workbook-only correction; active indicators unchanged.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+DYSPROSIUM REDUCTION COVERAGE, 2026-10-20. Replace Dy2O3-equivalent feed by equal containedDy from dysprosium production, calcium reduction. Dy-specific reported reduction response and Ca/DyF3 charge inform an explicit engineering ledger,not a commercial-purity claim. HF preparation,utilities,passivation and vessellife are tested assumptions. Retain A1Dy0.5/100.1,95%fabricationretention,otheringredients,downstreamenergy,allequipment/per-MJ doses and EOL. B3 has noDy and is unchanged. ExistingCaO constituent pending speciation; alloy/powder/coating and industrialqualification remain open. ActiveDy/Ca indicators unchanged under workbook-only scope.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 TERBIUM REDUCTION COVERAGE, 2026-10-20. Replace Tb4O7-equivalent feed by equal containedTb from terbium production, calcium reduction. Explicit H2pre-reduction handles mixed-valence oxygen beforeHF/calcium reduction; engineering recovery,utilities,vessel and treatment assumptions are documented/tested,not commercial qualification. Keep Tb fraction,95%magnet retention,other ingredients,energy,equipment/per-MJ doses and EOL unchanged. Keep existing magnetCaO constituent pending speciation. Dy reduction and alloy/powder/coating remain open. ActiveTb/Ca indicators unchanged under workbook-only scope.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
@@ -3733,6 +3807,76 @@
         </is>
       </c>
     </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>market for hydrogen, gaseous, medium pressure, merchant</t>
+        </is>
+      </c>
+      <c r="B148">
+        <v>0.004526315789473684</v>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>hydrogen, gaseous, medium pressure, merchant</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Source0.43wt%=0.0043kgH2/kgalloy times existing1/0.95fabricationthroughput. Native merchant-H2 supply reference. No second processing-electricity purchase.</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>hydrogen, gaseous, medium pressure, merchant</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Hydrogen</t>
+        </is>
+      </c>
+      <c r="B149">
+        <v>0.004526315789473684</v>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>biosphere</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Selected no-recovery/no-oxidation fate:temporary hydride uptake released at sintering. Equal externalH2input/output; not a measured stack factor. Alternative recovery evaluated separately.</t>
+        </is>
+      </c>
+    </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
